--- a/Prototypes/KiwiFruit/Yield.xlsx
+++ b/Prototypes/KiwiFruit/Yield.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB4A3BB-9510-4EB1-9089-A220AE2D3C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1F05B7-EB18-4243-8EB8-4B8557381F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SingleBerryFW" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8836" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8780" uniqueCount="33">
   <si>
     <t>SimulationName</t>
   </si>
@@ -40085,8 +40085,7 @@
         <v>16.594899999999999</v>
       </c>
       <c r="G630">
-        <f>F630</f>
-        <v>16.594899999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H630" t="s">
         <v>27</v>
@@ -40108,13 +40107,6 @@
       <c r="F631">
         <v>20.163</v>
       </c>
-      <c r="G631">
-        <f>F631</f>
-        <v>20.163</v>
-      </c>
-      <c r="H631" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
@@ -40269,7 +40261,7 @@
         <v>13.636800000000001</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>10</v>
       </c>
@@ -40286,7 +40278,7 @@
         <v>15.061199999999999</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>10</v>
       </c>
@@ -40303,7 +40295,7 @@
         <v>17.472000000000001</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>10</v>
       </c>
@@ -40320,7 +40312,7 @@
         <v>17.167999999999999</v>
       </c>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>10</v>
       </c>
@@ -40337,7 +40329,7 @@
         <v>18.612000000000002</v>
       </c>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>10</v>
       </c>
@@ -40354,7 +40346,7 @@
         <v>18.392800000000001</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>10</v>
       </c>
@@ -40370,15 +40362,8 @@
       <c r="F646">
         <v>19.4208</v>
       </c>
-      <c r="G646">
-        <f>F646</f>
-        <v>19.4208</v>
-      </c>
-      <c r="H646" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>10</v>
       </c>
@@ -40395,7 +40380,7 @@
         <v>20.248800000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>10</v>
       </c>
@@ -40412,7 +40397,7 @@
         <v>20.370199999999997</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>10</v>
       </c>
@@ -40429,7 +40414,7 @@
         <v>21.318899999999999</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>10</v>
       </c>
@@ -40446,7 +40431,7 @@
         <v>5.0204000000000004</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>10</v>
       </c>
@@ -40463,7 +40448,7 @@
         <v>4.4855999999999998</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>10</v>
       </c>
@@ -40480,7 +40465,7 @@
         <v>4.4676</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>10</v>
       </c>
@@ -40497,7 +40482,7 @@
         <v>4.758</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>10</v>
       </c>
@@ -40514,7 +40499,7 @@
         <v>12.196100000000001</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>10</v>
       </c>
@@ -40531,7 +40516,7 @@
         <v>11.2395</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>10</v>
       </c>
@@ -40820,7 +40805,7 @@
         <v>17.6311</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>10</v>
       </c>
@@ -40837,7 +40822,7 @@
         <v>15.853599999999998</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>10</v>
       </c>
@@ -40854,7 +40839,7 @@
         <v>20.432100000000002</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>10</v>
       </c>
@@ -40871,7 +40856,7 @@
         <v>17.929400000000001</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>10</v>
       </c>
@@ -40888,7 +40873,7 @@
         <v>15.902999999999999</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>10</v>
       </c>
@@ -40905,7 +40890,7 @@
         <v>15.250999999999999</v>
       </c>
     </row>
-    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>10</v>
       </c>
@@ -40922,7 +40907,7 @@
         <v>21.367199999999997</v>
       </c>
     </row>
-    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>10</v>
       </c>
@@ -40939,7 +40924,7 @@
         <v>18.768000000000001</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>10</v>
       </c>
@@ -40956,7 +40941,7 @@
         <v>16.2181</v>
       </c>
     </row>
-    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>10</v>
       </c>
@@ -40973,7 +40958,7 @@
         <v>16.453599999999998</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>10</v>
       </c>
@@ -40989,15 +40974,8 @@
       <c r="F682">
         <v>17.5168</v>
       </c>
-      <c r="G682">
-        <f>F682</f>
-        <v>17.5168</v>
-      </c>
-      <c r="H682" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>10</v>
       </c>
@@ -41013,12 +40991,8 @@
       <c r="F683">
         <v>20.984000000000002</v>
       </c>
-      <c r="G683">
-        <f t="shared" ref="G683:G746" si="9">F683</f>
-        <v>20.984000000000002</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>10</v>
       </c>
@@ -41034,12 +41008,8 @@
       <c r="F684">
         <v>19.8352</v>
       </c>
-      <c r="G684">
-        <f t="shared" si="9"/>
-        <v>19.8352</v>
-      </c>
-    </row>
-    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>10</v>
       </c>
@@ -41055,12 +41025,8 @@
       <c r="F685">
         <v>16.9938</v>
       </c>
-      <c r="G685">
-        <f t="shared" si="9"/>
-        <v>16.9938</v>
-      </c>
-    </row>
-    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>10</v>
       </c>
@@ -41076,12 +41042,8 @@
       <c r="F686">
         <v>21.454999999999998</v>
       </c>
-      <c r="G686">
-        <f t="shared" si="9"/>
-        <v>21.454999999999998</v>
-      </c>
-    </row>
-    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>10</v>
       </c>
@@ -41097,12 +41059,8 @@
       <c r="F687">
         <v>18.9468</v>
       </c>
-      <c r="G687">
-        <f t="shared" si="9"/>
-        <v>18.9468</v>
-      </c>
-    </row>
-    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>10</v>
       </c>
@@ -41118,12 +41076,8 @@
       <c r="F688">
         <v>18.04</v>
       </c>
-      <c r="G688">
-        <f t="shared" si="9"/>
-        <v>18.04</v>
-      </c>
-    </row>
-    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>10</v>
       </c>
@@ -41139,12 +41093,8 @@
       <c r="F689">
         <v>20.445600000000002</v>
       </c>
-      <c r="G689">
-        <f t="shared" si="9"/>
-        <v>20.445600000000002</v>
-      </c>
-    </row>
-    <row r="690" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>10</v>
       </c>
@@ -41160,12 +41110,8 @@
       <c r="F690">
         <v>18.638999999999999</v>
       </c>
-      <c r="G690">
-        <f t="shared" si="9"/>
-        <v>18.638999999999999</v>
-      </c>
-    </row>
-    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>10</v>
       </c>
@@ -41181,12 +41127,8 @@
       <c r="F691">
         <v>21.87</v>
       </c>
-      <c r="G691">
-        <f t="shared" si="9"/>
-        <v>21.87</v>
-      </c>
-    </row>
-    <row r="692" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>10</v>
       </c>
@@ -41202,12 +41144,8 @@
       <c r="F692">
         <v>20.708099999999998</v>
       </c>
-      <c r="G692">
-        <f t="shared" si="9"/>
-        <v>20.708099999999998</v>
-      </c>
-    </row>
-    <row r="693" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>10</v>
       </c>
@@ -41223,12 +41161,8 @@
       <c r="F693">
         <v>18.211200000000002</v>
       </c>
-      <c r="G693">
-        <f t="shared" si="9"/>
-        <v>18.211200000000002</v>
-      </c>
-    </row>
-    <row r="694" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>10</v>
       </c>
@@ -41244,12 +41178,8 @@
       <c r="F694">
         <v>20.832000000000004</v>
       </c>
-      <c r="G694">
-        <f t="shared" si="9"/>
-        <v>20.832000000000004</v>
-      </c>
-    </row>
-    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>10</v>
       </c>
@@ -41265,12 +41195,8 @@
       <c r="F695">
         <v>22.302000000000003</v>
       </c>
-      <c r="G695">
-        <f t="shared" si="9"/>
-        <v>22.302000000000003</v>
-      </c>
-    </row>
-    <row r="696" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>10</v>
       </c>
@@ -41286,12 +41212,8 @@
       <c r="F696">
         <v>19.825800000000001</v>
       </c>
-      <c r="G696">
-        <f t="shared" si="9"/>
-        <v>19.825800000000001</v>
-      </c>
-    </row>
-    <row r="697" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>11</v>
       </c>
@@ -41307,12 +41229,8 @@
       <c r="F697">
         <v>5.5297999999999989</v>
       </c>
-      <c r="G697">
-        <f t="shared" si="9"/>
-        <v>5.5297999999999989</v>
-      </c>
-    </row>
-    <row r="698" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>11</v>
       </c>
@@ -41328,12 +41246,8 @@
       <c r="F698">
         <v>3.9312</v>
       </c>
-      <c r="G698">
-        <f t="shared" si="9"/>
-        <v>3.9312</v>
-      </c>
-    </row>
-    <row r="699" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>11</v>
       </c>
@@ -41349,12 +41263,8 @@
       <c r="F699">
         <v>11.007999999999999</v>
       </c>
-      <c r="G699">
-        <f t="shared" si="9"/>
-        <v>11.007999999999999</v>
-      </c>
-    </row>
-    <row r="700" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>11</v>
       </c>
@@ -41370,12 +41280,8 @@
       <c r="F700">
         <v>9.4163999999999994</v>
       </c>
-      <c r="G700">
-        <f t="shared" si="9"/>
-        <v>9.4163999999999994</v>
-      </c>
-    </row>
-    <row r="701" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>11</v>
       </c>
@@ -41391,12 +41297,8 @@
       <c r="F701">
         <v>13.7995</v>
       </c>
-      <c r="G701">
-        <f t="shared" si="9"/>
-        <v>13.7995</v>
-      </c>
-    </row>
-    <row r="702" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>11</v>
       </c>
@@ -41412,12 +41314,8 @@
       <c r="F702">
         <v>11.226800000000001</v>
       </c>
-      <c r="G702">
-        <f t="shared" si="9"/>
-        <v>11.226800000000001</v>
-      </c>
-    </row>
-    <row r="703" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>11</v>
       </c>
@@ -41433,12 +41331,8 @@
       <c r="F703">
         <v>15.111599999999999</v>
       </c>
-      <c r="G703">
-        <f t="shared" si="9"/>
-        <v>15.111599999999999</v>
-      </c>
-    </row>
-    <row r="704" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>11</v>
       </c>
@@ -41452,10 +41346,6 @@
         <v>6</v>
       </c>
       <c r="F704">
-        <v>12.8232</v>
-      </c>
-      <c r="G704">
-        <f t="shared" si="9"/>
         <v>12.8232</v>
       </c>
     </row>
@@ -41475,10 +41365,6 @@
       <c r="F705">
         <v>17.962200000000003</v>
       </c>
-      <c r="G705">
-        <f t="shared" si="9"/>
-        <v>17.962200000000003</v>
-      </c>
     </row>
     <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
@@ -41496,10 +41382,6 @@
       <c r="F706">
         <v>14.860800000000001</v>
       </c>
-      <c r="G706">
-        <f t="shared" si="9"/>
-        <v>14.860800000000001</v>
-      </c>
     </row>
     <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
@@ -41517,10 +41399,6 @@
       <c r="F707">
         <v>17.060500000000001</v>
       </c>
-      <c r="G707">
-        <f t="shared" si="9"/>
-        <v>17.060500000000001</v>
-      </c>
     </row>
     <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
@@ -41538,10 +41416,6 @@
       <c r="F708">
         <v>15.463800000000001</v>
       </c>
-      <c r="G708">
-        <f t="shared" si="9"/>
-        <v>15.463800000000001</v>
-      </c>
     </row>
     <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
@@ -41559,10 +41433,6 @@
       <c r="F709">
         <v>18.667300000000001</v>
       </c>
-      <c r="G709">
-        <f t="shared" si="9"/>
-        <v>18.667300000000001</v>
-      </c>
     </row>
     <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
@@ -41580,10 +41450,6 @@
       <c r="F710">
         <v>16.658200000000001</v>
       </c>
-      <c r="G710">
-        <f t="shared" si="9"/>
-        <v>16.658200000000001</v>
-      </c>
     </row>
     <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
@@ -41601,10 +41467,6 @@
       <c r="F711">
         <v>16.6402</v>
       </c>
-      <c r="G711">
-        <f t="shared" si="9"/>
-        <v>16.6402</v>
-      </c>
     </row>
     <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
@@ -41622,10 +41484,6 @@
       <c r="F712">
         <v>19.811399999999999</v>
       </c>
-      <c r="G712">
-        <f t="shared" si="9"/>
-        <v>19.811399999999999</v>
-      </c>
     </row>
     <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
@@ -41644,8 +41502,7 @@
         <v>19.400500000000001</v>
       </c>
       <c r="G713">
-        <f t="shared" si="9"/>
-        <v>19.400500000000001</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="H713" t="s">
         <v>27</v>
@@ -41667,13 +41524,6 @@
       <c r="F714">
         <v>16.364999999999998</v>
       </c>
-      <c r="G714">
-        <f t="shared" si="9"/>
-        <v>16.364999999999998</v>
-      </c>
-      <c r="H714" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
@@ -41691,10 +41541,6 @@
       <c r="F715">
         <v>20.764800000000001</v>
       </c>
-      <c r="G715">
-        <f t="shared" si="9"/>
-        <v>20.764800000000001</v>
-      </c>
     </row>
     <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
@@ -41712,10 +41558,6 @@
       <c r="F716">
         <v>19.067399999999999</v>
       </c>
-      <c r="G716">
-        <f t="shared" si="9"/>
-        <v>19.067399999999999</v>
-      </c>
     </row>
     <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
@@ -41733,10 +41575,6 @@
       <c r="F717">
         <v>20.5335</v>
       </c>
-      <c r="G717">
-        <f t="shared" si="9"/>
-        <v>20.5335</v>
-      </c>
     </row>
     <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
@@ -41754,10 +41592,6 @@
       <c r="F718">
         <v>19.3644</v>
       </c>
-      <c r="G718">
-        <f t="shared" si="9"/>
-        <v>19.3644</v>
-      </c>
     </row>
     <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
@@ -41775,10 +41609,6 @@
       <c r="F719">
         <v>20.930400000000006</v>
       </c>
-      <c r="G719">
-        <f t="shared" si="9"/>
-        <v>20.930400000000006</v>
-      </c>
     </row>
     <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
@@ -41796,12 +41626,8 @@
       <c r="F720">
         <v>18.645</v>
       </c>
-      <c r="G720">
-        <f t="shared" si="9"/>
-        <v>18.645</v>
-      </c>
-    </row>
-    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>11</v>
       </c>
@@ -41817,12 +41643,8 @@
       <c r="F721">
         <v>20.050700000000003</v>
       </c>
-      <c r="G721">
-        <f t="shared" si="9"/>
-        <v>20.050700000000003</v>
-      </c>
-    </row>
-    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>11</v>
       </c>
@@ -41838,12 +41660,8 @@
       <c r="F722">
         <v>19.302800000000001</v>
       </c>
-      <c r="G722">
-        <f t="shared" si="9"/>
-        <v>19.302800000000001</v>
-      </c>
-    </row>
-    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>11</v>
       </c>
@@ -41859,12 +41677,8 @@
       <c r="F723">
         <v>5.1040000000000001</v>
       </c>
-      <c r="G723">
-        <f t="shared" si="9"/>
-        <v>5.1040000000000001</v>
-      </c>
-    </row>
-    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>11</v>
       </c>
@@ -41880,12 +41694,8 @@
       <c r="F724">
         <v>11.519600000000001</v>
       </c>
-      <c r="G724">
-        <f t="shared" si="9"/>
-        <v>11.519600000000001</v>
-      </c>
-    </row>
-    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>11</v>
       </c>
@@ -41901,12 +41711,8 @@
       <c r="F725">
         <v>15.008799999999999</v>
       </c>
-      <c r="G725">
-        <f t="shared" si="9"/>
-        <v>15.008799999999999</v>
-      </c>
-    </row>
-    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>11</v>
       </c>
@@ -41922,12 +41728,8 @@
       <c r="F726">
         <v>17.391000000000002</v>
       </c>
-      <c r="G726">
-        <f t="shared" si="9"/>
-        <v>17.391000000000002</v>
-      </c>
-    </row>
-    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>11</v>
       </c>
@@ -41943,12 +41745,8 @@
       <c r="F727">
         <v>19.684200000000001</v>
       </c>
-      <c r="G727">
-        <f t="shared" si="9"/>
-        <v>19.684200000000001</v>
-      </c>
-    </row>
-    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>11</v>
       </c>
@@ -41964,12 +41762,8 @@
       <c r="F728">
         <v>20.144000000000002</v>
       </c>
-      <c r="G728">
-        <f t="shared" si="9"/>
-        <v>20.144000000000002</v>
-      </c>
-    </row>
-    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>11</v>
       </c>
@@ -41985,12 +41779,8 @@
       <c r="F729">
         <v>21.559699999999999</v>
       </c>
-      <c r="G729">
-        <f t="shared" si="9"/>
-        <v>21.559699999999999</v>
-      </c>
-    </row>
-    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>11</v>
       </c>
@@ -42006,12 +41796,8 @@
       <c r="F730">
         <v>22.3249</v>
       </c>
-      <c r="G730">
-        <f t="shared" si="9"/>
-        <v>22.3249</v>
-      </c>
-    </row>
-    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>11</v>
       </c>
@@ -42027,15 +41813,8 @@
       <c r="F731">
         <v>22.423000000000002</v>
       </c>
-      <c r="G731">
-        <f t="shared" si="9"/>
-        <v>22.423000000000002</v>
-      </c>
-      <c r="H731" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>11</v>
       </c>
@@ -42051,12 +41830,8 @@
       <c r="F732">
         <v>23.824199999999998</v>
       </c>
-      <c r="G732">
-        <f t="shared" si="9"/>
-        <v>23.824199999999998</v>
-      </c>
-    </row>
-    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>11</v>
       </c>
@@ -42072,12 +41847,8 @@
       <c r="F733">
         <v>23.8596</v>
       </c>
-      <c r="G733">
-        <f t="shared" si="9"/>
-        <v>23.8596</v>
-      </c>
-    </row>
-    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>11</v>
       </c>
@@ -42093,12 +41864,8 @@
       <c r="F734">
         <v>23.692900000000005</v>
       </c>
-      <c r="G734">
-        <f t="shared" si="9"/>
-        <v>23.692900000000005</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>11</v>
       </c>
@@ -42114,12 +41881,8 @@
       <c r="F735">
         <v>22.8583</v>
       </c>
-      <c r="G735">
-        <f t="shared" si="9"/>
-        <v>22.8583</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>11</v>
       </c>
@@ -42135,12 +41898,8 @@
       <c r="F736">
         <v>5.0960000000000001</v>
       </c>
-      <c r="G736">
-        <f t="shared" si="9"/>
-        <v>5.0960000000000001</v>
-      </c>
-    </row>
-    <row r="737" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>11</v>
       </c>
@@ -42156,12 +41915,8 @@
       <c r="F737">
         <v>5.0466000000000006</v>
       </c>
-      <c r="G737">
-        <f t="shared" si="9"/>
-        <v>5.0466000000000006</v>
-      </c>
-    </row>
-    <row r="738" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>11</v>
       </c>
@@ -42177,12 +41932,8 @@
       <c r="F738">
         <v>5.4350999999999985</v>
       </c>
-      <c r="G738">
-        <f t="shared" si="9"/>
-        <v>5.4350999999999985</v>
-      </c>
-    </row>
-    <row r="739" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>11</v>
       </c>
@@ -42198,12 +41949,8 @@
       <c r="F739">
         <v>5.9670000000000005</v>
       </c>
-      <c r="G739">
-        <f t="shared" si="9"/>
-        <v>5.9670000000000005</v>
-      </c>
-    </row>
-    <row r="740" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>11</v>
       </c>
@@ -42219,12 +41966,8 @@
       <c r="F740">
         <v>12.300900000000002</v>
       </c>
-      <c r="G740">
-        <f t="shared" si="9"/>
-        <v>12.300900000000002</v>
-      </c>
-    </row>
-    <row r="741" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>11</v>
       </c>
@@ -42240,12 +41983,8 @@
       <c r="F741">
         <v>10.933</v>
       </c>
-      <c r="G741">
-        <f t="shared" si="9"/>
-        <v>10.933</v>
-      </c>
-    </row>
-    <row r="742" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>11</v>
       </c>
@@ -42261,12 +42000,8 @@
       <c r="F742">
         <v>11.904000000000002</v>
       </c>
-      <c r="G742">
-        <f t="shared" si="9"/>
-        <v>11.904000000000002</v>
-      </c>
-    </row>
-    <row r="743" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>11</v>
       </c>
@@ -42282,12 +42017,8 @@
       <c r="F743">
         <v>11.153999999999998</v>
       </c>
-      <c r="G743">
-        <f t="shared" si="9"/>
-        <v>11.153999999999998</v>
-      </c>
-    </row>
-    <row r="744" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>11</v>
       </c>
@@ -42303,12 +42034,8 @@
       <c r="F744">
         <v>15.537600000000003</v>
       </c>
-      <c r="G744">
-        <f t="shared" si="9"/>
-        <v>15.537600000000003</v>
-      </c>
-    </row>
-    <row r="745" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>11</v>
       </c>
@@ -42324,12 +42051,8 @@
       <c r="F745">
         <v>15.332100000000001</v>
       </c>
-      <c r="G745">
-        <f t="shared" si="9"/>
-        <v>15.332100000000001</v>
-      </c>
-    </row>
-    <row r="746" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>11</v>
       </c>
@@ -42345,12 +42068,8 @@
       <c r="F746">
         <v>14.284599999999998</v>
       </c>
-      <c r="G746">
-        <f t="shared" si="9"/>
-        <v>14.284599999999998</v>
-      </c>
-    </row>
-    <row r="747" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>11</v>
       </c>
@@ -42366,12 +42085,8 @@
       <c r="F747">
         <v>14.5383</v>
       </c>
-      <c r="G747">
-        <f t="shared" ref="G747:G810" si="10">F747</f>
-        <v>14.5383</v>
-      </c>
-    </row>
-    <row r="748" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>11</v>
       </c>
@@ -42387,12 +42102,8 @@
       <c r="F748">
         <v>17.3004</v>
       </c>
-      <c r="G748">
-        <f t="shared" si="10"/>
-        <v>17.3004</v>
-      </c>
-    </row>
-    <row r="749" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>11</v>
       </c>
@@ -42408,12 +42119,8 @@
       <c r="F749">
         <v>15.833999999999998</v>
       </c>
-      <c r="G749">
-        <f t="shared" si="10"/>
-        <v>15.833999999999998</v>
-      </c>
-    </row>
-    <row r="750" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>11</v>
       </c>
@@ -42429,12 +42136,8 @@
       <c r="F750">
         <v>16.7029</v>
       </c>
-      <c r="G750">
-        <f t="shared" si="10"/>
-        <v>16.7029</v>
-      </c>
-    </row>
-    <row r="751" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>11</v>
       </c>
@@ -42450,12 +42153,8 @@
       <c r="F751">
         <v>16.610599999999998</v>
       </c>
-      <c r="G751">
-        <f t="shared" si="10"/>
-        <v>16.610599999999998</v>
-      </c>
-    </row>
-    <row r="752" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>11</v>
       </c>
@@ -42471,12 +42170,8 @@
       <c r="F752">
         <v>20.302099999999999</v>
       </c>
-      <c r="G752">
-        <f t="shared" si="10"/>
-        <v>20.302099999999999</v>
-      </c>
-    </row>
-    <row r="753" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>11</v>
       </c>
@@ -42492,12 +42187,8 @@
       <c r="F753">
         <v>17.552</v>
       </c>
-      <c r="G753">
-        <f t="shared" si="10"/>
-        <v>17.552</v>
-      </c>
-    </row>
-    <row r="754" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>11</v>
       </c>
@@ -42513,12 +42204,8 @@
       <c r="F754">
         <v>18.972800000000003</v>
       </c>
-      <c r="G754">
-        <f t="shared" si="10"/>
-        <v>18.972800000000003</v>
-      </c>
-    </row>
-    <row r="755" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>11</v>
       </c>
@@ -42534,12 +42221,8 @@
       <c r="F755">
         <v>18.937799999999999</v>
       </c>
-      <c r="G755">
-        <f t="shared" si="10"/>
-        <v>18.937799999999999</v>
-      </c>
-    </row>
-    <row r="756" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>11</v>
       </c>
@@ -42555,12 +42238,8 @@
       <c r="F756">
         <v>20.720700000000001</v>
       </c>
-      <c r="G756">
-        <f t="shared" si="10"/>
-        <v>20.720700000000001</v>
-      </c>
-    </row>
-    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>11</v>
       </c>
@@ -42576,12 +42255,8 @@
       <c r="F757">
         <v>18.531100000000002</v>
       </c>
-      <c r="G757">
-        <f t="shared" si="10"/>
-        <v>18.531100000000002</v>
-      </c>
-    </row>
-    <row r="758" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>11</v>
       </c>
@@ -42597,12 +42272,8 @@
       <c r="F758">
         <v>19.588800000000003</v>
       </c>
-      <c r="G758">
-        <f t="shared" si="10"/>
-        <v>19.588800000000003</v>
-      </c>
-    </row>
-    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>11</v>
       </c>
@@ -42618,12 +42289,8 @@
       <c r="F759">
         <v>19.1751</v>
       </c>
-      <c r="G759">
-        <f t="shared" si="10"/>
-        <v>19.1751</v>
-      </c>
-    </row>
-    <row r="760" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>11</v>
       </c>
@@ -42639,12 +42306,8 @@
       <c r="F760">
         <v>21.203699999999998</v>
       </c>
-      <c r="G760">
-        <f t="shared" si="10"/>
-        <v>21.203699999999998</v>
-      </c>
-    </row>
-    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>11</v>
       </c>
@@ -42660,12 +42323,8 @@
       <c r="F761">
         <v>18.908000000000001</v>
       </c>
-      <c r="G761">
-        <f t="shared" si="10"/>
-        <v>18.908000000000001</v>
-      </c>
-    </row>
-    <row r="762" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>11</v>
       </c>
@@ -42681,12 +42340,8 @@
       <c r="F762">
         <v>19.421499999999998</v>
       </c>
-      <c r="G762">
-        <f t="shared" si="10"/>
-        <v>19.421499999999998</v>
-      </c>
-    </row>
-    <row r="763" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>11</v>
       </c>
@@ -42702,12 +42357,8 @@
       <c r="F763">
         <v>20.1936</v>
       </c>
-      <c r="G763">
-        <f t="shared" si="10"/>
-        <v>20.1936</v>
-      </c>
-    </row>
-    <row r="764" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>11</v>
       </c>
@@ -42723,12 +42374,8 @@
       <c r="F764">
         <v>19.071399999999997</v>
       </c>
-      <c r="G764">
-        <f t="shared" si="10"/>
-        <v>19.071399999999997</v>
-      </c>
-    </row>
-    <row r="765" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>11</v>
       </c>
@@ -42744,12 +42391,8 @@
       <c r="F765">
         <v>20.347199999999997</v>
       </c>
-      <c r="G765">
-        <f t="shared" si="10"/>
-        <v>20.347199999999997</v>
-      </c>
-    </row>
-    <row r="766" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>11</v>
       </c>
@@ -42765,12 +42408,8 @@
       <c r="F766">
         <v>20.553000000000001</v>
       </c>
-      <c r="G766">
-        <f t="shared" si="10"/>
-        <v>20.553000000000001</v>
-      </c>
-    </row>
-    <row r="767" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>11</v>
       </c>
@@ -42786,12 +42425,8 @@
       <c r="F767">
         <v>22.151000000000003</v>
       </c>
-      <c r="G767">
-        <f t="shared" si="10"/>
-        <v>22.151000000000003</v>
-      </c>
-    </row>
-    <row r="768" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>11</v>
       </c>
@@ -42807,12 +42442,8 @@
       <c r="F768">
         <v>23.3748</v>
       </c>
-      <c r="G768">
-        <f t="shared" si="10"/>
-        <v>23.3748</v>
-      </c>
-    </row>
-    <row r="769" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>11</v>
       </c>
@@ -42828,15 +42459,8 @@
       <c r="F769">
         <v>21.057599999999997</v>
       </c>
-      <c r="G769">
-        <f t="shared" si="10"/>
-        <v>21.057599999999997</v>
-      </c>
-      <c r="H769" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>11</v>
       </c>
@@ -42852,15 +42476,8 @@
       <c r="F770">
         <v>19.488000000000003</v>
       </c>
-      <c r="G770">
-        <f t="shared" si="10"/>
-        <v>19.488000000000003</v>
-      </c>
-      <c r="H770" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="771" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>11</v>
       </c>
@@ -42876,15 +42493,8 @@
       <c r="F771">
         <v>20.897999999999996</v>
       </c>
-      <c r="G771">
-        <f t="shared" si="10"/>
-        <v>20.897999999999996</v>
-      </c>
-      <c r="H771" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="772" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>11</v>
       </c>
@@ -42900,12 +42510,8 @@
       <c r="F772">
         <v>23.063099999999999</v>
       </c>
-      <c r="G772">
-        <f t="shared" si="10"/>
-        <v>23.063099999999999</v>
-      </c>
-    </row>
-    <row r="773" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="773" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>11</v>
       </c>
@@ -42921,12 +42527,8 @@
       <c r="F773">
         <v>20.915199999999999</v>
       </c>
-      <c r="G773">
-        <f t="shared" si="10"/>
-        <v>20.915199999999999</v>
-      </c>
-    </row>
-    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="774" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>11</v>
       </c>
@@ -42942,12 +42544,8 @@
       <c r="F774">
         <v>21.977199999999996</v>
       </c>
-      <c r="G774">
-        <f t="shared" si="10"/>
-        <v>21.977199999999996</v>
-      </c>
-    </row>
-    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="775" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>11</v>
       </c>
@@ -42963,12 +42561,8 @@
       <c r="F775">
         <v>21.648000000000003</v>
       </c>
-      <c r="G775">
-        <f t="shared" si="10"/>
-        <v>21.648000000000003</v>
-      </c>
-    </row>
-    <row r="776" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>11</v>
       </c>
@@ -42984,12 +42578,8 @@
       <c r="F776">
         <v>23.957999999999998</v>
       </c>
-      <c r="G776">
-        <f t="shared" si="10"/>
-        <v>23.957999999999998</v>
-      </c>
-    </row>
-    <row r="777" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="777" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>11</v>
       </c>
@@ -43005,12 +42595,8 @@
       <c r="F777">
         <v>20.253599999999999</v>
       </c>
-      <c r="G777">
-        <f t="shared" si="10"/>
-        <v>20.253599999999999</v>
-      </c>
-    </row>
-    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="778" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>11</v>
       </c>
@@ -43026,12 +42612,8 @@
       <c r="F778">
         <v>22.2911</v>
       </c>
-      <c r="G778">
-        <f t="shared" si="10"/>
-        <v>22.2911</v>
-      </c>
-    </row>
-    <row r="779" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="779" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>11</v>
       </c>
@@ -43047,12 +42629,8 @@
       <c r="F779">
         <v>22.445999999999998</v>
       </c>
-      <c r="G779">
-        <f t="shared" si="10"/>
-        <v>22.445999999999998</v>
-      </c>
-    </row>
-    <row r="780" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="780" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>11</v>
       </c>
@@ -43068,12 +42646,8 @@
       <c r="F780">
         <v>21.300999999999998</v>
       </c>
-      <c r="G780">
-        <f t="shared" si="10"/>
-        <v>21.300999999999998</v>
-      </c>
-    </row>
-    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="781" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>11</v>
       </c>
@@ -43089,12 +42663,8 @@
       <c r="F781">
         <v>21.573600000000003</v>
       </c>
-      <c r="G781">
-        <f t="shared" si="10"/>
-        <v>21.573600000000003</v>
-      </c>
-    </row>
-    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="782" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>11</v>
       </c>
@@ -43110,12 +42680,8 @@
       <c r="F782">
         <v>23.470199999999998</v>
       </c>
-      <c r="G782">
-        <f t="shared" si="10"/>
-        <v>23.470199999999998</v>
-      </c>
-    </row>
-    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="783" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>11</v>
       </c>
@@ -43131,12 +42697,8 @@
       <c r="F783">
         <v>20.5625</v>
       </c>
-      <c r="G783">
-        <f t="shared" si="10"/>
-        <v>20.5625</v>
-      </c>
-    </row>
-    <row r="784" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="784" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>11</v>
       </c>
@@ -43152,12 +42714,8 @@
       <c r="F784">
         <v>21.905999999999999</v>
       </c>
-      <c r="G784">
-        <f t="shared" si="10"/>
-        <v>21.905999999999999</v>
-      </c>
-    </row>
-    <row r="785" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="785" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>11</v>
       </c>
@@ -43173,12 +42731,8 @@
       <c r="F785">
         <v>23.157800000000002</v>
       </c>
-      <c r="G785">
-        <f t="shared" si="10"/>
-        <v>23.157800000000002</v>
-      </c>
-    </row>
-    <row r="786" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="786" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>12</v>
       </c>
@@ -43194,12 +42748,8 @@
       <c r="F786">
         <v>4.8048000000000002</v>
       </c>
-      <c r="G786">
-        <f t="shared" si="10"/>
-        <v>4.8048000000000002</v>
-      </c>
-    </row>
-    <row r="787" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="787" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>12</v>
       </c>
@@ -43215,12 +42765,8 @@
       <c r="F787">
         <v>3.8827999999999996</v>
       </c>
-      <c r="G787">
-        <f t="shared" si="10"/>
-        <v>3.8827999999999996</v>
-      </c>
-    </row>
-    <row r="788" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="788" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>12</v>
       </c>
@@ -43236,12 +42782,8 @@
       <c r="F788">
         <v>10.344599999999998</v>
       </c>
-      <c r="G788">
-        <f t="shared" si="10"/>
-        <v>10.344599999999998</v>
-      </c>
-    </row>
-    <row r="789" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="789" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>12</v>
       </c>
@@ -43257,12 +42799,8 @@
       <c r="F789">
         <v>9.0858000000000008</v>
       </c>
-      <c r="G789">
-        <f t="shared" si="10"/>
-        <v>9.0858000000000008</v>
-      </c>
-    </row>
-    <row r="790" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="790" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>12</v>
       </c>
@@ -43278,12 +42816,8 @@
       <c r="F790">
         <v>12.855700000000002</v>
       </c>
-      <c r="G790">
-        <f t="shared" si="10"/>
-        <v>12.855700000000002</v>
-      </c>
-    </row>
-    <row r="791" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="791" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>12</v>
       </c>
@@ -43299,12 +42833,8 @@
       <c r="F791">
         <v>11.650799999999998</v>
       </c>
-      <c r="G791">
-        <f t="shared" si="10"/>
-        <v>11.650799999999998</v>
-      </c>
-    </row>
-    <row r="792" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="792" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>12</v>
       </c>
@@ -43320,12 +42850,8 @@
       <c r="F792">
         <v>14.632400000000001</v>
       </c>
-      <c r="G792">
-        <f t="shared" si="10"/>
-        <v>14.632400000000001</v>
-      </c>
-    </row>
-    <row r="793" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="793" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>12</v>
       </c>
@@ -43341,12 +42867,8 @@
       <c r="F793">
         <v>13.244699999999998</v>
       </c>
-      <c r="G793">
-        <f t="shared" si="10"/>
-        <v>13.244699999999998</v>
-      </c>
-    </row>
-    <row r="794" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="794" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>12</v>
       </c>
@@ -43362,12 +42884,8 @@
       <c r="F794">
         <v>16.777199999999997</v>
       </c>
-      <c r="G794">
-        <f t="shared" si="10"/>
-        <v>16.777199999999997</v>
-      </c>
-    </row>
-    <row r="795" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="795" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>12</v>
       </c>
@@ -43383,12 +42901,8 @@
       <c r="F795">
         <v>15.1228</v>
       </c>
-      <c r="G795">
-        <f t="shared" si="10"/>
-        <v>15.1228</v>
-      </c>
-    </row>
-    <row r="796" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="796" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>12</v>
       </c>
@@ -43404,12 +42918,8 @@
       <c r="F796">
         <v>17.513000000000002</v>
       </c>
-      <c r="G796">
-        <f t="shared" si="10"/>
-        <v>17.513000000000002</v>
-      </c>
-    </row>
-    <row r="797" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="797" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>12</v>
       </c>
@@ -43425,12 +42935,8 @@
       <c r="F797">
         <v>15.6104</v>
       </c>
-      <c r="G797">
-        <f t="shared" si="10"/>
-        <v>15.6104</v>
-      </c>
-    </row>
-    <row r="798" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="798" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>12</v>
       </c>
@@ -43446,12 +42952,8 @@
       <c r="F798">
         <v>18.920000000000002</v>
       </c>
-      <c r="G798">
-        <f t="shared" si="10"/>
-        <v>18.920000000000002</v>
-      </c>
-    </row>
-    <row r="799" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="799" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>12</v>
       </c>
@@ -43467,12 +42969,8 @@
       <c r="F799">
         <v>15.888</v>
       </c>
-      <c r="G799">
-        <f t="shared" si="10"/>
-        <v>15.888</v>
-      </c>
-    </row>
-    <row r="800" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="800" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>12</v>
       </c>
@@ -43486,10 +42984,6 @@
         <v>6</v>
       </c>
       <c r="F800">
-        <v>19.357200000000002</v>
-      </c>
-      <c r="G800">
-        <f t="shared" si="10"/>
         <v>19.357200000000002</v>
       </c>
     </row>
@@ -43509,10 +43003,6 @@
       <c r="F801">
         <v>17.024000000000001</v>
       </c>
-      <c r="G801">
-        <f t="shared" si="10"/>
-        <v>17.024000000000001</v>
-      </c>
     </row>
     <row r="802" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
@@ -43531,8 +43021,7 @@
         <v>20.462399999999999</v>
       </c>
       <c r="G802">
-        <f t="shared" si="10"/>
-        <v>20.462399999999999</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="H802" t="s">
         <v>27</v>
@@ -43554,13 +43043,6 @@
       <c r="F803">
         <v>18.094000000000001</v>
       </c>
-      <c r="G803">
-        <f t="shared" si="10"/>
-        <v>18.094000000000001</v>
-      </c>
-      <c r="H803" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="804" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
@@ -43578,10 +43060,6 @@
       <c r="F804">
         <v>20.833099999999998</v>
       </c>
-      <c r="G804">
-        <f t="shared" si="10"/>
-        <v>20.833099999999998</v>
-      </c>
     </row>
     <row r="805" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
@@ -43599,10 +43077,6 @@
       <c r="F805">
         <v>17.977800000000002</v>
       </c>
-      <c r="G805">
-        <f t="shared" si="10"/>
-        <v>17.977800000000002</v>
-      </c>
     </row>
     <row r="806" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
@@ -43620,10 +43094,6 @@
       <c r="F806">
         <v>20.935199999999998</v>
       </c>
-      <c r="G806">
-        <f t="shared" si="10"/>
-        <v>20.935199999999998</v>
-      </c>
     </row>
     <row r="807" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
@@ -43641,10 +43111,6 @@
       <c r="F807">
         <v>18.2515</v>
       </c>
-      <c r="G807">
-        <f t="shared" si="10"/>
-        <v>18.2515</v>
-      </c>
     </row>
     <row r="808" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
@@ -43662,10 +43128,6 @@
       <c r="F808">
         <v>4.3664999999999994</v>
       </c>
-      <c r="G808">
-        <f t="shared" si="10"/>
-        <v>4.3664999999999994</v>
-      </c>
     </row>
     <row r="809" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
@@ -43683,10 +43145,6 @@
       <c r="F809">
         <v>9.3225000000000016</v>
       </c>
-      <c r="G809">
-        <f t="shared" si="10"/>
-        <v>9.3225000000000016</v>
-      </c>
     </row>
     <row r="810" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
@@ -43704,10 +43162,6 @@
       <c r="F810">
         <v>12.8369</v>
       </c>
-      <c r="G810">
-        <f t="shared" si="10"/>
-        <v>12.8369</v>
-      </c>
     </row>
     <row r="811" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
@@ -43725,10 +43179,6 @@
       <c r="F811">
         <v>14.657400000000001</v>
       </c>
-      <c r="G811">
-        <f t="shared" ref="G811:G874" si="11">F811</f>
-        <v>14.657400000000001</v>
-      </c>
     </row>
     <row r="812" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
@@ -43746,10 +43196,6 @@
       <c r="F812">
         <v>16.758600000000001</v>
       </c>
-      <c r="G812">
-        <f t="shared" si="11"/>
-        <v>16.758600000000001</v>
-      </c>
     </row>
     <row r="813" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
@@ -43767,10 +43213,6 @@
       <c r="F813">
         <v>17.236800000000002</v>
       </c>
-      <c r="G813">
-        <f t="shared" si="11"/>
-        <v>17.236800000000002</v>
-      </c>
     </row>
     <row r="814" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
@@ -43788,10 +43230,6 @@
       <c r="F814">
         <v>17.750700000000002</v>
       </c>
-      <c r="G814">
-        <f t="shared" si="11"/>
-        <v>17.750700000000002</v>
-      </c>
     </row>
     <row r="815" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
@@ -43809,10 +43247,6 @@
       <c r="F815">
         <v>18.916800000000002</v>
       </c>
-      <c r="G815">
-        <f t="shared" si="11"/>
-        <v>18.916800000000002</v>
-      </c>
     </row>
     <row r="816" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
@@ -43830,15 +43264,8 @@
       <c r="F816">
         <v>19.771000000000001</v>
       </c>
-      <c r="G816">
-        <f t="shared" si="11"/>
-        <v>19.771000000000001</v>
-      </c>
-      <c r="H816" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="817" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="817" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>12</v>
       </c>
@@ -43854,12 +43281,8 @@
       <c r="F817">
         <v>19.929600000000001</v>
       </c>
-      <c r="G817">
-        <f t="shared" si="11"/>
-        <v>19.929600000000001</v>
-      </c>
-    </row>
-    <row r="818" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="818" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>12</v>
       </c>
@@ -43875,12 +43298,8 @@
       <c r="F818">
         <v>20.310400000000001</v>
       </c>
-      <c r="G818">
-        <f t="shared" si="11"/>
-        <v>20.310400000000001</v>
-      </c>
-    </row>
-    <row r="819" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="819" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>12</v>
       </c>
@@ -43896,12 +43315,8 @@
       <c r="F819">
         <v>4.2911999999999999</v>
       </c>
-      <c r="G819">
-        <f t="shared" si="11"/>
-        <v>4.2911999999999999</v>
-      </c>
-    </row>
-    <row r="820" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="820" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>12</v>
       </c>
@@ -43917,12 +43332,8 @@
       <c r="F820">
         <v>5.2806000000000006</v>
       </c>
-      <c r="G820">
-        <f t="shared" si="11"/>
-        <v>5.2806000000000006</v>
-      </c>
-    </row>
-    <row r="821" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="821" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>12</v>
       </c>
@@ -43938,12 +43349,8 @@
       <c r="F821">
         <v>4.6694000000000004</v>
       </c>
-      <c r="G821">
-        <f t="shared" si="11"/>
-        <v>4.6694000000000004</v>
-      </c>
-    </row>
-    <row r="822" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="822" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>12</v>
       </c>
@@ -43959,12 +43366,8 @@
       <c r="F822">
         <v>5.0616000000000012</v>
       </c>
-      <c r="G822">
-        <f t="shared" si="11"/>
-        <v>5.0616000000000012</v>
-      </c>
-    </row>
-    <row r="823" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="823" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>12</v>
       </c>
@@ -43980,12 +43383,8 @@
       <c r="F823">
         <v>9.9429999999999996</v>
       </c>
-      <c r="G823">
-        <f t="shared" si="11"/>
-        <v>9.9429999999999996</v>
-      </c>
-    </row>
-    <row r="824" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="824" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>12</v>
       </c>
@@ -44001,12 +43400,8 @@
       <c r="F824">
         <v>10.384</v>
       </c>
-      <c r="G824">
-        <f t="shared" si="11"/>
-        <v>10.384</v>
-      </c>
-    </row>
-    <row r="825" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="825" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>12</v>
       </c>
@@ -44022,12 +43417,8 @@
       <c r="F825">
         <v>8.9551999999999996</v>
       </c>
-      <c r="G825">
-        <f t="shared" si="11"/>
-        <v>8.9551999999999996</v>
-      </c>
-    </row>
-    <row r="826" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="826" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>12</v>
       </c>
@@ -44043,12 +43434,8 @@
       <c r="F826">
         <v>10.104000000000001</v>
       </c>
-      <c r="G826">
-        <f t="shared" si="11"/>
-        <v>10.104000000000001</v>
-      </c>
-    </row>
-    <row r="827" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="827" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>12</v>
       </c>
@@ -44064,12 +43451,8 @@
       <c r="F827">
         <v>12.623800000000001</v>
       </c>
-      <c r="G827">
-        <f t="shared" si="11"/>
-        <v>12.623800000000001</v>
-      </c>
-    </row>
-    <row r="828" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="828" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>12</v>
       </c>
@@ -44085,12 +43468,8 @@
       <c r="F828">
         <v>13.277000000000001</v>
       </c>
-      <c r="G828">
-        <f t="shared" si="11"/>
-        <v>13.277000000000001</v>
-      </c>
-    </row>
-    <row r="829" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="829" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>12</v>
       </c>
@@ -44106,12 +43485,8 @@
       <c r="F829">
         <v>11.276800000000001</v>
       </c>
-      <c r="G829">
-        <f t="shared" si="11"/>
-        <v>11.276800000000001</v>
-      </c>
-    </row>
-    <row r="830" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="830" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>12</v>
       </c>
@@ -44127,12 +43502,8 @@
       <c r="F830">
         <v>13.3527</v>
       </c>
-      <c r="G830">
-        <f t="shared" si="11"/>
-        <v>13.3527</v>
-      </c>
-    </row>
-    <row r="831" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="831" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>12</v>
       </c>
@@ -44148,12 +43519,8 @@
       <c r="F831">
         <v>14.0128</v>
       </c>
-      <c r="G831">
-        <f t="shared" si="11"/>
-        <v>14.0128</v>
-      </c>
-    </row>
-    <row r="832" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="832" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>12</v>
       </c>
@@ -44169,12 +43536,8 @@
       <c r="F832">
         <v>15.7628</v>
       </c>
-      <c r="G832">
-        <f t="shared" si="11"/>
-        <v>15.7628</v>
-      </c>
-    </row>
-    <row r="833" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="833" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>12</v>
       </c>
@@ -44190,12 +43553,8 @@
       <c r="F833">
         <v>13.127099999999999</v>
       </c>
-      <c r="G833">
-        <f t="shared" si="11"/>
-        <v>13.127099999999999</v>
-      </c>
-    </row>
-    <row r="834" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="834" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>12</v>
       </c>
@@ -44211,12 +43570,8 @@
       <c r="F834">
         <v>14.7339</v>
       </c>
-      <c r="G834">
-        <f t="shared" si="11"/>
-        <v>14.7339</v>
-      </c>
-    </row>
-    <row r="835" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="835" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>12</v>
       </c>
@@ -44232,12 +43587,8 @@
       <c r="F835">
         <v>16.005600000000001</v>
       </c>
-      <c r="G835">
-        <f t="shared" si="11"/>
-        <v>16.005600000000001</v>
-      </c>
-    </row>
-    <row r="836" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="836" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>12</v>
       </c>
@@ -44253,12 +43604,8 @@
       <c r="F836">
         <v>18.276600000000002</v>
       </c>
-      <c r="G836">
-        <f t="shared" si="11"/>
-        <v>18.276600000000002</v>
-      </c>
-    </row>
-    <row r="837" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="837" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>12</v>
       </c>
@@ -44274,12 +43621,8 @@
       <c r="F837">
         <v>14.439400000000001</v>
       </c>
-      <c r="G837">
-        <f t="shared" si="11"/>
-        <v>14.439400000000001</v>
-      </c>
-    </row>
-    <row r="838" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="838" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>12</v>
       </c>
@@ -44295,12 +43638,8 @@
       <c r="F838">
         <v>16.700600000000001</v>
       </c>
-      <c r="G838">
-        <f t="shared" si="11"/>
-        <v>16.700600000000001</v>
-      </c>
-    </row>
-    <row r="839" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="839" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>12</v>
       </c>
@@ -44316,12 +43655,8 @@
       <c r="F839">
         <v>16.164400000000004</v>
       </c>
-      <c r="G839">
-        <f t="shared" si="11"/>
-        <v>16.164400000000004</v>
-      </c>
-    </row>
-    <row r="840" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="840" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>12</v>
       </c>
@@ -44337,12 +43672,8 @@
       <c r="F840">
         <v>18.335199999999997</v>
       </c>
-      <c r="G840">
-        <f t="shared" si="11"/>
-        <v>18.335199999999997</v>
-      </c>
-    </row>
-    <row r="841" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="841" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>12</v>
       </c>
@@ -44358,12 +43689,8 @@
       <c r="F841">
         <v>14.702199999999999</v>
       </c>
-      <c r="G841">
-        <f t="shared" si="11"/>
-        <v>14.702199999999999</v>
-      </c>
-    </row>
-    <row r="842" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>12</v>
       </c>
@@ -44379,12 +43706,8 @@
       <c r="F842">
         <v>17.832200000000004</v>
       </c>
-      <c r="G842">
-        <f t="shared" si="11"/>
-        <v>17.832200000000004</v>
-      </c>
-    </row>
-    <row r="843" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="843" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>12</v>
       </c>
@@ -44400,12 +43723,8 @@
       <c r="F843">
         <v>16.367999999999999</v>
       </c>
-      <c r="G843">
-        <f t="shared" si="11"/>
-        <v>16.367999999999999</v>
-      </c>
-    </row>
-    <row r="844" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="844" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>12</v>
       </c>
@@ -44421,12 +43740,8 @@
       <c r="F844">
         <v>18.904</v>
       </c>
-      <c r="G844">
-        <f t="shared" si="11"/>
-        <v>18.904</v>
-      </c>
-    </row>
-    <row r="845" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="845" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>12</v>
       </c>
@@ -44442,12 +43757,8 @@
       <c r="F845">
         <v>15.820200000000002</v>
       </c>
-      <c r="G845">
-        <f t="shared" si="11"/>
-        <v>15.820200000000002</v>
-      </c>
-    </row>
-    <row r="846" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="846" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>12</v>
       </c>
@@ -44463,12 +43774,8 @@
       <c r="F846">
         <v>18.990400000000001</v>
       </c>
-      <c r="G846">
-        <f t="shared" si="11"/>
-        <v>18.990400000000001</v>
-      </c>
-    </row>
-    <row r="847" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="847" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>12</v>
       </c>
@@ -44484,12 +43791,8 @@
       <c r="F847">
         <v>15.709200000000001</v>
       </c>
-      <c r="G847">
-        <f t="shared" si="11"/>
-        <v>15.709200000000001</v>
-      </c>
-    </row>
-    <row r="848" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="848" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>12</v>
       </c>
@@ -44505,12 +43808,8 @@
       <c r="F848">
         <v>17.629200000000004</v>
       </c>
-      <c r="G848">
-        <f t="shared" si="11"/>
-        <v>17.629200000000004</v>
-      </c>
-    </row>
-    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="849" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>12</v>
       </c>
@@ -44526,12 +43825,8 @@
       <c r="F849">
         <v>20.212200000000003</v>
       </c>
-      <c r="G849">
-        <f t="shared" si="11"/>
-        <v>20.212200000000003</v>
-      </c>
-    </row>
-    <row r="850" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="850" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>12</v>
       </c>
@@ -44547,12 +43842,8 @@
       <c r="F850">
         <v>19.511100000000003</v>
       </c>
-      <c r="G850">
-        <f t="shared" si="11"/>
-        <v>19.511100000000003</v>
-      </c>
-    </row>
-    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="851" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>12</v>
       </c>
@@ -44568,15 +43859,8 @@
       <c r="F851">
         <v>17.254300000000001</v>
       </c>
-      <c r="G851">
-        <f t="shared" si="11"/>
-        <v>17.254300000000001</v>
-      </c>
-      <c r="H851" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="852" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>12</v>
       </c>
@@ -44592,15 +43876,8 @@
       <c r="F852">
         <v>18.990400000000001</v>
       </c>
-      <c r="G852">
-        <f t="shared" si="11"/>
-        <v>18.990400000000001</v>
-      </c>
-      <c r="H852" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="853" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>12</v>
       </c>
@@ -44616,15 +43893,8 @@
       <c r="F853">
         <v>20.213000000000001</v>
       </c>
-      <c r="G853">
-        <f t="shared" si="11"/>
-        <v>20.213000000000001</v>
-      </c>
-      <c r="H853" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="854" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>12</v>
       </c>
@@ -44640,15 +43910,8 @@
       <c r="F854">
         <v>20.743199999999998</v>
       </c>
-      <c r="G854">
-        <f t="shared" si="11"/>
-        <v>20.743199999999998</v>
-      </c>
-      <c r="H854" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="855" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="855" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>12</v>
       </c>
@@ -44664,12 +43927,8 @@
       <c r="F855">
         <v>18.177</v>
       </c>
-      <c r="G855">
-        <f t="shared" si="11"/>
-        <v>18.177</v>
-      </c>
-    </row>
-    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="856" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>12</v>
       </c>
@@ -44685,12 +43944,8 @@
       <c r="F856">
         <v>21.1936</v>
       </c>
-      <c r="G856">
-        <f t="shared" si="11"/>
-        <v>21.1936</v>
-      </c>
-    </row>
-    <row r="857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="857" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>12</v>
       </c>
@@ -44706,12 +43961,8 @@
       <c r="F857">
         <v>17.12</v>
       </c>
-      <c r="G857">
-        <f t="shared" si="11"/>
-        <v>17.12</v>
-      </c>
-    </row>
-    <row r="858" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="858" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>12</v>
       </c>
@@ -44727,12 +43978,8 @@
       <c r="F858">
         <v>20.638199999999998</v>
       </c>
-      <c r="G858">
-        <f t="shared" si="11"/>
-        <v>20.638199999999998</v>
-      </c>
-    </row>
-    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="859" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>12</v>
       </c>
@@ -44748,12 +43995,8 @@
       <c r="F859">
         <v>19.418800000000001</v>
       </c>
-      <c r="G859">
-        <f t="shared" si="11"/>
-        <v>19.418800000000001</v>
-      </c>
-    </row>
-    <row r="860" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="860" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>12</v>
       </c>
@@ -44769,12 +44012,8 @@
       <c r="F860">
         <v>21.730399999999996</v>
       </c>
-      <c r="G860">
-        <f t="shared" si="11"/>
-        <v>21.730399999999996</v>
-      </c>
-    </row>
-    <row r="861" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="861" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>12</v>
       </c>
@@ -44790,12 +44029,8 @@
       <c r="F861">
         <v>17.313800000000001</v>
       </c>
-      <c r="G861">
-        <f t="shared" si="11"/>
-        <v>17.313800000000001</v>
-      </c>
-    </row>
-    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="862" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>12</v>
       </c>
@@ -44811,12 +44046,8 @@
       <c r="F862">
         <v>21.0396</v>
       </c>
-      <c r="G862">
-        <f t="shared" si="11"/>
-        <v>21.0396</v>
-      </c>
-    </row>
-    <row r="863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="863" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>13</v>
       </c>
@@ -44832,12 +44063,8 @@
       <c r="F863">
         <v>3.7132999999999998</v>
       </c>
-      <c r="G863">
-        <f t="shared" si="11"/>
-        <v>3.7132999999999998</v>
-      </c>
-    </row>
-    <row r="864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="864" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>13</v>
       </c>
@@ -44851,10 +44078,6 @@
         <v>6</v>
       </c>
       <c r="F864">
-        <v>9.0846</v>
-      </c>
-      <c r="G864">
-        <f t="shared" si="11"/>
         <v>9.0846</v>
       </c>
     </row>
@@ -44874,10 +44097,6 @@
       <c r="F865">
         <v>11.282700000000002</v>
       </c>
-      <c r="G865">
-        <f t="shared" si="11"/>
-        <v>11.282700000000002</v>
-      </c>
     </row>
     <row r="866" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
@@ -44895,10 +44114,6 @@
       <c r="F866">
         <v>14.1492</v>
       </c>
-      <c r="G866">
-        <f t="shared" si="11"/>
-        <v>14.1492</v>
-      </c>
     </row>
     <row r="867" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
@@ -44916,10 +44131,6 @@
       <c r="F867">
         <v>15.68</v>
       </c>
-      <c r="G867">
-        <f t="shared" si="11"/>
-        <v>15.68</v>
-      </c>
     </row>
     <row r="868" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
@@ -44937,10 +44148,6 @@
       <c r="F868">
         <v>16.533000000000001</v>
       </c>
-      <c r="G868">
-        <f t="shared" si="11"/>
-        <v>16.533000000000001</v>
-      </c>
     </row>
     <row r="869" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
@@ -44958,10 +44165,6 @@
       <c r="F869">
         <v>17.297200000000004</v>
       </c>
-      <c r="G869">
-        <f t="shared" si="11"/>
-        <v>17.297200000000004</v>
-      </c>
     </row>
     <row r="870" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
@@ -44980,8 +44183,7 @@
         <v>16.7501</v>
       </c>
       <c r="G870">
-        <f t="shared" si="11"/>
-        <v>16.7501</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="H870" t="s">
         <v>27</v>
@@ -45003,13 +44205,6 @@
       <c r="F871">
         <v>16.0398</v>
       </c>
-      <c r="G871">
-        <f t="shared" si="11"/>
-        <v>16.0398</v>
-      </c>
-      <c r="H871" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="872" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
@@ -45027,10 +44222,6 @@
       <c r="F872">
         <v>18.956099999999999</v>
       </c>
-      <c r="G872">
-        <f t="shared" si="11"/>
-        <v>18.956099999999999</v>
-      </c>
     </row>
     <row r="873" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
@@ -45048,10 +44239,6 @@
       <c r="F873">
         <v>4.1318000000000001</v>
       </c>
-      <c r="G873">
-        <f t="shared" si="11"/>
-        <v>4.1318000000000001</v>
-      </c>
     </row>
     <row r="874" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
@@ -45069,10 +44256,6 @@
       <c r="F874">
         <v>9.7136999999999993</v>
       </c>
-      <c r="G874">
-        <f t="shared" si="11"/>
-        <v>9.7136999999999993</v>
-      </c>
     </row>
     <row r="875" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
@@ -45090,10 +44273,6 @@
       <c r="F875">
         <v>12.059599999999998</v>
       </c>
-      <c r="G875">
-        <f t="shared" ref="G875:G938" si="12">F875</f>
-        <v>12.059599999999998</v>
-      </c>
     </row>
     <row r="876" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
@@ -45111,10 +44290,6 @@
       <c r="F876">
         <v>14.828099999999999</v>
       </c>
-      <c r="G876">
-        <f t="shared" si="12"/>
-        <v>14.828099999999999</v>
-      </c>
     </row>
     <row r="877" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
@@ -45132,10 +44307,6 @@
       <c r="F877">
         <v>17.16</v>
       </c>
-      <c r="G877">
-        <f t="shared" si="12"/>
-        <v>17.16</v>
-      </c>
     </row>
     <row r="878" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
@@ -45153,10 +44324,6 @@
       <c r="F878">
         <v>17.0183</v>
       </c>
-      <c r="G878">
-        <f t="shared" si="12"/>
-        <v>17.0183</v>
-      </c>
     </row>
     <row r="879" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
@@ -45174,10 +44341,6 @@
       <c r="F879">
         <v>17.153000000000002</v>
       </c>
-      <c r="G879">
-        <f t="shared" si="12"/>
-        <v>17.153000000000002</v>
-      </c>
     </row>
     <row r="880" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
@@ -45195,15 +44358,8 @@
       <c r="F880">
         <v>18.1996</v>
       </c>
-      <c r="G880">
-        <f t="shared" si="12"/>
-        <v>18.1996</v>
-      </c>
-      <c r="H880" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="881" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="881" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>13</v>
       </c>
@@ -45219,15 +44375,8 @@
       <c r="F881">
         <v>16.344999999999999</v>
       </c>
-      <c r="G881">
-        <f t="shared" si="12"/>
-        <v>16.344999999999999</v>
-      </c>
-      <c r="H881" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="882" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="882" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>13</v>
       </c>
@@ -45243,12 +44392,8 @@
       <c r="F882">
         <v>20.093399999999999</v>
       </c>
-      <c r="G882">
-        <f t="shared" si="12"/>
-        <v>20.093399999999999</v>
-      </c>
-    </row>
-    <row r="883" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="883" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>13</v>
       </c>
@@ -45264,12 +44409,8 @@
       <c r="F883">
         <v>4.6560000000000006</v>
       </c>
-      <c r="G883">
-        <f t="shared" si="12"/>
-        <v>4.6560000000000006</v>
-      </c>
-    </row>
-    <row r="884" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="884" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>13</v>
       </c>
@@ -45285,12 +44426,8 @@
       <c r="F884">
         <v>4.2772000000000006</v>
       </c>
-      <c r="G884">
-        <f t="shared" si="12"/>
-        <v>4.2772000000000006</v>
-      </c>
-    </row>
-    <row r="885" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="885" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>13</v>
       </c>
@@ -45306,12 +44443,8 @@
       <c r="F885">
         <v>4.8944000000000001</v>
       </c>
-      <c r="G885">
-        <f t="shared" si="12"/>
-        <v>4.8944000000000001</v>
-      </c>
-    </row>
-    <row r="886" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="886" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>13</v>
       </c>
@@ -45327,12 +44460,8 @@
       <c r="F886">
         <v>3.9389999999999996</v>
       </c>
-      <c r="G886">
-        <f t="shared" si="12"/>
-        <v>3.9389999999999996</v>
-      </c>
-    </row>
-    <row r="887" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="887" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>13</v>
       </c>
@@ -45348,12 +44477,8 @@
       <c r="F887">
         <v>10.8528</v>
       </c>
-      <c r="G887">
-        <f t="shared" si="12"/>
-        <v>10.8528</v>
-      </c>
-    </row>
-    <row r="888" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="888" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>13</v>
       </c>
@@ -45369,12 +44494,8 @@
       <c r="F888">
         <v>10.956800000000001</v>
       </c>
-      <c r="G888">
-        <f t="shared" si="12"/>
-        <v>10.956800000000001</v>
-      </c>
-    </row>
-    <row r="889" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="889" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>13</v>
       </c>
@@ -45390,12 +44511,8 @@
       <c r="F889">
         <v>11.326199999999998</v>
       </c>
-      <c r="G889">
-        <f t="shared" si="12"/>
-        <v>11.326199999999998</v>
-      </c>
-    </row>
-    <row r="890" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="890" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>13</v>
       </c>
@@ -45411,12 +44528,8 @@
       <c r="F890">
         <v>9.9293999999999993</v>
       </c>
-      <c r="G890">
-        <f t="shared" si="12"/>
-        <v>9.9293999999999993</v>
-      </c>
-    </row>
-    <row r="891" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="891" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>13</v>
       </c>
@@ -45432,12 +44545,8 @@
       <c r="F891">
         <v>13.165999999999999</v>
       </c>
-      <c r="G891">
-        <f t="shared" si="12"/>
-        <v>13.165999999999999</v>
-      </c>
-    </row>
-    <row r="892" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="892" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>13</v>
       </c>
@@ -45453,12 +44562,8 @@
       <c r="F892">
         <v>10.804500000000001</v>
       </c>
-      <c r="G892">
-        <f t="shared" si="12"/>
-        <v>10.804500000000001</v>
-      </c>
-    </row>
-    <row r="893" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="893" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>13</v>
       </c>
@@ -45474,12 +44579,8 @@
       <c r="F893">
         <v>12.7376</v>
       </c>
-      <c r="G893">
-        <f t="shared" si="12"/>
-        <v>12.7376</v>
-      </c>
-    </row>
-    <row r="894" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="894" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>13</v>
       </c>
@@ -45495,12 +44596,8 @@
       <c r="F894">
         <v>15.515600000000001</v>
       </c>
-      <c r="G894">
-        <f t="shared" si="12"/>
-        <v>15.515600000000001</v>
-      </c>
-    </row>
-    <row r="895" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="895" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>13</v>
       </c>
@@ -45516,12 +44613,8 @@
       <c r="F895">
         <v>12.581800000000001</v>
       </c>
-      <c r="G895">
-        <f t="shared" si="12"/>
-        <v>12.581800000000001</v>
-      </c>
-    </row>
-    <row r="896" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="896" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>13</v>
       </c>
@@ -45537,12 +44630,8 @@
       <c r="F896">
         <v>15.232000000000001</v>
       </c>
-      <c r="G896">
-        <f t="shared" si="12"/>
-        <v>15.232000000000001</v>
-      </c>
-    </row>
-    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="897" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>13</v>
       </c>
@@ -45558,12 +44647,8 @@
       <c r="F897">
         <v>16.212700000000002</v>
       </c>
-      <c r="G897">
-        <f t="shared" si="12"/>
-        <v>16.212700000000002</v>
-      </c>
-    </row>
-    <row r="898" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="898" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>13</v>
       </c>
@@ -45579,12 +44664,8 @@
       <c r="F898">
         <v>17.384</v>
       </c>
-      <c r="G898">
-        <f t="shared" si="12"/>
-        <v>17.384</v>
-      </c>
-    </row>
-    <row r="899" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="899" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>13</v>
       </c>
@@ -45600,12 +44681,8 @@
       <c r="F899">
         <v>17.828400000000002</v>
       </c>
-      <c r="G899">
-        <f t="shared" si="12"/>
-        <v>17.828400000000002</v>
-      </c>
-    </row>
-    <row r="900" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="900" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>13</v>
       </c>
@@ -45621,12 +44698,8 @@
       <c r="F900">
         <v>14.051499999999999</v>
       </c>
-      <c r="G900">
-        <f t="shared" si="12"/>
-        <v>14.051499999999999</v>
-      </c>
-    </row>
-    <row r="901" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="901" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>13</v>
       </c>
@@ -45642,12 +44715,8 @@
       <c r="F901">
         <v>16.912500000000001</v>
       </c>
-      <c r="G901">
-        <f t="shared" si="12"/>
-        <v>16.912500000000001</v>
-      </c>
-    </row>
-    <row r="902" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="902" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>13</v>
       </c>
@@ -45663,12 +44732,8 @@
       <c r="F902">
         <v>17.995200000000001</v>
       </c>
-      <c r="G902">
-        <f t="shared" si="12"/>
-        <v>17.995200000000001</v>
-      </c>
-    </row>
-    <row r="903" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="903" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>13</v>
       </c>
@@ -45684,12 +44749,8 @@
       <c r="F903">
         <v>18.420999999999999</v>
       </c>
-      <c r="G903">
-        <f t="shared" si="12"/>
-        <v>18.420999999999999</v>
-      </c>
-    </row>
-    <row r="904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="904" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>13</v>
       </c>
@@ -45705,12 +44766,8 @@
       <c r="F904">
         <v>15.370899999999999</v>
       </c>
-      <c r="G904">
-        <f t="shared" si="12"/>
-        <v>15.370899999999999</v>
-      </c>
-    </row>
-    <row r="905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="905" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>13</v>
       </c>
@@ -45726,12 +44783,8 @@
       <c r="F905">
         <v>17.330400000000001</v>
       </c>
-      <c r="G905">
-        <f t="shared" si="12"/>
-        <v>17.330400000000001</v>
-      </c>
-    </row>
-    <row r="906" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="906" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>13</v>
       </c>
@@ -45747,12 +44800,8 @@
       <c r="F906">
         <v>18.035999999999998</v>
       </c>
-      <c r="G906">
-        <f t="shared" si="12"/>
-        <v>18.035999999999998</v>
-      </c>
-    </row>
-    <row r="907" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="907" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>13</v>
       </c>
@@ -45768,12 +44817,8 @@
       <c r="F907">
         <v>19.583600000000001</v>
       </c>
-      <c r="G907">
-        <f t="shared" si="12"/>
-        <v>19.583600000000001</v>
-      </c>
-    </row>
-    <row r="908" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="908" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>13</v>
       </c>
@@ -45789,12 +44834,8 @@
       <c r="F908">
         <v>15.481599999999998</v>
       </c>
-      <c r="G908">
-        <f t="shared" si="12"/>
-        <v>15.481599999999998</v>
-      </c>
-    </row>
-    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="909" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>13</v>
       </c>
@@ -45810,15 +44851,8 @@
       <c r="F909">
         <v>16.8264</v>
       </c>
-      <c r="G909">
-        <f t="shared" si="12"/>
-        <v>16.8264</v>
-      </c>
-      <c r="H909" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="910" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="910" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>13</v>
       </c>
@@ -45834,15 +44868,8 @@
       <c r="F910">
         <v>18.564</v>
       </c>
-      <c r="G910">
-        <f t="shared" si="12"/>
-        <v>18.564</v>
-      </c>
-      <c r="H910" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="911" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>13</v>
       </c>
@@ -45858,15 +44885,8 @@
       <c r="F911">
         <v>18.948599999999999</v>
       </c>
-      <c r="G911">
-        <f t="shared" si="12"/>
-        <v>18.948599999999999</v>
-      </c>
-      <c r="H911" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="912" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="912" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>13</v>
       </c>
@@ -45882,15 +44902,8 @@
       <c r="F912">
         <v>15.484999999999999</v>
       </c>
-      <c r="G912">
-        <f t="shared" si="12"/>
-        <v>15.484999999999999</v>
-      </c>
-      <c r="H912" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="913" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>13</v>
       </c>
@@ -45906,15 +44919,8 @@
       <c r="F913">
         <v>15.664599999999998</v>
       </c>
-      <c r="G913">
-        <f t="shared" si="12"/>
-        <v>15.664599999999998</v>
-      </c>
-      <c r="H913" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="914" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="914" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>13</v>
       </c>
@@ -45930,15 +44936,8 @@
       <c r="F914">
         <v>16.6465</v>
       </c>
-      <c r="G914">
-        <f t="shared" si="12"/>
-        <v>16.6465</v>
-      </c>
-      <c r="H914" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="915" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="915" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>13</v>
       </c>
@@ -45954,15 +44953,8 @@
       <c r="F915">
         <v>18.004799999999999</v>
       </c>
-      <c r="G915">
-        <f t="shared" si="12"/>
-        <v>18.004799999999999</v>
-      </c>
-      <c r="H915" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="916" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>13</v>
       </c>
@@ -45978,15 +44970,8 @@
       <c r="F916">
         <v>14.176400000000003</v>
       </c>
-      <c r="G916">
-        <f t="shared" si="12"/>
-        <v>14.176400000000003</v>
-      </c>
-      <c r="H916" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="917" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="917" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>13</v>
       </c>
@@ -46002,12 +44987,8 @@
       <c r="F917">
         <v>21.337800000000001</v>
       </c>
-      <c r="G917">
-        <f t="shared" si="12"/>
-        <v>21.337800000000001</v>
-      </c>
-    </row>
-    <row r="918" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="918" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>13</v>
       </c>
@@ -46023,12 +45004,8 @@
       <c r="F918">
         <v>17.0625</v>
       </c>
-      <c r="G918">
-        <f t="shared" si="12"/>
-        <v>17.0625</v>
-      </c>
-    </row>
-    <row r="919" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="919" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>13</v>
       </c>
@@ -46044,12 +45021,8 @@
       <c r="F919">
         <v>18.391999999999999</v>
       </c>
-      <c r="G919">
-        <f t="shared" si="12"/>
-        <v>18.391999999999999</v>
-      </c>
-    </row>
-    <row r="920" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="920" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>13</v>
       </c>
@@ -46065,12 +45038,8 @@
       <c r="F920">
         <v>20.178000000000001</v>
       </c>
-      <c r="G920">
-        <f t="shared" si="12"/>
-        <v>20.178000000000001</v>
-      </c>
-    </row>
-    <row r="921" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="921" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>14</v>
       </c>
@@ -46086,12 +45055,8 @@
       <c r="F921">
         <v>4.7547000000000006</v>
       </c>
-      <c r="G921">
-        <f t="shared" si="12"/>
-        <v>4.7547000000000006</v>
-      </c>
-    </row>
-    <row r="922" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="922" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>14</v>
       </c>
@@ -46107,12 +45072,8 @@
       <c r="F922">
         <v>9.8704000000000001</v>
       </c>
-      <c r="G922">
-        <f t="shared" si="12"/>
-        <v>9.8704000000000001</v>
-      </c>
-    </row>
-    <row r="923" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="923" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>14</v>
       </c>
@@ -46128,12 +45089,8 @@
       <c r="F923">
         <v>10.906000000000001</v>
       </c>
-      <c r="G923">
-        <f t="shared" si="12"/>
-        <v>10.906000000000001</v>
-      </c>
-    </row>
-    <row r="924" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="924" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>14</v>
       </c>
@@ -46149,12 +45106,8 @@
       <c r="F924">
         <v>13.64</v>
       </c>
-      <c r="G924">
-        <f t="shared" si="12"/>
-        <v>13.64</v>
-      </c>
-    </row>
-    <row r="925" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="925" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>14</v>
       </c>
@@ -46170,12 +45123,8 @@
       <c r="F925">
         <v>18.305</v>
       </c>
-      <c r="G925">
-        <f t="shared" si="12"/>
-        <v>18.305</v>
-      </c>
-    </row>
-    <row r="926" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="926" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>14</v>
       </c>
@@ -46191,12 +45140,8 @@
       <c r="F926">
         <v>18.266399999999997</v>
       </c>
-      <c r="G926">
-        <f t="shared" si="12"/>
-        <v>18.266399999999997</v>
-      </c>
-    </row>
-    <row r="927" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="927" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>14</v>
       </c>
@@ -46212,12 +45157,8 @@
       <c r="F927">
         <v>17.912400000000002</v>
       </c>
-      <c r="G927">
-        <f t="shared" si="12"/>
-        <v>17.912400000000002</v>
-      </c>
-    </row>
-    <row r="928" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="928" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>14</v>
       </c>
@@ -46233,12 +45174,8 @@
       <c r="F928">
         <v>5.3330999999999991</v>
       </c>
-      <c r="G928">
-        <f t="shared" si="12"/>
-        <v>5.3330999999999991</v>
-      </c>
-    </row>
-    <row r="929" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="929" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>14</v>
       </c>
@@ -46254,12 +45191,8 @@
       <c r="F929">
         <v>11.4168</v>
       </c>
-      <c r="G929">
-        <f t="shared" si="12"/>
-        <v>11.4168</v>
-      </c>
-    </row>
-    <row r="930" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="930" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>14</v>
       </c>
@@ -46275,12 +45208,8 @@
       <c r="F930">
         <v>12.3223</v>
       </c>
-      <c r="G930">
-        <f t="shared" si="12"/>
-        <v>12.3223</v>
-      </c>
-    </row>
-    <row r="931" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="931" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>14</v>
       </c>
@@ -46296,12 +45225,8 @@
       <c r="F931">
         <v>15.345000000000001</v>
       </c>
-      <c r="G931">
-        <f t="shared" si="12"/>
-        <v>15.345000000000001</v>
-      </c>
-    </row>
-    <row r="932" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="932" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>14</v>
       </c>
@@ -46318,14 +45243,13 @@
         <v>20.304000000000002</v>
       </c>
       <c r="G932">
-        <f t="shared" si="12"/>
-        <v>20.304000000000002</v>
+        <v>20.09</v>
       </c>
       <c r="H932" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="933" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>14</v>
       </c>
@@ -46341,12 +45265,8 @@
       <c r="F933">
         <v>20.374199999999998</v>
       </c>
-      <c r="G933">
-        <f t="shared" si="12"/>
-        <v>20.374199999999998</v>
-      </c>
-    </row>
-    <row r="934" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="934" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>14</v>
       </c>
@@ -46362,12 +45282,8 @@
       <c r="F934">
         <v>21.040500000000002</v>
       </c>
-      <c r="G934">
-        <f t="shared" si="12"/>
-        <v>21.040500000000002</v>
-      </c>
-    </row>
-    <row r="935" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="935" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>14</v>
       </c>
@@ -46383,12 +45299,8 @@
       <c r="F935">
         <v>4.8761999999999999</v>
       </c>
-      <c r="G935">
-        <f t="shared" si="12"/>
-        <v>4.8761999999999999</v>
-      </c>
-    </row>
-    <row r="936" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="936" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>14</v>
       </c>
@@ -46404,12 +45316,8 @@
       <c r="F936">
         <v>6.0888</v>
       </c>
-      <c r="G936">
-        <f t="shared" si="12"/>
-        <v>6.0888</v>
-      </c>
-    </row>
-    <row r="937" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="937" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>14</v>
       </c>
@@ -46425,12 +45333,8 @@
       <c r="F937">
         <v>6.6393999999999993</v>
       </c>
-      <c r="G937">
-        <f t="shared" si="12"/>
-        <v>6.6393999999999993</v>
-      </c>
-    </row>
-    <row r="938" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="938" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>14</v>
       </c>
@@ -46446,12 +45350,8 @@
       <c r="F938">
         <v>10.094700000000001</v>
       </c>
-      <c r="G938">
-        <f t="shared" si="12"/>
-        <v>10.094700000000001</v>
-      </c>
-    </row>
-    <row r="939" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="939" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>14</v>
       </c>
@@ -46467,12 +45367,8 @@
       <c r="F939">
         <v>11.238399999999999</v>
       </c>
-      <c r="G939">
-        <f t="shared" ref="G939:G1002" si="13">F939</f>
-        <v>11.238399999999999</v>
-      </c>
-    </row>
-    <row r="940" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="940" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>14</v>
       </c>
@@ -46488,12 +45384,8 @@
       <c r="F940">
         <v>11.596500000000001</v>
       </c>
-      <c r="G940">
-        <f t="shared" si="13"/>
-        <v>11.596500000000001</v>
-      </c>
-    </row>
-    <row r="941" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="941" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>14</v>
       </c>
@@ -46509,12 +45401,8 @@
       <c r="F941">
         <v>11.636900000000001</v>
       </c>
-      <c r="G941">
-        <f t="shared" si="13"/>
-        <v>11.636900000000001</v>
-      </c>
-    </row>
-    <row r="942" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="942" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>14</v>
       </c>
@@ -46530,12 +45418,8 @@
       <c r="F942">
         <v>14.870200000000001</v>
       </c>
-      <c r="G942">
-        <f t="shared" si="13"/>
-        <v>14.870200000000001</v>
-      </c>
-    </row>
-    <row r="943" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="943" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>14</v>
       </c>
@@ -46551,12 +45435,8 @@
       <c r="F943">
         <v>13.32</v>
       </c>
-      <c r="G943">
-        <f t="shared" si="13"/>
-        <v>13.32</v>
-      </c>
-    </row>
-    <row r="944" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="944" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>14</v>
       </c>
@@ -46572,12 +45452,8 @@
       <c r="F944">
         <v>13.488</v>
       </c>
-      <c r="G944">
-        <f t="shared" si="13"/>
-        <v>13.488</v>
-      </c>
-    </row>
-    <row r="945" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="945" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>14</v>
       </c>
@@ -46593,12 +45469,8 @@
       <c r="F945">
         <v>17.408000000000001</v>
       </c>
-      <c r="G945">
-        <f t="shared" si="13"/>
-        <v>17.408000000000001</v>
-      </c>
-    </row>
-    <row r="946" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>14</v>
       </c>
@@ -46614,12 +45486,8 @@
       <c r="F946">
         <v>15.384600000000001</v>
       </c>
-      <c r="G946">
-        <f t="shared" si="13"/>
-        <v>15.384600000000001</v>
-      </c>
-    </row>
-    <row r="947" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>14</v>
       </c>
@@ -46635,15 +45503,8 @@
       <c r="F947">
         <v>17.500999999999998</v>
       </c>
-      <c r="G947">
-        <f t="shared" si="13"/>
-        <v>17.500999999999998</v>
-      </c>
-      <c r="H947" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="948" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>14</v>
       </c>
@@ -46659,15 +45520,8 @@
       <c r="F948">
         <v>22.477499999999999</v>
       </c>
-      <c r="G948">
-        <f t="shared" si="13"/>
-        <v>22.477499999999999</v>
-      </c>
-      <c r="H948" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="949" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>14</v>
       </c>
@@ -46683,12 +45537,8 @@
       <c r="F949">
         <v>19.583600000000001</v>
       </c>
-      <c r="G949">
-        <f t="shared" si="13"/>
-        <v>19.583600000000001</v>
-      </c>
-    </row>
-    <row r="950" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>14</v>
       </c>
@@ -46704,12 +45554,8 @@
       <c r="F950">
         <v>23.190299999999997</v>
       </c>
-      <c r="G950">
-        <f t="shared" si="13"/>
-        <v>23.190299999999997</v>
-      </c>
-    </row>
-    <row r="951" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="951" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>14</v>
       </c>
@@ -46725,12 +45571,8 @@
       <c r="F951">
         <v>18.668399999999998</v>
       </c>
-      <c r="G951">
-        <f t="shared" si="13"/>
-        <v>18.668399999999998</v>
-      </c>
-    </row>
-    <row r="952" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>14</v>
       </c>
@@ -46746,12 +45588,8 @@
       <c r="F952">
         <v>21.14</v>
       </c>
-      <c r="G952">
-        <f t="shared" si="13"/>
-        <v>21.14</v>
-      </c>
-    </row>
-    <row r="953" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="953" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>14</v>
       </c>
@@ -46767,12 +45605,8 @@
       <c r="F953">
         <v>17.422999999999998</v>
       </c>
-      <c r="G953">
-        <f t="shared" si="13"/>
-        <v>17.422999999999998</v>
-      </c>
-    </row>
-    <row r="954" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>14</v>
       </c>
@@ -46786,10 +45620,6 @@
         <v>6</v>
       </c>
       <c r="F954">
-        <v>21.057399999999998</v>
-      </c>
-      <c r="G954">
-        <f t="shared" si="13"/>
         <v>21.057399999999998</v>
       </c>
     </row>
@@ -46809,10 +45639,6 @@
       <c r="F955">
         <v>6.0801999999999996</v>
       </c>
-      <c r="G955">
-        <f t="shared" si="13"/>
-        <v>6.0801999999999996</v>
-      </c>
     </row>
     <row r="956" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
@@ -46830,10 +45656,6 @@
       <c r="F956">
         <v>12.821400000000001</v>
       </c>
-      <c r="G956">
-        <f t="shared" si="13"/>
-        <v>12.821400000000001</v>
-      </c>
     </row>
     <row r="957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
@@ -46851,10 +45673,6 @@
       <c r="F957">
         <v>14.503500000000001</v>
       </c>
-      <c r="G957">
-        <f t="shared" si="13"/>
-        <v>14.503500000000001</v>
-      </c>
     </row>
     <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
@@ -46872,10 +45690,6 @@
       <c r="F958">
         <v>15.633099999999999</v>
       </c>
-      <c r="G958">
-        <f t="shared" si="13"/>
-        <v>15.633099999999999</v>
-      </c>
     </row>
     <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
@@ -46894,7 +45708,7 @@
         <v>18.143800000000002</v>
       </c>
       <c r="G959">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="G959" si="9">F959</f>
         <v>18.143800000000002</v>
       </c>
       <c r="H959" t="s">
@@ -46917,10 +45731,6 @@
       <c r="F960">
         <v>19.821999999999999</v>
       </c>
-      <c r="G960">
-        <f t="shared" si="13"/>
-        <v>19.821999999999999</v>
-      </c>
     </row>
     <row r="961" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
@@ -46938,10 +45748,6 @@
       <c r="F961">
         <v>20.206400000000002</v>
       </c>
-      <c r="G961">
-        <f t="shared" si="13"/>
-        <v>20.206400000000002</v>
-      </c>
     </row>
     <row r="962" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
@@ -46959,10 +45765,6 @@
       <c r="F962">
         <v>6.2172349019108983</v>
       </c>
-      <c r="G962">
-        <f t="shared" si="13"/>
-        <v>6.2172349019108983</v>
-      </c>
     </row>
     <row r="963" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
@@ -46980,10 +45782,6 @@
       <c r="F963">
         <v>8.8543295541579354</v>
       </c>
-      <c r="G963">
-        <f t="shared" si="13"/>
-        <v>8.8543295541579354</v>
-      </c>
     </row>
     <row r="964" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
@@ -47001,10 +45799,6 @@
       <c r="F964">
         <v>11.907888730774177</v>
       </c>
-      <c r="G964">
-        <f t="shared" si="13"/>
-        <v>11.907888730774177</v>
-      </c>
     </row>
     <row r="965" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
@@ -47022,10 +45816,6 @@
       <c r="F965">
         <v>13.959946145677179</v>
       </c>
-      <c r="G965">
-        <f t="shared" si="13"/>
-        <v>13.959946145677179</v>
-      </c>
     </row>
     <row r="966" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
@@ -47043,10 +45833,6 @@
       <c r="F966">
         <v>15.94766682715896</v>
       </c>
-      <c r="G966">
-        <f t="shared" si="13"/>
-        <v>15.94766682715896</v>
-      </c>
     </row>
     <row r="967" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
@@ -47064,10 +45850,6 @@
       <c r="F967">
         <v>16.847079172988892</v>
       </c>
-      <c r="G967">
-        <f t="shared" si="13"/>
-        <v>16.847079172988892</v>
-      </c>
     </row>
     <row r="968" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
@@ -47086,8 +45868,7 @@
         <v>17.673615128971232</v>
       </c>
       <c r="G968">
-        <f t="shared" si="13"/>
-        <v>17.673615128971232</v>
+        <v>18.37</v>
       </c>
       <c r="H968" t="s">
         <v>27</v>
@@ -47109,13 +45890,6 @@
       <c r="F969">
         <v>17.494817081223879</v>
       </c>
-      <c r="G969">
-        <f t="shared" si="13"/>
-        <v>17.494817081223879</v>
-      </c>
-      <c r="H969" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="970" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
@@ -47133,10 +45907,6 @@
       <c r="F970">
         <v>19.714894814967227</v>
       </c>
-      <c r="G970">
-        <f t="shared" si="13"/>
-        <v>19.714894814967227</v>
-      </c>
     </row>
     <row r="971" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
@@ -47154,10 +45924,6 @@
       <c r="F971">
         <v>19.764897653038307</v>
       </c>
-      <c r="G971">
-        <f t="shared" si="13"/>
-        <v>19.764897653038307</v>
-      </c>
     </row>
     <row r="972" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
@@ -47175,10 +45941,6 @@
       <c r="F972">
         <v>20.837102416927618</v>
       </c>
-      <c r="G972">
-        <f t="shared" si="13"/>
-        <v>20.837102416927618</v>
-      </c>
     </row>
     <row r="973" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
@@ -47196,10 +45958,6 @@
       <c r="F973">
         <v>6.9319183664277553</v>
       </c>
-      <c r="G973">
-        <f t="shared" si="13"/>
-        <v>6.9319183664277553</v>
-      </c>
     </row>
     <row r="974" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
@@ -47217,10 +45975,6 @@
       <c r="F974">
         <v>13.780894783470638</v>
       </c>
-      <c r="G974">
-        <f t="shared" si="13"/>
-        <v>13.780894783470638</v>
-      </c>
     </row>
     <row r="975" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
@@ -47238,10 +45992,6 @@
       <c r="F975">
         <v>16.191051188890199</v>
       </c>
-      <c r="G975">
-        <f t="shared" si="13"/>
-        <v>16.191051188890199</v>
-      </c>
     </row>
     <row r="976" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
@@ -47259,12 +46009,8 @@
       <c r="F976">
         <v>17.405492056011052</v>
       </c>
-      <c r="G976">
-        <f t="shared" si="13"/>
-        <v>17.405492056011052</v>
-      </c>
-    </row>
-    <row r="977" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="977" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>15</v>
       </c>
@@ -47280,12 +46026,8 @@
       <c r="F977">
         <v>18.476749288753865</v>
       </c>
-      <c r="G977">
-        <f t="shared" si="13"/>
-        <v>18.476749288753865</v>
-      </c>
-    </row>
-    <row r="978" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="978" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>15</v>
       </c>
@@ -47301,15 +46043,8 @@
       <c r="F978">
         <v>18.760523213785294</v>
       </c>
-      <c r="G978">
-        <f t="shared" si="13"/>
-        <v>18.760523213785294</v>
-      </c>
-      <c r="H978" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="979" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="979" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>15</v>
       </c>
@@ -47325,15 +46060,8 @@
       <c r="F979">
         <v>19.48157763281246</v>
       </c>
-      <c r="G979">
-        <f t="shared" si="13"/>
-        <v>19.48157763281246</v>
-      </c>
-      <c r="H979" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="980" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="980" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>15</v>
       </c>
@@ -47349,12 +46077,8 @@
       <c r="F980">
         <v>17.781141937861513</v>
       </c>
-      <c r="G980">
-        <f t="shared" si="13"/>
-        <v>17.781141937861513</v>
-      </c>
-    </row>
-    <row r="981" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="981" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>15</v>
       </c>
@@ -47370,12 +46094,8 @@
       <c r="F981">
         <v>20.557990280205107</v>
       </c>
-      <c r="G981">
-        <f t="shared" si="13"/>
-        <v>20.557990280205107</v>
-      </c>
-    </row>
-    <row r="982" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="982" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>15</v>
       </c>
@@ -47391,12 +46111,8 @@
       <c r="F982">
         <v>19.39898301327348</v>
       </c>
-      <c r="G982">
-        <f t="shared" si="13"/>
-        <v>19.39898301327348</v>
-      </c>
-    </row>
-    <row r="983" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="983" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>15</v>
       </c>
@@ -47412,12 +46128,8 @@
       <c r="F983">
         <v>6.9315123712321158</v>
       </c>
-      <c r="G983">
-        <f t="shared" si="13"/>
-        <v>6.9315123712321158</v>
-      </c>
-    </row>
-    <row r="984" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="984" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>15</v>
       </c>
@@ -47433,12 +46145,8 @@
       <c r="F984">
         <v>5.4313511084294808</v>
       </c>
-      <c r="G984">
-        <f t="shared" si="13"/>
-        <v>5.4313511084294808</v>
-      </c>
-    </row>
-    <row r="985" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="985" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>15</v>
       </c>
@@ -47454,12 +46162,8 @@
       <c r="F985">
         <v>5.7144543386675126</v>
       </c>
-      <c r="G985">
-        <f t="shared" si="13"/>
-        <v>5.7144543386675126</v>
-      </c>
-    </row>
-    <row r="986" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="986" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>15</v>
       </c>
@@ -47475,12 +46179,8 @@
       <c r="F986">
         <v>8.8291548744930903</v>
       </c>
-      <c r="G986">
-        <f t="shared" si="13"/>
-        <v>8.8291548744930903</v>
-      </c>
-    </row>
-    <row r="987" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="987" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>15</v>
       </c>
@@ -47496,12 +46196,8 @@
       <c r="F987">
         <v>8.3138487145662179</v>
       </c>
-      <c r="G987">
-        <f t="shared" si="13"/>
-        <v>8.3138487145662179</v>
-      </c>
-    </row>
-    <row r="988" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="988" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>15</v>
       </c>
@@ -47517,12 +46213,8 @@
       <c r="F988">
         <v>8.0472565935445601</v>
       </c>
-      <c r="G988">
-        <f t="shared" si="13"/>
-        <v>8.0472565935445601</v>
-      </c>
-    </row>
-    <row r="989" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="989" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>15</v>
       </c>
@@ -47538,12 +46230,8 @@
       <c r="F989">
         <v>11.28362013570101</v>
       </c>
-      <c r="G989">
-        <f t="shared" si="13"/>
-        <v>11.28362013570101</v>
-      </c>
-    </row>
-    <row r="990" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="990" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>15</v>
       </c>
@@ -47559,12 +46247,8 @@
       <c r="F990">
         <v>12.996873220121543</v>
       </c>
-      <c r="G990">
-        <f t="shared" si="13"/>
-        <v>12.996873220121543</v>
-      </c>
-    </row>
-    <row r="991" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="991" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>15</v>
       </c>
@@ -47580,12 +46264,8 @@
       <c r="F991">
         <v>11.020121811353031</v>
       </c>
-      <c r="G991">
-        <f t="shared" si="13"/>
-        <v>11.020121811353031</v>
-      </c>
-    </row>
-    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="992" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>15</v>
       </c>
@@ -47601,12 +46281,8 @@
       <c r="F992">
         <v>13.065476193540855</v>
       </c>
-      <c r="G992">
-        <f t="shared" si="13"/>
-        <v>13.065476193540855</v>
-      </c>
-    </row>
-    <row r="993" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="993" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>15</v>
       </c>
@@ -47622,12 +46298,8 @@
       <c r="F993">
         <v>15.870028059077221</v>
       </c>
-      <c r="G993">
-        <f t="shared" si="13"/>
-        <v>15.870028059077221</v>
-      </c>
-    </row>
-    <row r="994" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="994" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>15</v>
       </c>
@@ -47643,12 +46315,8 @@
       <c r="F994">
         <v>14.223498689674621</v>
       </c>
-      <c r="G994">
-        <f t="shared" si="13"/>
-        <v>14.223498689674621</v>
-      </c>
-    </row>
-    <row r="995" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="995" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>15</v>
       </c>
@@ -47664,12 +46332,8 @@
       <c r="F995">
         <v>17.699191578753037</v>
       </c>
-      <c r="G995">
-        <f t="shared" si="13"/>
-        <v>17.699191578753037</v>
-      </c>
-    </row>
-    <row r="996" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="996" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>15</v>
       </c>
@@ -47685,12 +46349,8 @@
       <c r="F996">
         <v>15.108312942068499</v>
       </c>
-      <c r="G996">
-        <f t="shared" si="13"/>
-        <v>15.108312942068499</v>
-      </c>
-    </row>
-    <row r="997" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="997" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>15</v>
       </c>
@@ -47706,12 +46366,8 @@
       <c r="F997">
         <v>15.438316897742517</v>
       </c>
-      <c r="G997">
-        <f t="shared" si="13"/>
-        <v>15.438316897742517</v>
-      </c>
-    </row>
-    <row r="998" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="998" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>15</v>
       </c>
@@ -47727,12 +46383,8 @@
       <c r="F998">
         <v>18.205173511905102</v>
       </c>
-      <c r="G998">
-        <f t="shared" si="13"/>
-        <v>18.205173511905102</v>
-      </c>
-    </row>
-    <row r="999" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="999" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>15</v>
       </c>
@@ -47748,12 +46400,8 @@
       <c r="F999">
         <v>17.222989608255027</v>
       </c>
-      <c r="G999">
-        <f t="shared" si="13"/>
-        <v>17.222989608255027</v>
-      </c>
-    </row>
-    <row r="1000" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1000" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>15</v>
       </c>
@@ -47769,12 +46417,8 @@
       <c r="F1000">
         <v>16.211048258733999</v>
       </c>
-      <c r="G1000">
-        <f t="shared" si="13"/>
-        <v>16.211048258733999</v>
-      </c>
-    </row>
-    <row r="1001" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1001" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>15</v>
       </c>
@@ -47790,12 +46434,8 @@
       <c r="F1001">
         <v>16.707643098532472</v>
       </c>
-      <c r="G1001">
-        <f t="shared" si="13"/>
-        <v>16.707643098532472</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1002" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>15</v>
       </c>
@@ -47811,12 +46451,8 @@
       <c r="F1002">
         <v>19.537145853036414</v>
       </c>
-      <c r="G1002">
-        <f t="shared" si="13"/>
-        <v>19.537145853036414</v>
-      </c>
-    </row>
-    <row r="1003" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1003" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>15</v>
       </c>
@@ -47832,15 +46468,8 @@
       <c r="F1003">
         <v>17.291765167818632</v>
       </c>
-      <c r="G1003">
-        <f t="shared" ref="G1003:G1066" si="14">F1003</f>
-        <v>17.291765167818632</v>
-      </c>
-      <c r="H1003" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1004" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1004" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>15</v>
       </c>
@@ -47856,15 +46485,8 @@
       <c r="F1004">
         <v>19.369444542004405</v>
       </c>
-      <c r="G1004">
-        <f t="shared" si="14"/>
-        <v>19.369444542004405</v>
-      </c>
-      <c r="H1004" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1005" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1005" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>15</v>
       </c>
@@ -47880,12 +46502,8 @@
       <c r="F1005">
         <v>17.499025054421459</v>
       </c>
-      <c r="G1005">
-        <f t="shared" si="14"/>
-        <v>17.499025054421459</v>
-      </c>
-    </row>
-    <row r="1006" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1006" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>15</v>
       </c>
@@ -47901,12 +46519,8 @@
       <c r="F1006">
         <v>17.650603109848099</v>
       </c>
-      <c r="G1006">
-        <f t="shared" si="14"/>
-        <v>17.650603109848099</v>
-      </c>
-    </row>
-    <row r="1007" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1007" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>15</v>
       </c>
@@ -47922,12 +46536,8 @@
       <c r="F1007">
         <v>20.26370901829625</v>
       </c>
-      <c r="G1007">
-        <f t="shared" si="14"/>
-        <v>20.26370901829625</v>
-      </c>
-    </row>
-    <row r="1008" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1008" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>15</v>
       </c>
@@ -47941,10 +46551,6 @@
         <v>6</v>
       </c>
       <c r="F1008">
-        <v>17.354245507768088</v>
-      </c>
-      <c r="G1008">
-        <f t="shared" si="14"/>
         <v>17.354245507768088</v>
       </c>
     </row>
@@ -47964,10 +46570,6 @@
       <c r="F1009">
         <v>18.87174342283873</v>
       </c>
-      <c r="G1009">
-        <f t="shared" si="14"/>
-        <v>18.87174342283873</v>
-      </c>
     </row>
     <row r="1010" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
@@ -47985,10 +46587,6 @@
       <c r="F1010">
         <v>22.047358999831484</v>
       </c>
-      <c r="G1010">
-        <f t="shared" si="14"/>
-        <v>22.047358999831484</v>
-      </c>
     </row>
     <row r="1011" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
@@ -48006,10 +46604,6 @@
       <c r="F1011">
         <v>17.740085747275025</v>
       </c>
-      <c r="G1011">
-        <f t="shared" si="14"/>
-        <v>17.740085747275025</v>
-      </c>
     </row>
     <row r="1012" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
@@ -48027,10 +46621,6 @@
       <c r="F1012">
         <v>20.371931094087373</v>
       </c>
-      <c r="G1012">
-        <f t="shared" si="14"/>
-        <v>20.371931094087373</v>
-      </c>
     </row>
     <row r="1013" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
@@ -48048,10 +46638,6 @@
       <c r="F1013">
         <v>21.524553643903822</v>
       </c>
-      <c r="G1013">
-        <f t="shared" si="14"/>
-        <v>21.524553643903822</v>
-      </c>
     </row>
     <row r="1014" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
@@ -48069,10 +46655,6 @@
       <c r="F1014">
         <v>18.5648614072737</v>
       </c>
-      <c r="G1014">
-        <f t="shared" si="14"/>
-        <v>18.5648614072737</v>
-      </c>
     </row>
     <row r="1015" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
@@ -48090,10 +46672,6 @@
       <c r="F1015">
         <v>19.349351733779123</v>
       </c>
-      <c r="G1015">
-        <f t="shared" si="14"/>
-        <v>19.349351733779123</v>
-      </c>
     </row>
     <row r="1016" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
@@ -48111,10 +46689,6 @@
       <c r="F1016">
         <v>6.7398628846985886</v>
       </c>
-      <c r="G1016">
-        <f t="shared" si="14"/>
-        <v>6.7398628846985886</v>
-      </c>
     </row>
     <row r="1017" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
@@ -48132,10 +46706,6 @@
       <c r="F1017">
         <v>10.311391387844139</v>
       </c>
-      <c r="G1017">
-        <f t="shared" si="14"/>
-        <v>10.311391387844139</v>
-      </c>
     </row>
     <row r="1018" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
@@ -48153,10 +46723,6 @@
       <c r="F1018">
         <v>12.270177875075783</v>
       </c>
-      <c r="G1018">
-        <f t="shared" si="14"/>
-        <v>12.270177875075783</v>
-      </c>
     </row>
     <row r="1019" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
@@ -48174,10 +46740,6 @@
       <c r="F1019">
         <v>13.619012088702434</v>
       </c>
-      <c r="G1019">
-        <f t="shared" si="14"/>
-        <v>13.619012088702434</v>
-      </c>
     </row>
     <row r="1020" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
@@ -48195,10 +46757,6 @@
       <c r="F1020">
         <v>15.027232099000203</v>
       </c>
-      <c r="G1020">
-        <f t="shared" si="14"/>
-        <v>15.027232099000203</v>
-      </c>
     </row>
     <row r="1021" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
@@ -48216,10 +46774,6 @@
       <c r="F1021">
         <v>16.272488100957471</v>
       </c>
-      <c r="G1021">
-        <f t="shared" si="14"/>
-        <v>16.272488100957471</v>
-      </c>
     </row>
     <row r="1022" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
@@ -48237,10 +46791,6 @@
       <c r="F1022">
         <v>17.020663419496199</v>
       </c>
-      <c r="G1022">
-        <f t="shared" si="14"/>
-        <v>17.020663419496199</v>
-      </c>
     </row>
     <row r="1023" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
@@ -48258,10 +46808,6 @@
       <c r="F1023">
         <v>18.753000702450848</v>
       </c>
-      <c r="G1023">
-        <f t="shared" si="14"/>
-        <v>18.753000702450848</v>
-      </c>
     </row>
     <row r="1024" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
@@ -48280,7 +46826,7 @@
         <v>18.060959017147049</v>
       </c>
       <c r="G1024">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G1024:G1057" si="10">F1024</f>
         <v>18.060959017147049</v>
       </c>
       <c r="H1024" t="s">
@@ -48303,10 +46849,6 @@
       <c r="F1025">
         <v>18.922415892599915</v>
       </c>
-      <c r="G1025">
-        <f t="shared" si="14"/>
-        <v>18.922415892599915</v>
-      </c>
     </row>
     <row r="1026" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
@@ -48324,10 +46866,6 @@
       <c r="F1026">
         <v>20.1101714011625</v>
       </c>
-      <c r="G1026">
-        <f t="shared" si="14"/>
-        <v>20.1101714011625</v>
-      </c>
     </row>
     <row r="1027" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
@@ -48346,10 +46884,6 @@
       <c r="F1027">
         <v>7.4897999999999998</v>
       </c>
-      <c r="G1027">
-        <f t="shared" si="14"/>
-        <v>7.4897999999999998</v>
-      </c>
     </row>
     <row r="1028" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
@@ -48367,10 +46901,6 @@
       <c r="F1028">
         <v>10.318</v>
       </c>
-      <c r="G1028">
-        <f t="shared" si="14"/>
-        <v>10.318</v>
-      </c>
     </row>
     <row r="1029" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
@@ -48388,10 +46918,6 @@
       <c r="F1029">
         <v>12.741299999999999</v>
       </c>
-      <c r="G1029">
-        <f t="shared" si="14"/>
-        <v>12.741299999999999</v>
-      </c>
     </row>
     <row r="1030" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
@@ -48409,10 +46935,6 @@
       <c r="F1030">
         <v>10.8872</v>
       </c>
-      <c r="G1030">
-        <f t="shared" si="14"/>
-        <v>10.8872</v>
-      </c>
     </row>
     <row r="1031" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
@@ -48430,10 +46952,6 @@
       <c r="F1031">
         <v>13.892000000000001</v>
       </c>
-      <c r="G1031">
-        <f t="shared" si="14"/>
-        <v>13.892000000000001</v>
-      </c>
     </row>
     <row r="1032" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
@@ -48451,10 +46969,6 @@
       <c r="F1032">
         <v>15.2</v>
       </c>
-      <c r="G1032">
-        <f t="shared" si="14"/>
-        <v>15.2</v>
-      </c>
     </row>
     <row r="1033" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
@@ -48472,10 +46986,6 @@
       <c r="F1033">
         <v>16.432000000000002</v>
       </c>
-      <c r="G1033">
-        <f t="shared" si="14"/>
-        <v>16.432000000000002</v>
-      </c>
     </row>
     <row r="1034" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
@@ -48494,8 +47004,7 @@
         <v>16.502500000000001</v>
       </c>
       <c r="G1034">
-        <f t="shared" si="14"/>
-        <v>16.502500000000001</v>
+        <v>20.85</v>
       </c>
       <c r="H1034" t="s">
         <v>27</v>
@@ -48517,13 +47026,6 @@
       <c r="F1035">
         <v>16.732200000000002</v>
       </c>
-      <c r="G1035">
-        <f t="shared" si="14"/>
-        <v>16.732200000000002</v>
-      </c>
-      <c r="H1035" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1036" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
@@ -48541,10 +47043,6 @@
       <c r="F1036">
         <v>17.0655</v>
       </c>
-      <c r="G1036">
-        <f t="shared" si="14"/>
-        <v>17.0655</v>
-      </c>
     </row>
     <row r="1037" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
@@ -48562,10 +47060,6 @@
       <c r="F1037">
         <v>17.685500000000001</v>
       </c>
-      <c r="G1037">
-        <f t="shared" si="14"/>
-        <v>17.685500000000001</v>
-      </c>
     </row>
     <row r="1038" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
@@ -48583,10 +47077,6 @@
       <c r="F1038">
         <v>9.6047999999999991</v>
       </c>
-      <c r="G1038">
-        <f t="shared" si="14"/>
-        <v>9.6047999999999991</v>
-      </c>
     </row>
     <row r="1039" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
@@ -48604,10 +47094,6 @@
       <c r="F1039">
         <v>12.738</v>
       </c>
-      <c r="G1039">
-        <f t="shared" si="14"/>
-        <v>12.738</v>
-      </c>
     </row>
     <row r="1040" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
@@ -48625,12 +47111,8 @@
       <c r="F1040">
         <v>14.497</v>
       </c>
-      <c r="G1040">
-        <f t="shared" si="14"/>
-        <v>14.497</v>
-      </c>
-    </row>
-    <row r="1041" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1041" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -48646,12 +47128,8 @@
       <c r="F1041">
         <v>17.078399999999998</v>
       </c>
-      <c r="G1041">
-        <f t="shared" si="14"/>
-        <v>17.078399999999998</v>
-      </c>
-    </row>
-    <row r="1042" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1042" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -48667,12 +47145,8 @@
       <c r="F1042">
         <v>20.495999999999999</v>
       </c>
-      <c r="G1042">
-        <f t="shared" si="14"/>
-        <v>20.495999999999999</v>
-      </c>
-    </row>
-    <row r="1043" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1043" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -48688,12 +47162,8 @@
       <c r="F1043">
         <v>22.349699999999999</v>
       </c>
-      <c r="G1043">
-        <f t="shared" si="14"/>
-        <v>22.349699999999999</v>
-      </c>
-    </row>
-    <row r="1044" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1044" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -48709,12 +47179,8 @@
       <c r="F1044">
         <v>23.020800000000005</v>
       </c>
-      <c r="G1044">
-        <f t="shared" si="14"/>
-        <v>23.020800000000005</v>
-      </c>
-    </row>
-    <row r="1045" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1045" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -48730,12 +47196,8 @@
       <c r="F1045">
         <v>23.687999999999999</v>
       </c>
-      <c r="G1045">
-        <f t="shared" si="14"/>
-        <v>23.687999999999999</v>
-      </c>
-    </row>
-    <row r="1046" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1046" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -48751,15 +47213,8 @@
       <c r="F1046">
         <v>24.631799999999998</v>
       </c>
-      <c r="G1046">
-        <f t="shared" si="14"/>
-        <v>24.631799999999998</v>
-      </c>
-      <c r="H1046" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1047" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1047" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -48775,12 +47230,8 @@
       <c r="F1047">
         <v>25.207600000000003</v>
       </c>
-      <c r="G1047">
-        <f t="shared" si="14"/>
-        <v>25.207600000000003</v>
-      </c>
-    </row>
-    <row r="1048" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1048" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -48796,12 +47247,8 @@
       <c r="F1048">
         <v>24.039699999999996</v>
       </c>
-      <c r="G1048">
-        <f t="shared" si="14"/>
-        <v>24.039699999999996</v>
-      </c>
-    </row>
-    <row r="1049" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1049" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -48818,12 +47265,8 @@
       <c r="F1049">
         <v>7.4561999999999991</v>
       </c>
-      <c r="G1049">
-        <f t="shared" si="14"/>
-        <v>7.4561999999999991</v>
-      </c>
-    </row>
-    <row r="1050" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1050" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -48839,12 +47282,8 @@
       <c r="F1050">
         <v>11.081100000000001</v>
       </c>
-      <c r="G1050">
-        <f t="shared" si="14"/>
-        <v>11.081100000000001</v>
-      </c>
-    </row>
-    <row r="1051" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1051" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -48860,12 +47299,8 @@
       <c r="F1051">
         <v>12.922000000000001</v>
       </c>
-      <c r="G1051">
-        <f t="shared" si="14"/>
-        <v>12.922000000000001</v>
-      </c>
-    </row>
-    <row r="1052" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1052" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -48881,12 +47316,8 @@
       <c r="F1052">
         <v>16.5564</v>
       </c>
-      <c r="G1052">
-        <f t="shared" si="14"/>
-        <v>16.5564</v>
-      </c>
-    </row>
-    <row r="1053" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1053" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -48902,12 +47333,8 @@
       <c r="F1053">
         <v>17.243100000000002</v>
       </c>
-      <c r="G1053">
-        <f t="shared" si="14"/>
-        <v>17.243100000000002</v>
-      </c>
-    </row>
-    <row r="1054" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1054" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -48923,12 +47350,8 @@
       <c r="F1054">
         <v>18.874200000000002</v>
       </c>
-      <c r="G1054">
-        <f t="shared" si="14"/>
-        <v>18.874200000000002</v>
-      </c>
-    </row>
-    <row r="1055" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1055" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -48944,12 +47367,8 @@
       <c r="F1055">
         <v>19.495000000000001</v>
       </c>
-      <c r="G1055">
-        <f t="shared" si="14"/>
-        <v>19.495000000000001</v>
-      </c>
-    </row>
-    <row r="1056" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1056" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -48965,12 +47384,8 @@
       <c r="F1056">
         <v>20.399199999999997</v>
       </c>
-      <c r="G1056">
-        <f t="shared" si="14"/>
-        <v>20.399199999999997</v>
-      </c>
-    </row>
-    <row r="1057" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1057" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -48986,15 +47401,8 @@
       <c r="F1057">
         <v>22.8123</v>
       </c>
-      <c r="G1057">
-        <f t="shared" si="14"/>
-        <v>22.8123</v>
-      </c>
-      <c r="H1057" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1058" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1058" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -49010,12 +47418,8 @@
       <c r="F1058">
         <v>22.352000000000004</v>
       </c>
-      <c r="G1058">
-        <f t="shared" si="14"/>
-        <v>22.352000000000004</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1059" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -49031,12 +47435,8 @@
       <c r="F1059">
         <v>22.697199999999999</v>
       </c>
-      <c r="G1059">
-        <f t="shared" si="14"/>
-        <v>22.697199999999999</v>
-      </c>
-    </row>
-    <row r="1060" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1060" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -49052,12 +47452,8 @@
       <c r="F1060">
         <v>6.96</v>
       </c>
-      <c r="G1060">
-        <f t="shared" si="14"/>
-        <v>6.96</v>
-      </c>
-    </row>
-    <row r="1061" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1061" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -49073,12 +47469,8 @@
       <c r="F1061">
         <v>9.7843999999999998</v>
       </c>
-      <c r="G1061">
-        <f t="shared" si="14"/>
-        <v>9.7843999999999998</v>
-      </c>
-    </row>
-    <row r="1062" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1062" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -49094,12 +47486,8 @@
       <c r="F1062">
         <v>12.097799999999999</v>
       </c>
-      <c r="G1062">
-        <f t="shared" si="14"/>
-        <v>12.097799999999999</v>
-      </c>
-    </row>
-    <row r="1063" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1063" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -49115,12 +47503,8 @@
       <c r="F1063">
         <v>13.3996</v>
       </c>
-      <c r="G1063">
-        <f t="shared" si="14"/>
-        <v>13.3996</v>
-      </c>
-    </row>
-    <row r="1064" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1064" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
         <v>16</v>
       </c>
@@ -49136,12 +47520,8 @@
       <c r="F1064">
         <v>18.352399999999999</v>
       </c>
-      <c r="G1064">
-        <f t="shared" si="14"/>
-        <v>18.352399999999999</v>
-      </c>
-    </row>
-    <row r="1065" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1065" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
         <v>16</v>
       </c>
@@ -49157,12 +47537,8 @@
       <c r="F1065">
         <v>17.783999999999999</v>
       </c>
-      <c r="G1065">
-        <f t="shared" si="14"/>
-        <v>17.783999999999999</v>
-      </c>
-    </row>
-    <row r="1066" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1066" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
         <v>16</v>
       </c>
@@ -49178,12 +47554,8 @@
       <c r="F1066">
         <v>17.6967</v>
       </c>
-      <c r="G1066">
-        <f t="shared" si="14"/>
-        <v>17.6967</v>
-      </c>
-    </row>
-    <row r="1067" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1067" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>16</v>
       </c>
@@ -49199,12 +47571,8 @@
       <c r="F1067">
         <v>19.3248</v>
       </c>
-      <c r="G1067">
-        <f t="shared" ref="G1067:G1130" si="15">F1067</f>
-        <v>19.3248</v>
-      </c>
-    </row>
-    <row r="1068" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1068" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
         <v>16</v>
       </c>
@@ -49220,15 +47588,8 @@
       <c r="F1068">
         <v>20.511399999999998</v>
       </c>
-      <c r="G1068">
-        <f t="shared" si="15"/>
-        <v>20.511399999999998</v>
-      </c>
-      <c r="H1068" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1069" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1069" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
         <v>16</v>
       </c>
@@ -49244,12 +47605,8 @@
       <c r="F1069">
         <v>20.461199999999998</v>
       </c>
-      <c r="G1069">
-        <f t="shared" si="15"/>
-        <v>20.461199999999998</v>
-      </c>
-    </row>
-    <row r="1070" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1070" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>16</v>
       </c>
@@ -49265,12 +47622,8 @@
       <c r="F1070">
         <v>21.339900000000004</v>
       </c>
-      <c r="G1070">
-        <f t="shared" si="15"/>
-        <v>21.339900000000004</v>
-      </c>
-    </row>
-    <row r="1071" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1071" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
         <v>16</v>
       </c>
@@ -49286,12 +47639,8 @@
       <c r="F1071">
         <v>8.0898000000000003</v>
       </c>
-      <c r="G1071">
-        <f t="shared" si="15"/>
-        <v>8.0898000000000003</v>
-      </c>
-    </row>
-    <row r="1072" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1072" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
         <v>16</v>
       </c>
@@ -49307,12 +47656,8 @@
       <c r="F1072">
         <v>10.7502</v>
       </c>
-      <c r="G1072">
-        <f t="shared" si="15"/>
-        <v>10.7502</v>
-      </c>
-    </row>
-    <row r="1073" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1073" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
         <v>16</v>
       </c>
@@ -49328,12 +47673,8 @@
       <c r="F1073">
         <v>13.171200000000001</v>
       </c>
-      <c r="G1073">
-        <f t="shared" si="15"/>
-        <v>13.171200000000001</v>
-      </c>
-    </row>
-    <row r="1074" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1074" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
         <v>16</v>
       </c>
@@ -49349,12 +47690,8 @@
       <c r="F1074">
         <v>12.583999999999998</v>
       </c>
-      <c r="G1074">
-        <f t="shared" si="15"/>
-        <v>12.583999999999998</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1075" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
         <v>16</v>
       </c>
@@ -49370,12 +47707,8 @@
       <c r="F1075">
         <v>16.5564</v>
       </c>
-      <c r="G1075">
-        <f t="shared" si="15"/>
-        <v>16.5564</v>
-      </c>
-    </row>
-    <row r="1076" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1076" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
         <v>16</v>
       </c>
@@ -49391,12 +47724,8 @@
       <c r="F1076">
         <v>18.115200000000002</v>
       </c>
-      <c r="G1076">
-        <f t="shared" si="15"/>
-        <v>18.115200000000002</v>
-      </c>
-    </row>
-    <row r="1077" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1077" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
         <v>16</v>
       </c>
@@ -49412,12 +47741,8 @@
       <c r="F1077">
         <v>19.6692</v>
       </c>
-      <c r="G1077">
-        <f t="shared" si="15"/>
-        <v>19.6692</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1078" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
         <v>16</v>
       </c>
@@ -49433,12 +47758,8 @@
       <c r="F1078">
         <v>20.550599999999999</v>
       </c>
-      <c r="G1078">
-        <f t="shared" si="15"/>
-        <v>20.550599999999999</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1079" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
         <v>16</v>
       </c>
@@ -49454,15 +47775,8 @@
       <c r="F1079">
         <v>19.724599999999999</v>
       </c>
-      <c r="G1079">
-        <f t="shared" si="15"/>
-        <v>19.724599999999999</v>
-      </c>
-      <c r="H1079" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1080" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1080" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
         <v>16</v>
       </c>
@@ -49478,12 +47792,8 @@
       <c r="F1080">
         <v>21.819800000000001</v>
       </c>
-      <c r="G1080">
-        <f t="shared" si="15"/>
-        <v>21.819800000000001</v>
-      </c>
-    </row>
-    <row r="1081" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1081" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>16</v>
       </c>
@@ -49499,12 +47809,8 @@
       <c r="F1081">
         <v>22.72</v>
       </c>
-      <c r="G1081">
-        <f t="shared" si="15"/>
-        <v>22.72</v>
-      </c>
-    </row>
-    <row r="1082" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1082" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
         <v>21</v>
       </c>
@@ -49520,12 +47826,8 @@
       <c r="F1082">
         <v>6.507200000000001</v>
       </c>
-      <c r="G1082">
-        <f t="shared" si="15"/>
-        <v>6.507200000000001</v>
-      </c>
-    </row>
-    <row r="1083" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1083" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>21</v>
       </c>
@@ -49541,12 +47843,8 @@
       <c r="F1083">
         <v>9.6515999999999984</v>
       </c>
-      <c r="G1083">
-        <f t="shared" si="15"/>
-        <v>9.6515999999999984</v>
-      </c>
-    </row>
-    <row r="1084" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1084" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>21</v>
       </c>
@@ -49562,12 +47860,8 @@
       <c r="F1084">
         <v>12.1128</v>
       </c>
-      <c r="G1084">
-        <f t="shared" si="15"/>
-        <v>12.1128</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1085" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
         <v>21</v>
       </c>
@@ -49583,12 +47877,8 @@
       <c r="F1085">
         <v>16.083900000000003</v>
       </c>
-      <c r="G1085">
-        <f t="shared" si="15"/>
-        <v>16.083900000000003</v>
-      </c>
-    </row>
-    <row r="1086" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1086" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
         <v>21</v>
       </c>
@@ -49604,12 +47894,8 @@
       <c r="F1086">
         <v>13.984200000000001</v>
       </c>
-      <c r="G1086">
-        <f t="shared" si="15"/>
-        <v>13.984200000000001</v>
-      </c>
-    </row>
-    <row r="1087" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1087" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
         <v>21</v>
       </c>
@@ -49625,12 +47911,8 @@
       <c r="F1087">
         <v>17.474599999999999</v>
       </c>
-      <c r="G1087">
-        <f t="shared" si="15"/>
-        <v>17.474599999999999</v>
-      </c>
-    </row>
-    <row r="1088" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1088" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
         <v>21</v>
       </c>
@@ -49644,10 +47926,6 @@
         <v>9</v>
       </c>
       <c r="F1088">
-        <v>18.167499999999997</v>
-      </c>
-      <c r="G1088">
-        <f t="shared" si="15"/>
         <v>18.167499999999997</v>
       </c>
     </row>
@@ -49667,10 +47945,6 @@
       <c r="F1089">
         <v>18.589999999999996</v>
       </c>
-      <c r="G1089">
-        <f t="shared" si="15"/>
-        <v>18.589999999999996</v>
-      </c>
     </row>
     <row r="1090" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
@@ -49688,10 +47962,6 @@
       <c r="F1090">
         <v>19.700099999999999</v>
       </c>
-      <c r="G1090">
-        <f t="shared" si="15"/>
-        <v>19.700099999999999</v>
-      </c>
     </row>
     <row r="1091" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
@@ -49710,8 +47980,7 @@
         <v>20.844000000000001</v>
       </c>
       <c r="G1091">
-        <f t="shared" si="15"/>
-        <v>20.844000000000001</v>
+        <v>21</v>
       </c>
       <c r="H1091" t="s">
         <v>27</v>
@@ -49733,13 +48002,6 @@
       <c r="F1092">
         <v>21.191399999999998</v>
       </c>
-      <c r="G1092">
-        <f t="shared" si="15"/>
-        <v>21.191399999999998</v>
-      </c>
-      <c r="H1092" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1093" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
@@ -49757,10 +48019,6 @@
       <c r="F1093">
         <v>6.3356000000000003</v>
       </c>
-      <c r="G1093">
-        <f t="shared" si="15"/>
-        <v>6.3356000000000003</v>
-      </c>
     </row>
     <row r="1094" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
@@ -49778,10 +48036,6 @@
       <c r="F1094">
         <v>9.4124999999999996</v>
       </c>
-      <c r="G1094">
-        <f t="shared" si="15"/>
-        <v>9.4124999999999996</v>
-      </c>
     </row>
     <row r="1095" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
@@ -49799,10 +48053,6 @@
       <c r="F1095">
         <v>11.8299</v>
       </c>
-      <c r="G1095">
-        <f t="shared" si="15"/>
-        <v>11.8299</v>
-      </c>
     </row>
     <row r="1096" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
@@ -49820,10 +48070,6 @@
       <c r="F1096">
         <v>14.16</v>
       </c>
-      <c r="G1096">
-        <f t="shared" si="15"/>
-        <v>14.16</v>
-      </c>
     </row>
     <row r="1097" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
@@ -49841,10 +48087,6 @@
       <c r="F1097">
         <v>15.593</v>
       </c>
-      <c r="G1097">
-        <f t="shared" si="15"/>
-        <v>15.593</v>
-      </c>
     </row>
     <row r="1098" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
@@ -49862,10 +48104,6 @@
       <c r="F1098">
         <v>16.170999999999999</v>
       </c>
-      <c r="G1098">
-        <f t="shared" si="15"/>
-        <v>16.170999999999999</v>
-      </c>
     </row>
     <row r="1099" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
@@ -49883,10 +48121,6 @@
       <c r="F1099">
         <v>18.248999999999999</v>
       </c>
-      <c r="G1099">
-        <f t="shared" si="15"/>
-        <v>18.248999999999999</v>
-      </c>
     </row>
     <row r="1100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
@@ -49905,8 +48139,7 @@
         <v>18.7944</v>
       </c>
       <c r="G1100">
-        <f t="shared" si="15"/>
-        <v>18.7944</v>
+        <v>20.87</v>
       </c>
       <c r="H1100" t="s">
         <v>27</v>
@@ -49928,13 +48161,6 @@
       <c r="F1101">
         <v>19.488899999999997</v>
       </c>
-      <c r="G1101">
-        <f t="shared" si="15"/>
-        <v>19.488899999999997</v>
-      </c>
-      <c r="H1101" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
@@ -49952,10 +48178,6 @@
       <c r="F1102">
         <v>20.195999999999998</v>
       </c>
-      <c r="G1102">
-        <f t="shared" si="15"/>
-        <v>20.195999999999998</v>
-      </c>
     </row>
     <row r="1103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
@@ -49973,10 +48195,6 @@
       <c r="F1103">
         <v>19.545300000000001</v>
       </c>
-      <c r="G1103">
-        <f t="shared" si="15"/>
-        <v>19.545300000000001</v>
-      </c>
     </row>
     <row r="1104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
@@ -49994,12 +48212,8 @@
       <c r="F1104">
         <v>7.68</v>
       </c>
-      <c r="G1104">
-        <f t="shared" si="15"/>
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="1105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
         <v>17</v>
       </c>
@@ -50015,12 +48229,8 @@
       <c r="F1105">
         <v>11.2468</v>
       </c>
-      <c r="G1105">
-        <f t="shared" si="15"/>
-        <v>11.2468</v>
-      </c>
-    </row>
-    <row r="1106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
         <v>17</v>
       </c>
@@ -50036,12 +48246,8 @@
       <c r="F1106">
         <v>14.643999999999998</v>
       </c>
-      <c r="G1106">
-        <f t="shared" si="15"/>
-        <v>14.643999999999998</v>
-      </c>
-    </row>
-    <row r="1107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
         <v>17</v>
       </c>
@@ -50057,12 +48263,8 @@
       <c r="F1107">
         <v>18.2835</v>
       </c>
-      <c r="G1107">
-        <f t="shared" si="15"/>
-        <v>18.2835</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
         <v>17</v>
       </c>
@@ -50078,12 +48280,8 @@
       <c r="F1108">
         <v>20.590500000000002</v>
       </c>
-      <c r="G1108">
-        <f t="shared" si="15"/>
-        <v>20.590500000000002</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
         <v>17</v>
       </c>
@@ -50099,12 +48297,8 @@
       <c r="F1109">
         <v>22.845600000000001</v>
       </c>
-      <c r="G1109">
-        <f t="shared" si="15"/>
-        <v>22.845600000000001</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
         <v>17</v>
       </c>
@@ -50120,12 +48314,8 @@
       <c r="F1110">
         <v>23.795200000000001</v>
       </c>
-      <c r="G1110">
-        <f t="shared" si="15"/>
-        <v>23.795200000000001</v>
-      </c>
-    </row>
-    <row r="1111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
         <v>17</v>
       </c>
@@ -50141,15 +48331,8 @@
       <c r="F1111">
         <v>24.320799999999998</v>
       </c>
-      <c r="G1111">
-        <f t="shared" si="15"/>
-        <v>24.320799999999998</v>
-      </c>
-      <c r="H1111" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
         <v>17</v>
       </c>
@@ -50165,15 +48348,8 @@
       <c r="F1112">
         <v>24.446999999999999</v>
       </c>
-      <c r="G1112">
-        <f t="shared" si="15"/>
-        <v>24.446999999999999</v>
-      </c>
-      <c r="H1112" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
         <v>17</v>
       </c>
@@ -50189,12 +48365,8 @@
       <c r="F1113">
         <v>24.847199999999997</v>
       </c>
-      <c r="G1113">
-        <f t="shared" si="15"/>
-        <v>24.847199999999997</v>
-      </c>
-    </row>
-    <row r="1114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
         <v>17</v>
       </c>
@@ -50210,12 +48382,8 @@
       <c r="F1114">
         <v>22.531999999999996</v>
       </c>
-      <c r="G1114">
-        <f t="shared" si="15"/>
-        <v>22.531999999999996</v>
-      </c>
-    </row>
-    <row r="1115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
         <v>17</v>
       </c>
@@ -50231,12 +48399,8 @@
       <c r="F1115">
         <v>7.3137999999999996</v>
       </c>
-      <c r="G1115">
-        <f t="shared" si="15"/>
-        <v>7.3137999999999996</v>
-      </c>
-    </row>
-    <row r="1116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>17</v>
       </c>
@@ -50252,12 +48416,8 @@
       <c r="F1116">
         <v>11.023599999999998</v>
       </c>
-      <c r="G1116">
-        <f t="shared" si="15"/>
-        <v>11.023599999999998</v>
-      </c>
-    </row>
-    <row r="1117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>17</v>
       </c>
@@ -50273,12 +48433,8 @@
       <c r="F1117">
         <v>13.492799999999999</v>
       </c>
-      <c r="G1117">
-        <f t="shared" si="15"/>
-        <v>13.492799999999999</v>
-      </c>
-    </row>
-    <row r="1118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
         <v>17</v>
       </c>
@@ -50294,12 +48450,8 @@
       <c r="F1118">
         <v>16.840599999999998</v>
       </c>
-      <c r="G1118">
-        <f t="shared" si="15"/>
-        <v>16.840599999999998</v>
-      </c>
-    </row>
-    <row r="1119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
         <v>17</v>
       </c>
@@ -50315,12 +48467,8 @@
       <c r="F1119">
         <v>19.481999999999999</v>
       </c>
-      <c r="G1119">
-        <f t="shared" si="15"/>
-        <v>19.481999999999999</v>
-      </c>
-    </row>
-    <row r="1120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
         <v>17</v>
       </c>
@@ -50336,12 +48484,8 @@
       <c r="F1120">
         <v>22.633600000000001</v>
       </c>
-      <c r="G1120">
-        <f t="shared" si="15"/>
-        <v>22.633600000000001</v>
-      </c>
-    </row>
-    <row r="1121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
         <v>17</v>
       </c>
@@ -50357,12 +48501,8 @@
       <c r="F1121">
         <v>24.105599999999999</v>
       </c>
-      <c r="G1121">
-        <f t="shared" si="15"/>
-        <v>24.105599999999999</v>
-      </c>
-    </row>
-    <row r="1122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
         <v>17</v>
       </c>
@@ -50378,15 +48518,8 @@
       <c r="F1122">
         <v>25.936899999999994</v>
       </c>
-      <c r="G1122">
-        <f t="shared" si="15"/>
-        <v>25.936899999999994</v>
-      </c>
-      <c r="H1122" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
         <v>17</v>
       </c>
@@ -50402,15 +48535,8 @@
       <c r="F1123">
         <v>24.915800000000001</v>
       </c>
-      <c r="G1123">
-        <f t="shared" si="15"/>
-        <v>24.915800000000001</v>
-      </c>
-      <c r="H1123" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
         <v>17</v>
       </c>
@@ -50426,12 +48552,8 @@
       <c r="F1124">
         <v>24.590499999999999</v>
       </c>
-      <c r="G1124">
-        <f t="shared" si="15"/>
-        <v>24.590499999999999</v>
-      </c>
-    </row>
-    <row r="1125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
         <v>17</v>
       </c>
@@ -50447,12 +48569,8 @@
       <c r="F1125">
         <v>25.136999999999997</v>
       </c>
-      <c r="G1125">
-        <f t="shared" si="15"/>
-        <v>25.136999999999997</v>
-      </c>
-    </row>
-    <row r="1126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
         <v>17</v>
       </c>
@@ -50468,12 +48586,8 @@
       <c r="F1126">
         <v>5.7330000000000005</v>
       </c>
-      <c r="G1126">
-        <f t="shared" si="15"/>
-        <v>5.7330000000000005</v>
-      </c>
-    </row>
-    <row r="1127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
         <v>17</v>
       </c>
@@ -50489,12 +48603,8 @@
       <c r="F1127">
         <v>8.2151000000000014</v>
       </c>
-      <c r="G1127">
-        <f t="shared" si="15"/>
-        <v>8.2151000000000014</v>
-      </c>
-    </row>
-    <row r="1128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
         <v>17</v>
       </c>
@@ -50510,12 +48620,8 @@
       <c r="F1128">
         <v>10.610999999999999</v>
       </c>
-      <c r="G1128">
-        <f t="shared" si="15"/>
-        <v>10.610999999999999</v>
-      </c>
-    </row>
-    <row r="1129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
         <v>17</v>
       </c>
@@ -50531,12 +48637,8 @@
       <c r="F1129">
         <v>13.234500000000001</v>
       </c>
-      <c r="G1129">
-        <f t="shared" si="15"/>
-        <v>13.234500000000001</v>
-      </c>
-    </row>
-    <row r="1130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>17</v>
       </c>
@@ -50552,12 +48654,8 @@
       <c r="F1130">
         <v>15.264000000000001</v>
       </c>
-      <c r="G1130">
-        <f t="shared" si="15"/>
-        <v>15.264000000000001</v>
-      </c>
-    </row>
-    <row r="1131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
         <v>17</v>
       </c>
@@ -50573,12 +48671,8 @@
       <c r="F1131">
         <v>16.933800000000002</v>
       </c>
-      <c r="G1131">
-        <f t="shared" ref="G1131:G1195" si="16">F1131</f>
-        <v>16.933800000000002</v>
-      </c>
-    </row>
-    <row r="1132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
         <v>17</v>
       </c>
@@ -50594,12 +48688,8 @@
       <c r="F1132">
         <v>18.791999999999998</v>
       </c>
-      <c r="G1132">
-        <f t="shared" si="16"/>
-        <v>18.791999999999998</v>
-      </c>
-    </row>
-    <row r="1133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
         <v>17</v>
       </c>
@@ -50615,15 +48705,8 @@
       <c r="F1133">
         <v>19.670000000000002</v>
       </c>
-      <c r="G1133">
-        <f t="shared" si="16"/>
-        <v>19.670000000000002</v>
-      </c>
-      <c r="H1133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
         <v>17</v>
       </c>
@@ -50639,15 +48722,8 @@
       <c r="F1134">
         <v>20.914999999999999</v>
       </c>
-      <c r="G1134">
-        <f t="shared" si="16"/>
-        <v>20.914999999999999</v>
-      </c>
-      <c r="H1134" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
         <v>17</v>
       </c>
@@ -50663,12 +48739,8 @@
       <c r="F1135">
         <v>20.790399999999998</v>
       </c>
-      <c r="G1135">
-        <f t="shared" si="16"/>
-        <v>20.790399999999998</v>
-      </c>
-    </row>
-    <row r="1136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
         <v>17</v>
       </c>
@@ -50684,12 +48756,8 @@
       <c r="F1136">
         <v>20.262799999999999</v>
       </c>
-      <c r="G1136">
-        <f t="shared" si="16"/>
-        <v>20.262799999999999</v>
-      </c>
-    </row>
-    <row r="1137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
         <v>17</v>
       </c>
@@ -50705,12 +48773,8 @@
       <c r="F1137">
         <v>5.0961999999999996</v>
       </c>
-      <c r="G1137">
-        <f t="shared" si="16"/>
-        <v>5.0961999999999996</v>
-      </c>
-    </row>
-    <row r="1138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
         <v>17</v>
       </c>
@@ -50726,12 +48790,8 @@
       <c r="F1138">
         <v>7.1189999999999998</v>
       </c>
-      <c r="G1138">
-        <f t="shared" si="16"/>
-        <v>7.1189999999999998</v>
-      </c>
-    </row>
-    <row r="1139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
         <v>17</v>
       </c>
@@ -50747,12 +48807,8 @@
       <c r="F1139">
         <v>9.0643999999999991</v>
       </c>
-      <c r="G1139">
-        <f t="shared" si="16"/>
-        <v>9.0643999999999991</v>
-      </c>
-    </row>
-    <row r="1140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
         <v>17</v>
       </c>
@@ -50768,12 +48824,8 @@
       <c r="F1140">
         <v>11.168299999999999</v>
       </c>
-      <c r="G1140">
-        <f t="shared" si="16"/>
-        <v>11.168299999999999</v>
-      </c>
-    </row>
-    <row r="1141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
         <v>17</v>
       </c>
@@ -50789,12 +48841,8 @@
       <c r="F1141">
         <v>12.615</v>
       </c>
-      <c r="G1141">
-        <f t="shared" si="16"/>
-        <v>12.615</v>
-      </c>
-    </row>
-    <row r="1142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
         <v>17</v>
       </c>
@@ -50810,12 +48858,8 @@
       <c r="F1142">
         <v>13.9345</v>
       </c>
-      <c r="G1142">
-        <f t="shared" si="16"/>
-        <v>13.9345</v>
-      </c>
-    </row>
-    <row r="1143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1143" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
         <v>17</v>
       </c>
@@ -50831,12 +48875,8 @@
       <c r="F1143">
         <v>15.344000000000001</v>
       </c>
-      <c r="G1143">
-        <f t="shared" si="16"/>
-        <v>15.344000000000001</v>
-      </c>
-    </row>
-    <row r="1144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
         <v>17</v>
       </c>
@@ -50852,15 +48892,8 @@
       <c r="F1144">
         <v>15.1944</v>
       </c>
-      <c r="G1144">
-        <f t="shared" si="16"/>
-        <v>15.1944</v>
-      </c>
-      <c r="H1144" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1145" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
         <v>17</v>
       </c>
@@ -50876,15 +48909,8 @@
       <c r="F1145">
         <v>15.061199999999999</v>
       </c>
-      <c r="G1145">
-        <f t="shared" si="16"/>
-        <v>15.061199999999999</v>
-      </c>
-      <c r="H1145" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
         <v>17</v>
       </c>
@@ -50900,12 +48926,8 @@
       <c r="F1146">
         <v>15.968</v>
       </c>
-      <c r="G1146">
-        <f t="shared" si="16"/>
-        <v>15.968</v>
-      </c>
-    </row>
-    <row r="1147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
         <v>17</v>
       </c>
@@ -50921,12 +48943,8 @@
       <c r="F1147">
         <v>18.631999999999998</v>
       </c>
-      <c r="G1147">
-        <f t="shared" si="16"/>
-        <v>18.631999999999998</v>
-      </c>
-    </row>
-    <row r="1148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1148" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
         <v>22</v>
       </c>
@@ -50942,12 +48960,8 @@
       <c r="F1148">
         <v>6.8713999999999995</v>
       </c>
-      <c r="G1148">
-        <f t="shared" si="16"/>
-        <v>6.8713999999999995</v>
-      </c>
-    </row>
-    <row r="1149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
         <v>22</v>
       </c>
@@ -50963,12 +48977,8 @@
       <c r="F1149">
         <v>11.225600000000002</v>
       </c>
-      <c r="G1149">
-        <f t="shared" si="16"/>
-        <v>11.225600000000002</v>
-      </c>
-    </row>
-    <row r="1150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1150" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
         <v>22</v>
       </c>
@@ -50984,12 +48994,8 @@
       <c r="F1150">
         <v>15.862</v>
       </c>
-      <c r="G1150">
-        <f t="shared" si="16"/>
-        <v>15.862</v>
-      </c>
-    </row>
-    <row r="1151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1151" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
         <v>22</v>
       </c>
@@ -51005,12 +49011,8 @@
       <c r="F1151">
         <v>16.912800000000001</v>
       </c>
-      <c r="G1151">
-        <f t="shared" si="16"/>
-        <v>16.912800000000001</v>
-      </c>
-    </row>
-    <row r="1152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
         <v>22</v>
       </c>
@@ -51024,10 +49026,6 @@
         <v>9</v>
       </c>
       <c r="F1152">
-        <v>20.674400000000002</v>
-      </c>
-      <c r="G1152">
-        <f t="shared" si="16"/>
         <v>20.674400000000002</v>
       </c>
     </row>
@@ -51047,10 +49045,6 @@
       <c r="F1153">
         <v>22.05</v>
       </c>
-      <c r="G1153">
-        <f t="shared" si="16"/>
-        <v>22.05</v>
-      </c>
     </row>
     <row r="1154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
@@ -51068,10 +49062,6 @@
       <c r="F1154">
         <v>23.294399999999996</v>
       </c>
-      <c r="G1154">
-        <f t="shared" si="16"/>
-        <v>23.294399999999996</v>
-      </c>
     </row>
     <row r="1155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
@@ -51089,10 +49079,6 @@
       <c r="F1155">
         <v>23.439500000000002</v>
       </c>
-      <c r="G1155">
-        <f t="shared" si="16"/>
-        <v>23.439500000000002</v>
-      </c>
     </row>
     <row r="1156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
@@ -51111,7 +49097,7 @@
         <v>24.252000000000002</v>
       </c>
       <c r="G1156">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G1156:G1175" si="11">F1156</f>
         <v>24.252000000000002</v>
       </c>
       <c r="H1156" t="s">
@@ -51134,10 +49120,6 @@
       <c r="F1157">
         <v>24.935600000000001</v>
       </c>
-      <c r="G1157">
-        <f t="shared" si="16"/>
-        <v>24.935600000000001</v>
-      </c>
     </row>
     <row r="1158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
@@ -51155,12 +49137,8 @@
       <c r="F1158">
         <v>24.414500000000004</v>
       </c>
-      <c r="G1158">
-        <f t="shared" si="16"/>
-        <v>24.414500000000004</v>
-      </c>
-    </row>
-    <row r="1159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
         <v>18</v>
       </c>
@@ -51176,12 +49154,8 @@
       <c r="F1159">
         <v>5.22</v>
       </c>
-      <c r="G1159">
-        <f t="shared" si="16"/>
-        <v>5.22</v>
-      </c>
-    </row>
-    <row r="1160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
         <v>18</v>
       </c>
@@ -51197,12 +49171,8 @@
       <c r="F1160">
         <v>8.4240000000000013</v>
       </c>
-      <c r="G1160">
-        <f t="shared" si="16"/>
-        <v>8.4240000000000013</v>
-      </c>
-    </row>
-    <row r="1161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
         <v>18</v>
       </c>
@@ -51218,12 +49188,8 @@
       <c r="F1161">
         <v>10.503</v>
       </c>
-      <c r="G1161">
-        <f t="shared" si="16"/>
-        <v>10.503</v>
-      </c>
-    </row>
-    <row r="1162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
         <v>18</v>
       </c>
@@ -51239,12 +49205,8 @@
       <c r="F1162">
         <v>12.1472</v>
       </c>
-      <c r="G1162">
-        <f t="shared" si="16"/>
-        <v>12.1472</v>
-      </c>
-    </row>
-    <row r="1163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
         <v>18</v>
       </c>
@@ -51260,12 +49222,8 @@
       <c r="F1163">
         <v>13.311000000000002</v>
       </c>
-      <c r="G1163">
-        <f t="shared" si="16"/>
-        <v>13.311000000000002</v>
-      </c>
-    </row>
-    <row r="1164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
         <v>18</v>
       </c>
@@ -51282,14 +49240,13 @@
         <v>12.973500000000001</v>
       </c>
       <c r="G1164">
-        <f t="shared" si="16"/>
-        <v>12.973500000000001</v>
+        <v>15.73</v>
       </c>
       <c r="H1164" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="1165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
         <v>18</v>
       </c>
@@ -51305,15 +49262,8 @@
       <c r="F1165">
         <v>14.267999999999999</v>
       </c>
-      <c r="G1165">
-        <f t="shared" si="16"/>
-        <v>14.267999999999999</v>
-      </c>
-      <c r="H1165" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
         <v>18</v>
       </c>
@@ -51329,12 +49279,8 @@
       <c r="F1166">
         <v>15.624000000000001</v>
       </c>
-      <c r="G1166">
-        <f t="shared" si="16"/>
-        <v>15.624000000000001</v>
-      </c>
-    </row>
-    <row r="1167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
         <v>18</v>
       </c>
@@ -51350,12 +49296,8 @@
       <c r="F1167">
         <v>15.652000000000001</v>
       </c>
-      <c r="G1167">
-        <f t="shared" si="16"/>
-        <v>15.652000000000001</v>
-      </c>
-    </row>
-    <row r="1168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
         <v>18</v>
       </c>
@@ -51371,12 +49313,8 @@
       <c r="F1168">
         <v>14.858400000000001</v>
       </c>
-      <c r="G1168">
-        <f t="shared" si="16"/>
-        <v>14.858400000000001</v>
-      </c>
-    </row>
-    <row r="1169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
         <v>18</v>
       </c>
@@ -51392,12 +49330,8 @@
       <c r="F1169">
         <v>14.500800000000002</v>
       </c>
-      <c r="G1169">
-        <f t="shared" si="16"/>
-        <v>14.500800000000002</v>
-      </c>
-    </row>
-    <row r="1170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
         <v>18</v>
       </c>
@@ -51413,12 +49347,8 @@
       <c r="F1170">
         <v>5.7376000000000014</v>
       </c>
-      <c r="G1170">
-        <f t="shared" si="16"/>
-        <v>5.7376000000000014</v>
-      </c>
-    </row>
-    <row r="1171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
         <v>18</v>
       </c>
@@ -51434,12 +49364,8 @@
       <c r="F1171">
         <v>10.566399999999998</v>
       </c>
-      <c r="G1171">
-        <f t="shared" si="16"/>
-        <v>10.566399999999998</v>
-      </c>
-    </row>
-    <row r="1172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
         <v>18</v>
       </c>
@@ -51455,12 +49381,8 @@
       <c r="F1172">
         <v>11.4376</v>
       </c>
-      <c r="G1172">
-        <f t="shared" si="16"/>
-        <v>11.4376</v>
-      </c>
-    </row>
-    <row r="1173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
         <v>18</v>
       </c>
@@ -51476,12 +49398,8 @@
       <c r="F1173">
         <v>14.351400000000002</v>
       </c>
-      <c r="G1173">
-        <f t="shared" si="16"/>
-        <v>14.351400000000002</v>
-      </c>
-    </row>
-    <row r="1174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
         <v>18</v>
       </c>
@@ -51497,12 +49415,8 @@
       <c r="F1174">
         <v>16.467200000000002</v>
       </c>
-      <c r="G1174">
-        <f t="shared" si="16"/>
-        <v>16.467200000000002</v>
-      </c>
-    </row>
-    <row r="1175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
         <v>18</v>
       </c>
@@ -51518,15 +49432,8 @@
       <c r="F1175">
         <v>17.629000000000001</v>
       </c>
-      <c r="G1175">
-        <f t="shared" si="16"/>
-        <v>17.629000000000001</v>
-      </c>
-      <c r="H1175" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
         <v>18</v>
       </c>
@@ -51542,12 +49449,8 @@
       <c r="F1176">
         <v>18.948599999999999</v>
       </c>
-      <c r="G1176">
-        <f t="shared" si="16"/>
-        <v>18.948599999999999</v>
-      </c>
-    </row>
-    <row r="1177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
         <v>18</v>
       </c>
@@ -51563,12 +49466,8 @@
       <c r="F1177">
         <v>20.6096</v>
       </c>
-      <c r="G1177">
-        <f t="shared" si="16"/>
-        <v>20.6096</v>
-      </c>
-    </row>
-    <row r="1178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
         <v>18</v>
       </c>
@@ -51584,12 +49483,8 @@
       <c r="F1178">
         <v>20.810399999999994</v>
       </c>
-      <c r="G1178">
-        <f t="shared" si="16"/>
-        <v>20.810399999999994</v>
-      </c>
-    </row>
-    <row r="1179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
         <v>18</v>
       </c>
@@ -51605,12 +49500,8 @@
       <c r="F1179">
         <v>20.833099999999998</v>
       </c>
-      <c r="G1179">
-        <f t="shared" si="16"/>
-        <v>20.833099999999998</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
         <v>18</v>
       </c>
@@ -51626,12 +49517,8 @@
       <c r="F1180">
         <v>20.495499999999996</v>
       </c>
-      <c r="G1180">
-        <f t="shared" si="16"/>
-        <v>20.495499999999996</v>
-      </c>
-    </row>
-    <row r="1181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
         <v>18</v>
       </c>
@@ -51647,12 +49534,8 @@
       <c r="F1181">
         <v>4.9717000000000002</v>
       </c>
-      <c r="G1181">
-        <f t="shared" si="16"/>
-        <v>4.9717000000000002</v>
-      </c>
-    </row>
-    <row r="1182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
         <v>18</v>
       </c>
@@ -51668,12 +49551,8 @@
       <c r="F1182">
         <v>7.9373000000000005</v>
       </c>
-      <c r="G1182">
-        <f t="shared" si="16"/>
-        <v>7.9373000000000005</v>
-      </c>
-    </row>
-    <row r="1183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
         <v>18</v>
       </c>
@@ -51689,12 +49568,8 @@
       <c r="F1183">
         <v>10.111500000000001</v>
       </c>
-      <c r="G1183">
-        <f t="shared" si="16"/>
-        <v>10.111500000000001</v>
-      </c>
-    </row>
-    <row r="1184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
         <v>18</v>
       </c>
@@ -51710,12 +49585,8 @@
       <c r="F1184">
         <v>12.935199999999998</v>
       </c>
-      <c r="G1184">
-        <f t="shared" si="16"/>
-        <v>12.935199999999998</v>
-      </c>
-    </row>
-    <row r="1185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
         <v>18</v>
       </c>
@@ -51731,12 +49602,8 @@
       <c r="F1185">
         <v>14.8748</v>
       </c>
-      <c r="G1185">
-        <f t="shared" si="16"/>
-        <v>14.8748</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
         <v>18</v>
       </c>
@@ -51752,15 +49619,8 @@
       <c r="F1186">
         <v>15.4224</v>
       </c>
-      <c r="G1186">
-        <f t="shared" si="16"/>
-        <v>15.4224</v>
-      </c>
-      <c r="H1186" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
         <v>18</v>
       </c>
@@ -51776,15 +49636,8 @@
       <c r="F1187">
         <v>16.8904</v>
       </c>
-      <c r="G1187">
-        <f t="shared" si="16"/>
-        <v>16.8904</v>
-      </c>
-      <c r="H1187" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
         <v>18</v>
       </c>
@@ -51800,12 +49653,8 @@
       <c r="F1188">
         <v>18.000899999999998</v>
       </c>
-      <c r="G1188">
-        <f t="shared" si="16"/>
-        <v>18.000899999999998</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
         <v>18</v>
       </c>
@@ -51821,12 +49670,8 @@
       <c r="F1189">
         <v>19.007199999999997</v>
       </c>
-      <c r="G1189">
-        <f t="shared" si="16"/>
-        <v>19.007199999999997</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
         <v>18</v>
       </c>
@@ -51842,12 +49687,8 @@
       <c r="F1190">
         <v>17.756799999999998</v>
       </c>
-      <c r="G1190">
-        <f t="shared" si="16"/>
-        <v>17.756799999999998</v>
-      </c>
-    </row>
-    <row r="1191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
         <v>18</v>
       </c>
@@ -51863,12 +49704,8 @@
       <c r="F1191">
         <v>17.963999999999999</v>
       </c>
-      <c r="G1191">
-        <f t="shared" si="16"/>
-        <v>17.963999999999999</v>
-      </c>
-    </row>
-    <row r="1192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
         <v>18</v>
       </c>
@@ -51884,12 +49721,8 @@
       <c r="F1192">
         <v>4.739300000000001</v>
       </c>
-      <c r="G1192">
-        <f t="shared" si="16"/>
-        <v>4.739300000000001</v>
-      </c>
-    </row>
-    <row r="1193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
         <v>18</v>
       </c>
@@ -51905,12 +49738,8 @@
       <c r="F1193">
         <v>8.3186999999999998</v>
       </c>
-      <c r="G1193">
-        <f t="shared" si="16"/>
-        <v>8.3186999999999998</v>
-      </c>
-    </row>
-    <row r="1194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
         <v>18</v>
       </c>
@@ -51926,12 +49755,8 @@
       <c r="F1194">
         <v>10.472000000000001</v>
       </c>
-      <c r="G1194">
-        <f t="shared" si="16"/>
-        <v>10.472000000000001</v>
-      </c>
-    </row>
-    <row r="1195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
         <v>18</v>
       </c>
@@ -51947,12 +49772,8 @@
       <c r="F1195">
         <v>12.465</v>
       </c>
-      <c r="G1195">
-        <f t="shared" si="16"/>
-        <v>12.465</v>
-      </c>
-    </row>
-    <row r="1196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
         <v>18</v>
       </c>
@@ -51968,12 +49789,8 @@
       <c r="F1196">
         <v>13.880699999999999</v>
       </c>
-      <c r="G1196">
-        <f t="shared" ref="G1196:G1224" si="17">F1196</f>
-        <v>13.880699999999999</v>
-      </c>
-    </row>
-    <row r="1197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
         <v>18</v>
       </c>
@@ -51989,15 +49806,8 @@
       <c r="F1197">
         <v>14.1158</v>
       </c>
-      <c r="G1197">
-        <f t="shared" si="17"/>
-        <v>14.1158</v>
-      </c>
-      <c r="H1197" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
         <v>18</v>
       </c>
@@ -52013,15 +49823,8 @@
       <c r="F1198">
         <v>14.5962</v>
       </c>
-      <c r="G1198">
-        <f t="shared" si="17"/>
-        <v>14.5962</v>
-      </c>
-      <c r="H1198" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
         <v>18</v>
       </c>
@@ -52037,12 +49840,8 @@
       <c r="F1199">
         <v>17.0487</v>
       </c>
-      <c r="G1199">
-        <f t="shared" si="17"/>
-        <v>17.0487</v>
-      </c>
-    </row>
-    <row r="1200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
         <v>18</v>
       </c>
@@ -52058,12 +49857,8 @@
       <c r="F1200">
         <v>17.490300000000001</v>
       </c>
-      <c r="G1200">
-        <f t="shared" si="17"/>
-        <v>17.490300000000001</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
         <v>18</v>
       </c>
@@ -52079,12 +49874,8 @@
       <c r="F1201">
         <v>17.7531</v>
       </c>
-      <c r="G1201">
-        <f t="shared" si="17"/>
-        <v>17.7531</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
         <v>18</v>
       </c>
@@ -52100,12 +49891,8 @@
       <c r="F1202">
         <v>17.337200000000003</v>
       </c>
-      <c r="G1202">
-        <f t="shared" si="17"/>
-        <v>17.337200000000003</v>
-      </c>
-    </row>
-    <row r="1203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
         <v>18</v>
       </c>
@@ -52121,12 +49908,8 @@
       <c r="F1203">
         <v>5.6027999999999993</v>
       </c>
-      <c r="G1203">
-        <f t="shared" si="17"/>
-        <v>5.6027999999999993</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
         <v>18</v>
       </c>
@@ -52142,12 +49925,8 @@
       <c r="F1204">
         <v>8.3005999999999993</v>
       </c>
-      <c r="G1204">
-        <f t="shared" si="17"/>
-        <v>8.3005999999999993</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
         <v>18</v>
       </c>
@@ -52163,12 +49942,8 @@
       <c r="F1205">
         <v>11.6775</v>
       </c>
-      <c r="G1205">
-        <f t="shared" si="17"/>
-        <v>11.6775</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
         <v>18</v>
       </c>
@@ -52184,12 +49959,8 @@
       <c r="F1206">
         <v>13.23</v>
       </c>
-      <c r="G1206">
-        <f t="shared" si="17"/>
-        <v>13.23</v>
-      </c>
-    </row>
-    <row r="1207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
         <v>18</v>
       </c>
@@ -52205,12 +49976,8 @@
       <c r="F1207">
         <v>15.4488</v>
       </c>
-      <c r="G1207">
-        <f t="shared" si="17"/>
-        <v>15.4488</v>
-      </c>
-    </row>
-    <row r="1208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
         <v>18</v>
       </c>
@@ -52226,15 +49993,8 @@
       <c r="F1208">
         <v>16.945499999999999</v>
       </c>
-      <c r="G1208">
-        <f t="shared" si="17"/>
-        <v>16.945499999999999</v>
-      </c>
-      <c r="H1208" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
         <v>18</v>
       </c>
@@ -52250,15 +50010,8 @@
       <c r="F1209">
         <v>16.8795</v>
       </c>
-      <c r="G1209">
-        <f t="shared" si="17"/>
-        <v>16.8795</v>
-      </c>
-      <c r="H1209" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
         <v>18</v>
       </c>
@@ -52274,12 +50027,8 @@
       <c r="F1210">
         <v>17.455200000000001</v>
       </c>
-      <c r="G1210">
-        <f t="shared" si="17"/>
-        <v>17.455200000000001</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
         <v>18</v>
       </c>
@@ -52295,12 +50044,8 @@
       <c r="F1211">
         <v>17.835600000000003</v>
       </c>
-      <c r="G1211">
-        <f t="shared" si="17"/>
-        <v>17.835600000000003</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
         <v>18</v>
       </c>
@@ -52316,12 +50061,8 @@
       <c r="F1212">
         <v>15.45</v>
       </c>
-      <c r="G1212">
-        <f t="shared" si="17"/>
-        <v>15.45</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
         <v>18</v>
       </c>
@@ -52337,12 +50078,8 @@
       <c r="F1213">
         <v>17.71</v>
       </c>
-      <c r="G1213">
-        <f t="shared" si="17"/>
-        <v>17.71</v>
-      </c>
-    </row>
-    <row r="1214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
         <v>23</v>
       </c>
@@ -52358,12 +50095,8 @@
       <c r="F1214">
         <v>6.6825000000000001</v>
       </c>
-      <c r="G1214">
-        <f t="shared" si="17"/>
-        <v>6.6825000000000001</v>
-      </c>
-    </row>
-    <row r="1215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
         <v>23</v>
       </c>
@@ -52379,12 +50112,8 @@
       <c r="F1215">
         <v>10.244200000000001</v>
       </c>
-      <c r="G1215">
-        <f t="shared" si="17"/>
-        <v>10.244200000000001</v>
-      </c>
-    </row>
-    <row r="1216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
         <v>23</v>
       </c>
@@ -52398,10 +50127,6 @@
         <v>9</v>
       </c>
       <c r="F1216">
-        <v>12.918300000000002</v>
-      </c>
-      <c r="G1216">
-        <f t="shared" si="17"/>
         <v>12.918300000000002</v>
       </c>
     </row>
@@ -52421,10 +50146,6 @@
       <c r="F1217">
         <v>14.815999999999999</v>
       </c>
-      <c r="G1217">
-        <f t="shared" si="17"/>
-        <v>14.815999999999999</v>
-      </c>
     </row>
     <row r="1218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
@@ -52442,10 +50163,6 @@
       <c r="F1218">
         <v>16.666599999999999</v>
       </c>
-      <c r="G1218">
-        <f t="shared" si="17"/>
-        <v>16.666599999999999</v>
-      </c>
     </row>
     <row r="1219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
@@ -52463,10 +50180,6 @@
       <c r="F1219">
         <v>17.594999999999999</v>
       </c>
-      <c r="G1219">
-        <f t="shared" si="17"/>
-        <v>17.594999999999999</v>
-      </c>
     </row>
     <row r="1220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
@@ -52485,8 +50198,7 @@
         <v>19.6874</v>
       </c>
       <c r="G1220">
-        <f t="shared" si="17"/>
-        <v>19.6874</v>
+        <v>17.62</v>
       </c>
       <c r="H1220" t="s">
         <v>27</v>
@@ -52508,13 +50220,6 @@
       <c r="F1221">
         <v>15.558299999999999</v>
       </c>
-      <c r="G1221">
-        <f t="shared" si="17"/>
-        <v>15.558299999999999</v>
-      </c>
-      <c r="H1221" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
@@ -52532,10 +50237,6 @@
       <c r="F1222">
         <v>18.902399999999997</v>
       </c>
-      <c r="G1222">
-        <f t="shared" si="17"/>
-        <v>18.902399999999997</v>
-      </c>
     </row>
     <row r="1223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
@@ -52553,10 +50254,6 @@
       <c r="F1223">
         <v>17.7288</v>
       </c>
-      <c r="G1223">
-        <f t="shared" si="17"/>
-        <v>17.7288</v>
-      </c>
     </row>
     <row r="1224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
@@ -52572,10 +50269,6 @@
         <v>9</v>
       </c>
       <c r="F1224">
-        <v>18.723399999999998</v>
-      </c>
-      <c r="G1224">
-        <f t="shared" si="17"/>
         <v>18.723399999999998</v>
       </c>
     </row>
@@ -52583,7 +50276,7 @@
   <autoFilter ref="A1:A1224" xr:uid="{3C95387D-0458-4499-B052-84055CDD2D26}">
     <filterColumn colId="0">
       <filters>
-        <filter val="TPHW2020"/>
+        <filter val="TPHW2024"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -94530,7 +92223,7 @@
         <v>86.7</v>
       </c>
       <c r="I604" s="4">
-        <f t="shared" ref="I602:I612" si="20" xml:space="preserve"> DATEDIF(DATE(YEAR(M604),1,0),M604,"d")+1</f>
+        <f t="shared" ref="I604:I612" si="20" xml:space="preserve"> DATEDIF(DATE(YEAR(M604),1,0),M604,"d")+1</f>
         <v>327</v>
       </c>
       <c r="J604">

--- a/Prototypes/KiwiFruit/Yield.xlsx
+++ b/Prototypes/KiwiFruit/Yield.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1F05B7-EB18-4243-8EB8-4B8557381F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583BCCF3-6030-4013-9903-3D49400B045A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SingleBerryFW" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8780" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8718" uniqueCount="33">
   <si>
     <t>SimulationName</t>
   </si>
@@ -11486,7 +11486,7 @@
       </c>
     </row>
     <row r="613" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>10</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>10</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>10</v>
       </c>
@@ -11570,7 +11570,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>10</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>10</v>
       </c>
@@ -11626,7 +11626,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>10</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>10</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>10</v>
       </c>
@@ -11710,7 +11710,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>10</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>10</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>10</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>10</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>10</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>10</v>
       </c>
@@ -11878,7 +11878,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>10</v>
       </c>
@@ -11906,7 +11906,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>10</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>10</v>
       </c>
@@ -11951,8 +11951,7 @@
         <v>105.7</v>
       </c>
       <c r="G630">
-        <f t="shared" si="9"/>
-        <v>105.7</v>
+        <v>113.07</v>
       </c>
       <c r="H630" t="s">
         <v>27</v>
@@ -11965,7 +11964,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>10</v>
       </c>
@@ -11985,9 +11984,6 @@
         <f t="shared" si="9"/>
         <v>122.2</v>
       </c>
-      <c r="H631" t="s">
-        <v>27</v>
-      </c>
       <c r="I631" s="5">
         <f t="shared" si="10"/>
         <v>327</v>
@@ -11996,7 +11992,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>10</v>
       </c>
@@ -12024,7 +12020,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>10</v>
       </c>
@@ -12052,7 +12048,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>10</v>
       </c>
@@ -12080,7 +12076,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>10</v>
       </c>
@@ -12108,7 +12104,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>10</v>
       </c>
@@ -12136,7 +12132,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>10</v>
       </c>
@@ -12164,7 +12160,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>10</v>
       </c>
@@ -12192,7 +12188,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>10</v>
       </c>
@@ -12220,7 +12216,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>10</v>
       </c>
@@ -12248,7 +12244,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>10</v>
       </c>
@@ -12276,7 +12272,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>10</v>
       </c>
@@ -12304,7 +12300,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>10</v>
       </c>
@@ -12332,7 +12328,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>10</v>
       </c>
@@ -12360,7 +12356,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>10</v>
       </c>
@@ -12388,7 +12384,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>10</v>
       </c>
@@ -12408,9 +12404,6 @@
         <f t="shared" si="9"/>
         <v>115.6</v>
       </c>
-      <c r="H646" t="s">
-        <v>27</v>
-      </c>
       <c r="I646" s="5">
         <f t="shared" si="10"/>
         <v>331</v>
@@ -12419,7 +12412,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>10</v>
       </c>
@@ -12447,7 +12440,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>10</v>
       </c>
@@ -12475,7 +12468,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>10</v>
       </c>
@@ -12503,7 +12496,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>10</v>
       </c>
@@ -12531,7 +12524,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>10</v>
       </c>
@@ -12559,7 +12552,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>10</v>
       </c>
@@ -12587,7 +12580,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>10</v>
       </c>
@@ -12615,7 +12608,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>10</v>
       </c>
@@ -12643,7 +12636,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>10</v>
       </c>
@@ -12671,7 +12664,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>10</v>
       </c>
@@ -12699,7 +12692,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>10</v>
       </c>
@@ -12727,7 +12720,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>10</v>
       </c>
@@ -12755,7 +12748,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>10</v>
       </c>
@@ -12783,7 +12776,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>10</v>
       </c>
@@ -12811,7 +12804,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>10</v>
       </c>
@@ -12839,7 +12832,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>10</v>
       </c>
@@ -12867,7 +12860,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>10</v>
       </c>
@@ -12895,7 +12888,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>10</v>
       </c>
@@ -12923,7 +12916,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>10</v>
       </c>
@@ -12951,7 +12944,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>10</v>
       </c>
@@ -12979,7 +12972,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>10</v>
       </c>
@@ -13007,7 +13000,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>10</v>
       </c>
@@ -13035,7 +13028,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>10</v>
       </c>
@@ -13063,7 +13056,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>10</v>
       </c>
@@ -13091,7 +13084,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>10</v>
       </c>
@@ -13119,7 +13112,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>10</v>
       </c>
@@ -13147,7 +13140,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>10</v>
       </c>
@@ -13175,7 +13168,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>10</v>
       </c>
@@ -13203,7 +13196,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>10</v>
       </c>
@@ -13231,7 +13224,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>10</v>
       </c>
@@ -13259,7 +13252,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>10</v>
       </c>
@@ -13287,7 +13280,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>10</v>
       </c>
@@ -13315,7 +13308,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>10</v>
       </c>
@@ -13343,7 +13336,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>10</v>
       </c>
@@ -13371,7 +13364,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>10</v>
       </c>
@@ -13399,7 +13392,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>10</v>
       </c>
@@ -13419,9 +13412,6 @@
         <f t="shared" si="11"/>
         <v>108.8</v>
       </c>
-      <c r="H682" t="s">
-        <v>27</v>
-      </c>
       <c r="I682" s="5">
         <f t="shared" si="12"/>
         <v>336</v>
@@ -13430,7 +13420,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>10</v>
       </c>
@@ -13458,7 +13448,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>10</v>
       </c>
@@ -13486,7 +13476,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>10</v>
       </c>
@@ -13514,7 +13504,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>10</v>
       </c>
@@ -13542,7 +13532,7 @@
         <v>42333</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>10</v>
       </c>
@@ -13570,7 +13560,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>10</v>
       </c>
@@ -13598,7 +13588,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>10</v>
       </c>
@@ -13626,7 +13616,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>10</v>
       </c>
@@ -13654,7 +13644,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>10</v>
       </c>
@@ -13682,7 +13672,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>10</v>
       </c>
@@ -13710,7 +13700,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>10</v>
       </c>
@@ -13738,7 +13728,7 @@
         <v>42330</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>10</v>
       </c>
@@ -13766,7 +13756,7 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>10</v>
       </c>
@@ -13794,7 +13784,7 @@
         <v>42334</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>10</v>
       </c>
@@ -13822,7 +13812,7 @@
         <v>42336</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>11</v>
       </c>
@@ -13850,7 +13840,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>11</v>
       </c>
@@ -13878,7 +13868,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>11</v>
       </c>
@@ -13906,7 +13896,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>11</v>
       </c>
@@ -13934,7 +13924,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>11</v>
       </c>
@@ -13962,7 +13952,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>11</v>
       </c>
@@ -13990,7 +13980,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>11</v>
       </c>
@@ -14018,7 +14008,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>11</v>
       </c>
@@ -14046,7 +14036,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>11</v>
       </c>
@@ -14074,7 +14064,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>11</v>
       </c>
@@ -14102,7 +14092,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>11</v>
       </c>
@@ -14130,7 +14120,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>11</v>
       </c>
@@ -14158,7 +14148,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>11</v>
       </c>
@@ -14186,7 +14176,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>11</v>
       </c>
@@ -14214,7 +14204,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>11</v>
       </c>
@@ -14242,7 +14232,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>11</v>
       </c>
@@ -14270,7 +14260,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>11</v>
       </c>
@@ -14287,8 +14277,7 @@
         <v>120.5</v>
       </c>
       <c r="G713">
-        <f t="shared" si="11"/>
-        <v>120.5</v>
+        <v>123.32</v>
       </c>
       <c r="H713" t="s">
         <v>27</v>
@@ -14301,7 +14290,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>11</v>
       </c>
@@ -14321,9 +14310,6 @@
         <f t="shared" si="11"/>
         <v>109.1</v>
       </c>
-      <c r="H714" t="s">
-        <v>27</v>
-      </c>
       <c r="I714" s="5">
         <f t="shared" si="12"/>
         <v>325</v>
@@ -14332,7 +14318,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>11</v>
       </c>
@@ -14360,7 +14346,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>11</v>
       </c>
@@ -14388,7 +14374,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>11</v>
       </c>
@@ -14416,7 +14402,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>11</v>
       </c>
@@ -14444,7 +14430,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>11</v>
       </c>
@@ -14472,7 +14458,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>11</v>
       </c>
@@ -14500,7 +14486,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>11</v>
       </c>
@@ -14528,7 +14514,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>11</v>
       </c>
@@ -14556,7 +14542,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>11</v>
       </c>
@@ -14584,7 +14570,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>11</v>
       </c>
@@ -14612,7 +14598,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>11</v>
       </c>
@@ -14640,7 +14626,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>11</v>
       </c>
@@ -14668,7 +14654,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>11</v>
       </c>
@@ -14696,7 +14682,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>11</v>
       </c>
@@ -14724,7 +14710,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>11</v>
       </c>
@@ -14752,7 +14738,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>11</v>
       </c>
@@ -14780,7 +14766,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>11</v>
       </c>
@@ -14800,9 +14786,6 @@
         <f t="shared" si="11"/>
         <v>131.9</v>
       </c>
-      <c r="H731" t="s">
-        <v>27</v>
-      </c>
       <c r="I731" s="5">
         <f t="shared" si="12"/>
         <v>333</v>
@@ -14811,7 +14794,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>11</v>
       </c>
@@ -14839,7 +14822,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>11</v>
       </c>
@@ -14867,7 +14850,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>11</v>
       </c>
@@ -14895,7 +14878,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>11</v>
       </c>
@@ -14923,7 +14906,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>11</v>
       </c>
@@ -14951,7 +14934,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>11</v>
       </c>
@@ -14979,7 +14962,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>11</v>
       </c>
@@ -15007,7 +14990,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>11</v>
       </c>
@@ -15035,7 +15018,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>11</v>
       </c>
@@ -15063,7 +15046,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>11</v>
       </c>
@@ -15091,7 +15074,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>11</v>
       </c>
@@ -15119,7 +15102,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>11</v>
       </c>
@@ -15147,7 +15130,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>11</v>
       </c>
@@ -15175,7 +15158,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>11</v>
       </c>
@@ -15203,7 +15186,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>11</v>
       </c>
@@ -15231,7 +15214,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>11</v>
       </c>
@@ -15259,7 +15242,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>11</v>
       </c>
@@ -15287,7 +15270,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>11</v>
       </c>
@@ -15315,7 +15298,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>11</v>
       </c>
@@ -15343,7 +15326,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>11</v>
       </c>
@@ -15371,7 +15354,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>11</v>
       </c>
@@ -15399,7 +15382,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>11</v>
       </c>
@@ -15427,7 +15410,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>11</v>
       </c>
@@ -15455,7 +15438,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>11</v>
       </c>
@@ -15483,7 +15466,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>11</v>
       </c>
@@ -15511,7 +15494,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>11</v>
       </c>
@@ -15539,7 +15522,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>11</v>
       </c>
@@ -15567,7 +15550,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>11</v>
       </c>
@@ -15595,7 +15578,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>11</v>
       </c>
@@ -15623,7 +15606,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>11</v>
       </c>
@@ -15651,7 +15634,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>11</v>
       </c>
@@ -15679,7 +15662,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>11</v>
       </c>
@@ -15707,7 +15690,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>11</v>
       </c>
@@ -15735,7 +15718,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>11</v>
       </c>
@@ -15763,7 +15746,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>11</v>
       </c>
@@ -15791,7 +15774,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>11</v>
       </c>
@@ -15819,7 +15802,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>11</v>
       </c>
@@ -15839,9 +15822,6 @@
         <f t="shared" si="13"/>
         <v>135.9</v>
       </c>
-      <c r="H768" t="s">
-        <v>27</v>
-      </c>
       <c r="I768" s="5">
         <f t="shared" si="14"/>
         <v>340</v>
@@ -15850,7 +15830,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>11</v>
       </c>
@@ -15870,9 +15850,6 @@
         <f t="shared" si="13"/>
         <v>128.4</v>
       </c>
-      <c r="H769" t="s">
-        <v>27</v>
-      </c>
       <c r="I769" s="5">
         <f t="shared" si="14"/>
         <v>325</v>
@@ -15881,7 +15858,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>11</v>
       </c>
@@ -15901,9 +15878,6 @@
         <f t="shared" si="13"/>
         <v>116</v>
       </c>
-      <c r="H770" t="s">
-        <v>27</v>
-      </c>
       <c r="I770" s="5">
         <f t="shared" si="14"/>
         <v>324</v>
@@ -15912,7 +15886,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>11</v>
       </c>
@@ -15932,9 +15906,6 @@
         <f t="shared" si="13"/>
         <v>121.5</v>
       </c>
-      <c r="H771" t="s">
-        <v>27</v>
-      </c>
       <c r="I771" s="5">
         <f t="shared" si="14"/>
         <v>328</v>
@@ -15943,7 +15914,7 @@
         <v>42696</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>11</v>
       </c>
@@ -15971,7 +15942,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>11</v>
       </c>
@@ -15999,7 +15970,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>11</v>
       </c>
@@ -16027,7 +15998,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>11</v>
       </c>
@@ -16055,7 +16026,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>11</v>
       </c>
@@ -16083,7 +16054,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>11</v>
       </c>
@@ -16111,7 +16082,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>11</v>
       </c>
@@ -16139,7 +16110,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>11</v>
       </c>
@@ -16167,7 +16138,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="780" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>11</v>
       </c>
@@ -16195,7 +16166,7 @@
         <v>42698</v>
       </c>
     </row>
-    <row r="781" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>11</v>
       </c>
@@ -16223,7 +16194,7 @@
         <v>42692</v>
       </c>
     </row>
-    <row r="782" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>11</v>
       </c>
@@ -16251,7 +16222,7 @@
         <v>42708</v>
       </c>
     </row>
-    <row r="783" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>11</v>
       </c>
@@ -16279,7 +16250,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="784" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>11</v>
       </c>
@@ -16307,7 +16278,7 @@
         <v>42701</v>
       </c>
     </row>
-    <row r="785" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>11</v>
       </c>
@@ -16335,7 +16306,7 @@
         <v>42693</v>
       </c>
     </row>
-    <row r="786" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>12</v>
       </c>
@@ -16363,7 +16334,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="787" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>12</v>
       </c>
@@ -16391,7 +16362,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="788" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>12</v>
       </c>
@@ -16419,7 +16390,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="789" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>12</v>
       </c>
@@ -16447,7 +16418,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="790" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>12</v>
       </c>
@@ -16475,7 +16446,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="791" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>12</v>
       </c>
@@ -16503,7 +16474,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="792" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>12</v>
       </c>
@@ -16531,7 +16502,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="793" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>12</v>
       </c>
@@ -16559,7 +16530,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="794" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>12</v>
       </c>
@@ -16587,7 +16558,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="795" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>12</v>
       </c>
@@ -16615,7 +16586,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="796" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>12</v>
       </c>
@@ -16643,7 +16614,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="797" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>12</v>
       </c>
@@ -16671,7 +16642,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="798" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>12</v>
       </c>
@@ -16699,7 +16670,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="799" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>12</v>
       </c>
@@ -16727,7 +16698,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="800" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>12</v>
       </c>
@@ -16755,7 +16726,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="801" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>12</v>
       </c>
@@ -16783,7 +16754,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="802" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>12</v>
       </c>
@@ -16800,8 +16771,7 @@
         <v>117.6</v>
       </c>
       <c r="G802">
-        <f t="shared" si="13"/>
-        <v>117.6</v>
+        <v>115.24</v>
       </c>
       <c r="H802" t="s">
         <v>27</v>
@@ -16814,7 +16784,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="803" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>12</v>
       </c>
@@ -16834,9 +16804,6 @@
         <f t="shared" si="13"/>
         <v>109</v>
       </c>
-      <c r="H803" t="s">
-        <v>27</v>
-      </c>
       <c r="I803" s="5">
         <f t="shared" si="14"/>
         <v>327</v>
@@ -16845,7 +16812,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="804" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>12</v>
       </c>
@@ -16873,7 +16840,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="805" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>12</v>
       </c>
@@ -16901,7 +16868,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="806" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>12</v>
       </c>
@@ -16929,7 +16896,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="807" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>12</v>
       </c>
@@ -16957,7 +16924,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="808" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>12</v>
       </c>
@@ -16985,7 +16952,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="809" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>12</v>
       </c>
@@ -17013,7 +16980,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="810" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>12</v>
       </c>
@@ -17041,7 +17008,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="811" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>12</v>
       </c>
@@ -17069,7 +17036,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="812" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>12</v>
       </c>
@@ -17097,7 +17064,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="813" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>12</v>
       </c>
@@ -17125,7 +17092,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="814" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>12</v>
       </c>
@@ -17153,7 +17120,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="815" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>12</v>
       </c>
@@ -17181,7 +17148,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="816" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>12</v>
       </c>
@@ -17201,9 +17168,6 @@
         <f t="shared" si="15"/>
         <v>116.3</v>
       </c>
-      <c r="H816" t="s">
-        <v>27</v>
-      </c>
       <c r="I816" s="5">
         <f t="shared" si="16"/>
         <v>326</v>
@@ -17212,7 +17176,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="817" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>12</v>
       </c>
@@ -17240,7 +17204,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="818" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>12</v>
       </c>
@@ -17268,7 +17232,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="819" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>12</v>
       </c>
@@ -17296,7 +17260,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="820" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>12</v>
       </c>
@@ -17324,7 +17288,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="821" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>12</v>
       </c>
@@ -17352,7 +17316,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="822" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>12</v>
       </c>
@@ -17380,7 +17344,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="823" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>12</v>
       </c>
@@ -17408,7 +17372,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="824" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>12</v>
       </c>
@@ -17436,7 +17400,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="825" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>12</v>
       </c>
@@ -17464,7 +17428,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="826" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>12</v>
       </c>
@@ -17492,7 +17456,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="827" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>12</v>
       </c>
@@ -17520,7 +17484,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="828" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>12</v>
       </c>
@@ -17548,7 +17512,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="829" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>12</v>
       </c>
@@ -17576,7 +17540,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="830" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>12</v>
       </c>
@@ -17604,7 +17568,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="831" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>12</v>
       </c>
@@ -17632,7 +17596,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="832" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>12</v>
       </c>
@@ -17660,7 +17624,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="833" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>12</v>
       </c>
@@ -17688,7 +17652,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="834" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>12</v>
       </c>
@@ -17716,7 +17680,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="835" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>12</v>
       </c>
@@ -17744,7 +17708,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="836" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>12</v>
       </c>
@@ -17772,7 +17736,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="837" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>12</v>
       </c>
@@ -17800,7 +17764,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="838" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>12</v>
       </c>
@@ -17828,7 +17792,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="839" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>12</v>
       </c>
@@ -17856,7 +17820,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="840" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>12</v>
       </c>
@@ -17884,7 +17848,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="841" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>12</v>
       </c>
@@ -17912,7 +17876,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="842" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>12</v>
       </c>
@@ -17940,7 +17904,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="843" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>12</v>
       </c>
@@ -17968,7 +17932,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="844" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>12</v>
       </c>
@@ -17996,7 +17960,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="845" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>12</v>
       </c>
@@ -18024,7 +17988,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="846" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>12</v>
       </c>
@@ -18052,7 +18016,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="847" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>12</v>
       </c>
@@ -18080,7 +18044,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="848" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>12</v>
       </c>
@@ -18108,7 +18072,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="849" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>12</v>
       </c>
@@ -18136,7 +18100,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="850" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>12</v>
       </c>
@@ -18164,7 +18128,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="851" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>12</v>
       </c>
@@ -18184,9 +18148,6 @@
         <f t="shared" si="15"/>
         <v>109.9</v>
       </c>
-      <c r="H851" t="s">
-        <v>27</v>
-      </c>
       <c r="I851" s="5">
         <f t="shared" si="16"/>
         <v>331</v>
@@ -18195,7 +18156,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="852" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>12</v>
       </c>
@@ -18215,9 +18176,6 @@
         <f t="shared" si="15"/>
         <v>114.4</v>
       </c>
-      <c r="H852" t="s">
-        <v>27</v>
-      </c>
       <c r="I852" s="5">
         <f t="shared" si="16"/>
         <v>327</v>
@@ -18226,7 +18184,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="853" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>12</v>
       </c>
@@ -18246,9 +18204,6 @@
         <f t="shared" si="15"/>
         <v>118.9</v>
       </c>
-      <c r="H853" t="s">
-        <v>27</v>
-      </c>
       <c r="I853" s="5">
         <f t="shared" si="16"/>
         <v>336</v>
@@ -18257,7 +18212,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="854" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>12</v>
       </c>
@@ -18277,9 +18232,6 @@
         <f t="shared" si="15"/>
         <v>120.6</v>
       </c>
-      <c r="H854" t="s">
-        <v>27</v>
-      </c>
       <c r="I854" s="5">
         <f t="shared" si="16"/>
         <v>330</v>
@@ -18288,7 +18240,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="855" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>12</v>
       </c>
@@ -18316,7 +18268,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="856" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>12</v>
       </c>
@@ -18344,7 +18296,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="857" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>12</v>
       </c>
@@ -18372,7 +18324,7 @@
         <v>43060</v>
       </c>
     </row>
-    <row r="858" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>12</v>
       </c>
@@ -18400,7 +18352,7 @@
         <v>43065</v>
       </c>
     </row>
-    <row r="859" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>12</v>
       </c>
@@ -18428,7 +18380,7 @@
         <v>43061</v>
       </c>
     </row>
-    <row r="860" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>12</v>
       </c>
@@ -18456,7 +18408,7 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="861" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>12</v>
       </c>
@@ -18484,7 +18436,7 @@
         <v>43064</v>
       </c>
     </row>
-    <row r="862" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>12</v>
       </c>
@@ -18512,7 +18464,7 @@
         <v>43068</v>
       </c>
     </row>
-    <row r="863" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>13</v>
       </c>
@@ -18540,7 +18492,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="864" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>13</v>
       </c>
@@ -18568,7 +18520,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="865" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>13</v>
       </c>
@@ -18596,7 +18548,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="866" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>13</v>
       </c>
@@ -18624,7 +18576,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="867" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>13</v>
       </c>
@@ -18652,7 +18604,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="868" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>13</v>
       </c>
@@ -18680,7 +18632,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="869" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>13</v>
       </c>
@@ -18708,7 +18660,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="870" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>13</v>
       </c>
@@ -18725,8 +18677,7 @@
         <v>100.3</v>
       </c>
       <c r="G870">
-        <f t="shared" si="15"/>
-        <v>100.3</v>
+        <v>99.14</v>
       </c>
       <c r="H870" t="s">
         <v>27</v>
@@ -18739,7 +18690,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="871" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>13</v>
       </c>
@@ -18759,9 +18710,6 @@
         <f t="shared" ref="G871:G934" si="17">F871</f>
         <v>93.8</v>
       </c>
-      <c r="H871" t="s">
-        <v>27</v>
-      </c>
       <c r="I871" s="5">
         <f t="shared" ref="I871:I934" si="18" xml:space="preserve"> DATEDIF(DATE(YEAR(M871),1,0),M871,"d")+1</f>
         <v>325</v>
@@ -18770,7 +18718,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="872" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>13</v>
       </c>
@@ -18798,7 +18746,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="873" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>13</v>
       </c>
@@ -18826,7 +18774,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="874" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>13</v>
       </c>
@@ -18854,7 +18802,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="875" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>13</v>
       </c>
@@ -18882,7 +18830,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="876" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>13</v>
       </c>
@@ -18910,7 +18858,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="877" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>13</v>
       </c>
@@ -18938,7 +18886,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="878" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>13</v>
       </c>
@@ -18966,7 +18914,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="879" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>13</v>
       </c>
@@ -18994,7 +18942,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="880" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>13</v>
       </c>
@@ -19014,9 +18962,6 @@
         <f t="shared" si="17"/>
         <v>105.2</v>
       </c>
-      <c r="H880" t="s">
-        <v>27</v>
-      </c>
       <c r="I880" s="5">
         <f t="shared" si="18"/>
         <v>331</v>
@@ -19025,7 +18970,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="881" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>13</v>
       </c>
@@ -19045,9 +18990,6 @@
         <f t="shared" si="17"/>
         <v>93.4</v>
       </c>
-      <c r="H881" t="s">
-        <v>27</v>
-      </c>
       <c r="I881" s="5">
         <f t="shared" si="18"/>
         <v>325</v>
@@ -19056,7 +18998,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="882" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>13</v>
       </c>
@@ -19084,7 +19026,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="883" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>13</v>
       </c>
@@ -19112,7 +19054,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="884" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>13</v>
       </c>
@@ -19140,7 +19082,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="885" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>13</v>
       </c>
@@ -19168,7 +19110,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="886" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>13</v>
       </c>
@@ -19196,7 +19138,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="887" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>13</v>
       </c>
@@ -19224,7 +19166,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="888" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>13</v>
       </c>
@@ -19252,7 +19194,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="889" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>13</v>
       </c>
@@ -19280,7 +19222,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="890" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>13</v>
       </c>
@@ -19308,7 +19250,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="891" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>13</v>
       </c>
@@ -19336,7 +19278,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="892" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>13</v>
       </c>
@@ -19364,7 +19306,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="893" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>13</v>
       </c>
@@ -19392,7 +19334,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="894" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>13</v>
       </c>
@@ -19420,7 +19362,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="895" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>13</v>
       </c>
@@ -19448,7 +19390,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="896" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>13</v>
       </c>
@@ -19476,7 +19418,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="897" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>13</v>
       </c>
@@ -19504,7 +19446,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="898" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>13</v>
       </c>
@@ -19532,7 +19474,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="899" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>13</v>
       </c>
@@ -19560,7 +19502,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="900" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>13</v>
       </c>
@@ -19588,7 +19530,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="901" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>13</v>
       </c>
@@ -19616,7 +19558,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="902" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>13</v>
       </c>
@@ -19644,7 +19586,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="903" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>13</v>
       </c>
@@ -19672,7 +19614,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="904" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>13</v>
       </c>
@@ -19700,7 +19642,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="905" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>13</v>
       </c>
@@ -19728,7 +19670,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="906" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>13</v>
       </c>
@@ -19756,7 +19698,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="907" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>13</v>
       </c>
@@ -19784,7 +19726,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="908" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>13</v>
       </c>
@@ -19812,7 +19754,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="909" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>13</v>
       </c>
@@ -19832,9 +19774,6 @@
         <f t="shared" si="17"/>
         <v>102.6</v>
       </c>
-      <c r="H909" t="s">
-        <v>27</v>
-      </c>
       <c r="I909" s="5">
         <f t="shared" si="18"/>
         <v>325</v>
@@ -19843,7 +19782,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="910" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>13</v>
       </c>
@@ -19863,9 +19802,6 @@
         <f t="shared" si="17"/>
         <v>110.5</v>
       </c>
-      <c r="H910" t="s">
-        <v>27</v>
-      </c>
       <c r="I910" s="5">
         <f t="shared" si="18"/>
         <v>324</v>
@@ -19874,7 +19810,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="911" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>13</v>
       </c>
@@ -19894,9 +19830,6 @@
         <f t="shared" si="17"/>
         <v>108.9</v>
       </c>
-      <c r="H911" t="s">
-        <v>27</v>
-      </c>
       <c r="I911" s="5">
         <f t="shared" si="18"/>
         <v>329</v>
@@ -19905,7 +19838,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="912" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>13</v>
       </c>
@@ -19925,9 +19858,6 @@
         <f t="shared" si="17"/>
         <v>95</v>
       </c>
-      <c r="H912" t="s">
-        <v>27</v>
-      </c>
       <c r="I912" s="5">
         <f t="shared" si="18"/>
         <v>333</v>
@@ -19936,7 +19866,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="913" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>13</v>
       </c>
@@ -19956,9 +19886,6 @@
         <f t="shared" si="17"/>
         <v>93.8</v>
       </c>
-      <c r="H913" t="s">
-        <v>27</v>
-      </c>
       <c r="I913" s="5">
         <f t="shared" si="18"/>
         <v>325</v>
@@ -19967,7 +19894,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="914" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>13</v>
       </c>
@@ -19987,9 +19914,6 @@
         <f t="shared" si="17"/>
         <v>98.5</v>
       </c>
-      <c r="H914" t="s">
-        <v>27</v>
-      </c>
       <c r="I914" s="5">
         <f t="shared" si="18"/>
         <v>331</v>
@@ -19998,7 +19922,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="915" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>13</v>
       </c>
@@ -20018,9 +19942,6 @@
         <f t="shared" si="17"/>
         <v>102.3</v>
       </c>
-      <c r="H915" t="s">
-        <v>27</v>
-      </c>
       <c r="I915" s="5">
         <f t="shared" si="18"/>
         <v>325</v>
@@ -20029,7 +19950,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="916" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>13</v>
       </c>
@@ -20049,9 +19970,6 @@
         <f t="shared" si="17"/>
         <v>85.4</v>
       </c>
-      <c r="H916" t="s">
-        <v>27</v>
-      </c>
       <c r="I916" s="5">
         <f t="shared" si="18"/>
         <v>324</v>
@@ -20060,7 +19978,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="917" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>13</v>
       </c>
@@ -20088,7 +20006,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="918" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>13</v>
       </c>
@@ -20116,7 +20034,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="919" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>13</v>
       </c>
@@ -20144,7 +20062,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="920" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>13</v>
       </c>
@@ -20172,7 +20090,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="921" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>14</v>
       </c>
@@ -20200,7 +20118,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="922" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>14</v>
       </c>
@@ -20228,7 +20146,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="923" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>14</v>
       </c>
@@ -20256,7 +20174,7 @@
         <v>43424</v>
       </c>
     </row>
-    <row r="924" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>14</v>
       </c>
@@ -20284,7 +20202,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="925" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>14</v>
       </c>
@@ -20301,8 +20219,7 @@
         <v>104.6</v>
       </c>
       <c r="G925">
-        <f t="shared" si="17"/>
-        <v>104.6</v>
+        <v>108.38</v>
       </c>
       <c r="H925" t="s">
         <v>27</v>
@@ -20315,7 +20232,7 @@
         <v>43428</v>
       </c>
     </row>
-    <row r="926" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>14</v>
       </c>
@@ -20343,7 +20260,7 @@
         <v>43432</v>
       </c>
     </row>
-    <row r="927" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>14</v>
       </c>
@@ -20371,7 +20288,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="928" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>14</v>
       </c>
@@ -20399,7 +20316,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="929" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>14</v>
       </c>
@@ -20427,7 +20344,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="930" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>14</v>
       </c>
@@ -20455,7 +20372,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="931" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>14</v>
       </c>
@@ -20483,7 +20400,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="932" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>14</v>
       </c>
@@ -20503,9 +20420,6 @@
         <f t="shared" si="17"/>
         <v>108</v>
       </c>
-      <c r="H932" t="s">
-        <v>27</v>
-      </c>
       <c r="I932" s="5">
         <f t="shared" si="18"/>
         <v>328</v>
@@ -20514,7 +20428,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="933" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>14</v>
       </c>
@@ -20542,7 +20456,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="934" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>14</v>
       </c>
@@ -20570,7 +20484,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="935" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>14</v>
       </c>
@@ -20598,7 +20512,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="936" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>14</v>
       </c>
@@ -20626,7 +20540,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="937" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>14</v>
       </c>
@@ -20654,7 +20568,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="938" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>14</v>
       </c>
@@ -20682,7 +20596,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="939" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>14</v>
       </c>
@@ -20710,7 +20624,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="940" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>14</v>
       </c>
@@ -20738,7 +20652,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="941" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>14</v>
       </c>
@@ -20766,7 +20680,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="942" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>14</v>
       </c>
@@ -20794,7 +20708,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="943" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>14</v>
       </c>
@@ -20822,7 +20736,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="944" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>14</v>
       </c>
@@ -20850,7 +20764,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="945" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>14</v>
       </c>
@@ -20878,7 +20792,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="946" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>14</v>
       </c>
@@ -20906,7 +20820,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="947" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>14</v>
       </c>
@@ -20926,9 +20840,6 @@
         <f t="shared" si="19"/>
         <v>94.6</v>
       </c>
-      <c r="H947" t="s">
-        <v>27</v>
-      </c>
       <c r="I947" s="5">
         <f t="shared" si="20"/>
         <v>328</v>
@@ -20937,7 +20848,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="948" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>14</v>
       </c>
@@ -20957,9 +20868,6 @@
         <f t="shared" si="19"/>
         <v>121.5</v>
       </c>
-      <c r="H948" t="s">
-        <v>27</v>
-      </c>
       <c r="I948" s="5">
         <f t="shared" si="20"/>
         <v>328</v>
@@ -20968,7 +20876,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="949" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>14</v>
       </c>
@@ -20988,9 +20896,6 @@
         <f t="shared" si="19"/>
         <v>113.2</v>
       </c>
-      <c r="H949" t="s">
-        <v>27</v>
-      </c>
       <c r="I949" s="5">
         <f t="shared" si="20"/>
         <v>328</v>
@@ -20999,7 +20904,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="950" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>14</v>
       </c>
@@ -21027,7 +20932,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="951" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>14</v>
       </c>
@@ -21055,7 +20960,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="952" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>14</v>
       </c>
@@ -21083,7 +20988,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="953" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>14</v>
       </c>
@@ -21111,7 +21016,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="954" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>14</v>
       </c>
@@ -21139,7 +21044,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="955" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>19</v>
       </c>
@@ -21167,7 +21072,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="956" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>19</v>
       </c>
@@ -21195,7 +21100,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="957" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>19</v>
       </c>
@@ -21223,7 +21128,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="958" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>19</v>
       </c>
@@ -21251,7 +21156,7 @@
         <v>43802</v>
       </c>
     </row>
-    <row r="959" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>19</v>
       </c>
@@ -21282,7 +21187,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="960" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>19</v>
       </c>
@@ -21310,7 +21215,7 @@
         <v>43789</v>
       </c>
     </row>
-    <row r="961" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>19</v>
       </c>
@@ -21338,7 +21243,7 @@
         <v>43792</v>
       </c>
     </row>
-    <row r="962" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>15</v>
       </c>
@@ -21366,7 +21271,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="963" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>15</v>
       </c>
@@ -21394,7 +21299,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="964" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>15</v>
       </c>
@@ -21422,7 +21327,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="965" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>15</v>
       </c>
@@ -21450,7 +21355,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="966" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>15</v>
       </c>
@@ -21478,7 +21383,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="967" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>15</v>
       </c>
@@ -21495,8 +21400,7 @@
         <v>110.81411110000001</v>
       </c>
       <c r="G967">
-        <f t="shared" si="19"/>
-        <v>110.81411110000001</v>
+        <v>107.15</v>
       </c>
       <c r="H967" t="s">
         <v>27</v>
@@ -21509,7 +21413,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="968" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>15</v>
       </c>
@@ -21529,9 +21433,6 @@
         <f t="shared" si="19"/>
         <v>112.8977778</v>
       </c>
-      <c r="H968" t="s">
-        <v>27</v>
-      </c>
       <c r="I968" s="5">
         <f t="shared" si="21"/>
         <v>334</v>
@@ -21540,7 +21441,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="969" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>15</v>
       </c>
@@ -21560,9 +21461,6 @@
         <f t="shared" si="19"/>
         <v>114.4113333</v>
       </c>
-      <c r="H969" t="s">
-        <v>27</v>
-      </c>
       <c r="I969" s="5">
         <f t="shared" si="21"/>
         <v>328</v>
@@ -21571,7 +21469,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="970" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>15</v>
       </c>
@@ -21599,7 +21497,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="971" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>15</v>
       </c>
@@ -21627,7 +21525,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="972" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>15</v>
       </c>
@@ -21655,7 +21553,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="973" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>15</v>
       </c>
@@ -21683,7 +21581,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="974" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>15</v>
       </c>
@@ -21711,7 +21609,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="975" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>15</v>
       </c>
@@ -21739,7 +21637,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="976" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>15</v>
       </c>
@@ -21767,7 +21665,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="977" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>15</v>
       </c>
@@ -21795,7 +21693,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="978" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>15</v>
       </c>
@@ -21815,9 +21713,6 @@
         <f t="shared" si="19"/>
         <v>104.7833333</v>
       </c>
-      <c r="H978" t="s">
-        <v>27</v>
-      </c>
       <c r="I978" s="5">
         <f t="shared" si="21"/>
         <v>328</v>
@@ -21826,7 +21721,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="979" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>15</v>
       </c>
@@ -21846,9 +21741,6 @@
         <f t="shared" si="19"/>
         <v>107.1852222</v>
       </c>
-      <c r="H979" t="s">
-        <v>27</v>
-      </c>
       <c r="I979" s="5">
         <f t="shared" si="21"/>
         <v>334</v>
@@ -21857,7 +21749,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="980" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>15</v>
       </c>
@@ -21885,7 +21777,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="981" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>15</v>
       </c>
@@ -21913,7 +21805,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="982" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>15</v>
       </c>
@@ -21941,7 +21833,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="983" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>15</v>
       </c>
@@ -21969,7 +21861,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="984" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>15</v>
       </c>
@@ -21997,7 +21889,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="985" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>15</v>
       </c>
@@ -22025,7 +21917,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="986" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>15</v>
       </c>
@@ -22053,7 +21945,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="987" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>15</v>
       </c>
@@ -22081,7 +21973,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="988" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>15</v>
       </c>
@@ -22109,7 +22001,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="989" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>15</v>
       </c>
@@ -22137,7 +22029,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="990" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>15</v>
       </c>
@@ -22165,7 +22057,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="991" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>15</v>
       </c>
@@ -22193,7 +22085,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="992" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>15</v>
       </c>
@@ -22221,7 +22113,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="993" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>15</v>
       </c>
@@ -22249,7 +22141,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="994" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>15</v>
       </c>
@@ -22277,7 +22169,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="995" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>15</v>
       </c>
@@ -22305,7 +22197,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="996" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>15</v>
       </c>
@@ -22333,7 +22225,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="997" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>15</v>
       </c>
@@ -22361,7 +22253,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="998" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>15</v>
       </c>
@@ -22389,7 +22281,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="999" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>15</v>
       </c>
@@ -22417,7 +22309,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>15</v>
       </c>
@@ -22445,7 +22337,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>15</v>
       </c>
@@ -22473,7 +22365,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="1002" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>15</v>
       </c>
@@ -22501,7 +22393,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>15</v>
       </c>
@@ -22529,7 +22421,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>15</v>
       </c>
@@ -22549,9 +22441,6 @@
         <f t="shared" si="22"/>
         <v>110.3692222</v>
       </c>
-      <c r="H1004" t="s">
-        <v>27</v>
-      </c>
       <c r="I1004" s="5">
         <f t="shared" si="21"/>
         <v>328</v>
@@ -22560,7 +22449,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>15</v>
       </c>
@@ -22580,9 +22469,6 @@
         <f t="shared" si="22"/>
         <v>97.827444439999994</v>
       </c>
-      <c r="H1005" t="s">
-        <v>27</v>
-      </c>
       <c r="I1005" s="5">
         <f t="shared" si="21"/>
         <v>332</v>
@@ -22591,7 +22477,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>15</v>
       </c>
@@ -22611,9 +22497,6 @@
         <f t="shared" si="22"/>
         <v>98.942444440000003</v>
       </c>
-      <c r="H1006" t="s">
-        <v>27</v>
-      </c>
       <c r="I1006" s="5">
         <f t="shared" si="21"/>
         <v>330</v>
@@ -22622,7 +22505,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>15</v>
       </c>
@@ -22650,7 +22533,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1008" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>15</v>
       </c>
@@ -22678,7 +22561,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="1009" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>15</v>
       </c>
@@ -22706,7 +22589,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1010" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>15</v>
       </c>
@@ -22734,7 +22617,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="1011" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>15</v>
       </c>
@@ -22762,7 +22645,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="1012" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>15</v>
       </c>
@@ -22790,7 +22673,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1013" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>15</v>
       </c>
@@ -22818,7 +22701,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="1014" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>15</v>
       </c>
@@ -22846,7 +22729,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="1015" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>15</v>
       </c>
@@ -22874,7 +22757,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="1016" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>20</v>
       </c>
@@ -22902,7 +22785,7 @@
         <v>44159</v>
       </c>
     </row>
-    <row r="1017" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>20</v>
       </c>
@@ -22930,7 +22813,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1018" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>20</v>
       </c>
@@ -22958,7 +22841,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1019" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>20</v>
       </c>
@@ -22986,7 +22869,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1020" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>20</v>
       </c>
@@ -23014,7 +22897,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1021" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>20</v>
       </c>
@@ -23042,7 +22925,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1022" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>20</v>
       </c>
@@ -23070,7 +22953,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1023" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>20</v>
       </c>
@@ -23098,7 +22981,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1024" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>20</v>
       </c>
@@ -23129,7 +23012,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1025" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>20</v>
       </c>
@@ -23157,7 +23040,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1026" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>20</v>
       </c>
@@ -23185,7 +23068,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1027" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -23214,7 +23097,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1028" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -23242,7 +23125,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1029" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -23270,7 +23153,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1030" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -23298,7 +23181,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1031" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -23326,7 +23209,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1032" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -23354,7 +23237,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1033" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -23382,7 +23265,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1034" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -23410,7 +23293,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1035" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -23438,7 +23321,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1036" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -23466,7 +23349,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1037" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -23494,7 +23377,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1038" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -23522,7 +23405,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1039" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -23550,7 +23433,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1040" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -23578,7 +23461,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1041" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -23606,7 +23489,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1042" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -23634,7 +23517,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1043" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -23662,7 +23545,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1044" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -23690,7 +23573,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1045" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -23718,7 +23601,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1046" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -23735,8 +23618,7 @@
         <v>134.6</v>
       </c>
       <c r="G1046">
-        <f t="shared" si="22"/>
-        <v>134.6</v>
+        <v>124.47</v>
       </c>
       <c r="H1046" t="s">
         <v>27</v>
@@ -23749,7 +23631,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1047" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -23777,7 +23659,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1048" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -23805,7 +23687,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1049" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -23834,7 +23716,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1050" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -23862,7 +23744,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1051" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -23890,7 +23772,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1052" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -23918,7 +23800,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1053" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -23946,7 +23828,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1054" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -23974,7 +23856,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1055" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -24002,7 +23884,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1056" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -24022,9 +23904,6 @@
         <f t="shared" si="22"/>
         <v>118.6</v>
       </c>
-      <c r="H1056" t="s">
-        <v>27</v>
-      </c>
       <c r="I1056" s="5">
         <f t="shared" si="23"/>
         <v>327</v>
@@ -24033,7 +23912,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1057" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -24053,9 +23932,6 @@
         <f t="shared" si="22"/>
         <v>120.7</v>
       </c>
-      <c r="H1057" t="s">
-        <v>27</v>
-      </c>
       <c r="I1057" s="5">
         <f t="shared" si="23"/>
         <v>323</v>
@@ -24064,7 +23940,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1058" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -24092,7 +23968,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1059" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -24120,7 +23996,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1060" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -24148,7 +24024,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1061" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -24176,7 +24052,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1062" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -24204,7 +24080,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1063" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -24232,7 +24108,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1064" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
         <v>16</v>
       </c>
@@ -24260,7 +24136,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1065" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
         <v>16</v>
       </c>
@@ -24288,7 +24164,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1066" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
         <v>16</v>
       </c>
@@ -24316,7 +24192,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1067" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>16</v>
       </c>
@@ -24336,9 +24212,6 @@
         <f t="shared" si="24"/>
         <v>109.8</v>
       </c>
-      <c r="H1067" t="s">
-        <v>27</v>
-      </c>
       <c r="I1067" s="5">
         <f t="shared" si="23"/>
         <v>323</v>
@@ -24347,7 +24220,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1068" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
         <v>16</v>
       </c>
@@ -24367,9 +24240,6 @@
         <f t="shared" si="24"/>
         <v>112.7</v>
       </c>
-      <c r="H1068" t="s">
-        <v>27</v>
-      </c>
       <c r="I1068" s="5">
         <f t="shared" si="23"/>
         <v>324</v>
@@ -24378,7 +24248,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1069" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
         <v>16</v>
       </c>
@@ -24406,7 +24276,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1070" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>16</v>
       </c>
@@ -24434,7 +24304,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1071" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
         <v>16</v>
       </c>
@@ -24462,7 +24332,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1072" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
         <v>16</v>
       </c>
@@ -24490,7 +24360,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1073" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
         <v>16</v>
       </c>
@@ -24518,7 +24388,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1074" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
         <v>16</v>
       </c>
@@ -24546,7 +24416,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1075" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
         <v>16</v>
       </c>
@@ -24574,7 +24444,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1076" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
         <v>16</v>
       </c>
@@ -24602,7 +24472,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1077" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
         <v>16</v>
       </c>
@@ -24630,7 +24500,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1078" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
         <v>16</v>
       </c>
@@ -24650,9 +24520,6 @@
         <f t="shared" si="24"/>
         <v>139.80000000000001</v>
       </c>
-      <c r="H1078" t="s">
-        <v>27</v>
-      </c>
       <c r="I1078" s="5">
         <f t="shared" si="23"/>
         <v>324</v>
@@ -24661,7 +24528,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="1079" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
         <v>16</v>
       </c>
@@ -24681,9 +24548,6 @@
         <f t="shared" si="24"/>
         <v>135.1</v>
       </c>
-      <c r="H1079" t="s">
-        <v>27</v>
-      </c>
       <c r="I1079" s="5">
         <f t="shared" si="23"/>
         <v>334</v>
@@ -24692,7 +24556,7 @@
         <v>44529</v>
       </c>
     </row>
-    <row r="1080" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
         <v>16</v>
       </c>
@@ -24720,7 +24584,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="1081" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>16</v>
       </c>
@@ -24748,7 +24612,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="1082" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
         <v>21</v>
       </c>
@@ -24776,7 +24640,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1083" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>21</v>
       </c>
@@ -24804,7 +24668,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1084" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>21</v>
       </c>
@@ -24832,7 +24696,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1085" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
         <v>21</v>
       </c>
@@ -24860,7 +24724,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1086" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
         <v>21</v>
       </c>
@@ -24888,7 +24752,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1087" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
         <v>21</v>
       </c>
@@ -24916,7 +24780,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1088" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
         <v>21</v>
       </c>
@@ -24944,7 +24808,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1089" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
         <v>21</v>
       </c>
@@ -24972,7 +24836,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1090" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
         <v>21</v>
       </c>
@@ -25000,7 +24864,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1091" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
         <v>21</v>
       </c>
@@ -25031,7 +24895,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1092" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
         <v>21</v>
       </c>
@@ -25059,7 +24923,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1093" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
         <v>17</v>
       </c>
@@ -25087,7 +24951,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1094" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
         <v>17</v>
       </c>
@@ -25115,7 +24979,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1095" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
         <v>17</v>
       </c>
@@ -25143,7 +25007,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1096" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
         <v>17</v>
       </c>
@@ -25171,7 +25035,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1097" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
         <v>17</v>
       </c>
@@ -25199,7 +25063,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1098" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
         <v>17</v>
       </c>
@@ -25227,7 +25091,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1099" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
         <v>17</v>
       </c>
@@ -25255,7 +25119,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
         <v>17</v>
       </c>
@@ -25272,8 +25136,7 @@
         <v>114.6</v>
       </c>
       <c r="G1100">
-        <f t="shared" si="24"/>
-        <v>114.6</v>
+        <v>121.39</v>
       </c>
       <c r="H1100" t="s">
         <v>27</v>
@@ -25286,7 +25149,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
         <v>17</v>
       </c>
@@ -25306,9 +25169,6 @@
         <f t="shared" si="24"/>
         <v>116.7</v>
       </c>
-      <c r="H1101" t="s">
-        <v>27</v>
-      </c>
       <c r="I1101" s="5">
         <f t="shared" si="26"/>
         <v>333</v>
@@ -25317,7 +25177,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
         <v>17</v>
       </c>
@@ -25345,7 +25205,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
         <v>17</v>
       </c>
@@ -25373,7 +25233,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
         <v>17</v>
       </c>
@@ -25401,7 +25261,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
         <v>17</v>
       </c>
@@ -25429,7 +25289,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
         <v>17</v>
       </c>
@@ -25457,7 +25317,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
         <v>17</v>
       </c>
@@ -25485,7 +25345,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
         <v>17</v>
       </c>
@@ -25513,7 +25373,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
         <v>17</v>
       </c>
@@ -25541,7 +25401,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
         <v>17</v>
       </c>
@@ -25569,7 +25429,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
         <v>17</v>
       </c>
@@ -25589,9 +25449,6 @@
         <f t="shared" si="24"/>
         <v>141.4</v>
       </c>
-      <c r="H1111" t="s">
-        <v>27</v>
-      </c>
       <c r="I1111" s="5">
         <f t="shared" si="26"/>
         <v>326</v>
@@ -25600,7 +25457,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
         <v>17</v>
       </c>
@@ -25620,9 +25477,6 @@
         <f t="shared" si="24"/>
         <v>140.5</v>
       </c>
-      <c r="H1112" t="s">
-        <v>27</v>
-      </c>
       <c r="I1112" s="5">
         <f t="shared" si="26"/>
         <v>330</v>
@@ -25631,7 +25485,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
         <v>17</v>
       </c>
@@ -25659,7 +25513,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
         <v>17</v>
       </c>
@@ -25687,7 +25541,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
         <v>17</v>
       </c>
@@ -25715,7 +25569,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>17</v>
       </c>
@@ -25743,7 +25597,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>17</v>
       </c>
@@ -25771,7 +25625,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
         <v>17</v>
       </c>
@@ -25799,7 +25653,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
         <v>17</v>
       </c>
@@ -25827,7 +25681,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
         <v>17</v>
       </c>
@@ -25855,7 +25709,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
         <v>17</v>
       </c>
@@ -25883,7 +25737,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
         <v>17</v>
       </c>
@@ -25903,9 +25757,6 @@
         <f t="shared" si="24"/>
         <v>138.69999999999999</v>
       </c>
-      <c r="H1122" t="s">
-        <v>27</v>
-      </c>
       <c r="I1122" s="5">
         <f t="shared" si="26"/>
         <v>330</v>
@@ -25914,7 +25765,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
         <v>17</v>
       </c>
@@ -25934,9 +25785,6 @@
         <f t="shared" si="24"/>
         <v>136.9</v>
       </c>
-      <c r="H1123" t="s">
-        <v>27</v>
-      </c>
       <c r="I1123" s="5">
         <f t="shared" si="26"/>
         <v>326</v>
@@ -25945,7 +25793,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
         <v>17</v>
       </c>
@@ -25973,7 +25821,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
         <v>17</v>
       </c>
@@ -26001,7 +25849,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
         <v>17</v>
       </c>
@@ -26029,7 +25877,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
         <v>17</v>
       </c>
@@ -26057,7 +25905,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
         <v>17</v>
       </c>
@@ -26085,7 +25933,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
         <v>17</v>
       </c>
@@ -26113,7 +25961,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>17</v>
       </c>
@@ -26141,7 +25989,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
         <v>17</v>
       </c>
@@ -26169,7 +26017,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
         <v>17</v>
       </c>
@@ -26197,7 +26045,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
         <v>17</v>
       </c>
@@ -26217,9 +26065,6 @@
         <f t="shared" si="27"/>
         <v>112.4</v>
       </c>
-      <c r="H1133" t="s">
-        <v>27</v>
-      </c>
       <c r="I1133" s="5">
         <f t="shared" si="26"/>
         <v>326</v>
@@ -26228,7 +26073,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1134" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
         <v>17</v>
       </c>
@@ -26248,9 +26093,6 @@
         <f t="shared" si="27"/>
         <v>117.5</v>
       </c>
-      <c r="H1134" t="s">
-        <v>27</v>
-      </c>
       <c r="I1134" s="5">
         <f t="shared" si="26"/>
         <v>327</v>
@@ -26259,7 +26101,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
         <v>17</v>
       </c>
@@ -26287,7 +26129,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
         <v>17</v>
       </c>
@@ -26315,7 +26157,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
         <v>17</v>
       </c>
@@ -26343,7 +26185,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
         <v>17</v>
       </c>
@@ -26371,7 +26213,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
         <v>17</v>
       </c>
@@ -26399,7 +26241,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
         <v>17</v>
       </c>
@@ -26427,7 +26269,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
         <v>17</v>
       </c>
@@ -26455,7 +26297,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
         <v>17</v>
       </c>
@@ -26483,7 +26325,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
         <v>17</v>
       </c>
@@ -26511,7 +26353,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
         <v>17</v>
       </c>
@@ -26531,9 +26373,6 @@
         <f t="shared" si="27"/>
         <v>97.4</v>
       </c>
-      <c r="H1144" t="s">
-        <v>27</v>
-      </c>
       <c r="I1144" s="5">
         <f t="shared" si="26"/>
         <v>327</v>
@@ -26542,7 +26381,7 @@
         <v>44887</v>
       </c>
     </row>
-    <row r="1145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
         <v>17</v>
       </c>
@@ -26562,9 +26401,6 @@
         <f t="shared" si="27"/>
         <v>97.8</v>
       </c>
-      <c r="H1145" t="s">
-        <v>27</v>
-      </c>
       <c r="I1145" s="5">
         <f t="shared" si="26"/>
         <v>333</v>
@@ -26573,7 +26409,7 @@
         <v>44893</v>
       </c>
     </row>
-    <row r="1146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1146" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
         <v>17</v>
       </c>
@@ -26601,7 +26437,7 @@
         <v>44886</v>
       </c>
     </row>
-    <row r="1147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
         <v>17</v>
       </c>
@@ -26629,7 +26465,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="1148" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
         <v>22</v>
       </c>
@@ -26657,7 +26493,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1149" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
         <v>22</v>
       </c>
@@ -26685,7 +26521,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1150" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
         <v>22</v>
       </c>
@@ -26713,7 +26549,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1151" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
         <v>22</v>
       </c>
@@ -26741,7 +26577,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1152" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
         <v>22</v>
       </c>
@@ -26769,7 +26605,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1153" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
         <v>22</v>
       </c>
@@ -26797,7 +26633,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1154" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
         <v>22</v>
       </c>
@@ -26825,7 +26661,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1155" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
         <v>22</v>
       </c>
@@ -26853,7 +26689,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1156" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
         <v>22</v>
       </c>
@@ -26884,7 +26720,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1157" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
         <v>22</v>
       </c>
@@ -26912,7 +26748,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1158" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
         <v>22</v>
       </c>
@@ -26940,7 +26776,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
         <v>18</v>
       </c>
@@ -26968,7 +26804,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1160" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
         <v>18</v>
       </c>
@@ -26996,7 +26832,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
         <v>18</v>
       </c>
@@ -27024,7 +26860,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
         <v>18</v>
       </c>
@@ -27052,7 +26888,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
         <v>18</v>
       </c>
@@ -27080,7 +26916,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1164" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
         <v>18</v>
       </c>
@@ -27097,8 +26933,7 @@
         <v>83.7</v>
       </c>
       <c r="G1164">
-        <f t="shared" si="27"/>
-        <v>83.7</v>
+        <v>95.5</v>
       </c>
       <c r="H1164" t="s">
         <v>27</v>
@@ -27111,7 +26946,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
         <v>18</v>
       </c>
@@ -27131,9 +26966,6 @@
         <f t="shared" si="27"/>
         <v>87</v>
       </c>
-      <c r="H1165" t="s">
-        <v>27</v>
-      </c>
       <c r="I1165" s="5">
         <f t="shared" si="29"/>
         <v>327</v>
@@ -27142,7 +26974,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1166" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
         <v>18</v>
       </c>
@@ -27170,7 +27002,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
         <v>18</v>
       </c>
@@ -27198,7 +27030,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1168" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
         <v>18</v>
       </c>
@@ -27226,7 +27058,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
         <v>18</v>
       </c>
@@ -27254,7 +27086,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
         <v>18</v>
       </c>
@@ -27282,7 +27114,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
         <v>18</v>
       </c>
@@ -27310,7 +27142,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1172" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
         <v>18</v>
       </c>
@@ -27338,7 +27170,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
         <v>18</v>
       </c>
@@ -27366,7 +27198,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1174" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
         <v>18</v>
       </c>
@@ -27394,7 +27226,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
         <v>18</v>
       </c>
@@ -27414,9 +27246,6 @@
         <f t="shared" si="27"/>
         <v>103.7</v>
       </c>
-      <c r="H1175" t="s">
-        <v>27</v>
-      </c>
       <c r="I1175" s="5">
         <f t="shared" si="29"/>
         <v>334</v>
@@ -27425,7 +27254,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1176" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
         <v>18</v>
       </c>
@@ -27445,9 +27274,6 @@
         <f t="shared" si="27"/>
         <v>108.9</v>
       </c>
-      <c r="H1176" t="s">
-        <v>27</v>
-      </c>
       <c r="I1176" s="5">
         <f t="shared" si="29"/>
         <v>328</v>
@@ -27456,7 +27282,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
         <v>18</v>
       </c>
@@ -27484,7 +27310,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
         <v>18</v>
       </c>
@@ -27512,7 +27338,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
         <v>18</v>
       </c>
@@ -27540,7 +27366,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
         <v>18</v>
       </c>
@@ -27568,7 +27394,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
         <v>18</v>
       </c>
@@ -27596,7 +27422,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
         <v>18</v>
       </c>
@@ -27624,7 +27450,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
         <v>18</v>
       </c>
@@ -27652,7 +27478,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1184" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
         <v>18</v>
       </c>
@@ -27680,7 +27506,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
         <v>18</v>
       </c>
@@ -27708,7 +27534,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
         <v>18</v>
       </c>
@@ -27728,9 +27554,6 @@
         <f t="shared" si="27"/>
         <v>91.8</v>
       </c>
-      <c r="H1186" t="s">
-        <v>27</v>
-      </c>
       <c r="I1186" s="5">
         <f t="shared" si="29"/>
         <v>333</v>
@@ -27739,7 +27562,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1187" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
         <v>18</v>
       </c>
@@ -27759,9 +27582,6 @@
         <f t="shared" si="27"/>
         <v>98.2</v>
       </c>
-      <c r="H1187" t="s">
-        <v>27</v>
-      </c>
       <c r="I1187" s="5">
         <f t="shared" si="29"/>
         <v>334</v>
@@ -27770,7 +27590,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
         <v>18</v>
       </c>
@@ -27798,7 +27618,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
         <v>18</v>
       </c>
@@ -27826,7 +27646,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
         <v>18</v>
       </c>
@@ -27854,7 +27674,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
         <v>18</v>
       </c>
@@ -27882,7 +27702,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
         <v>18</v>
       </c>
@@ -27910,7 +27730,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
         <v>18</v>
       </c>
@@ -27938,7 +27758,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
         <v>18</v>
       </c>
@@ -27966,7 +27786,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
         <v>18</v>
       </c>
@@ -27994,7 +27814,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
         <v>18</v>
       </c>
@@ -28022,7 +27842,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
         <v>18</v>
       </c>
@@ -28042,9 +27862,6 @@
         <f t="shared" si="30"/>
         <v>86.6</v>
       </c>
-      <c r="H1197" t="s">
-        <v>27</v>
-      </c>
       <c r="I1197" s="5">
         <f t="shared" si="29"/>
         <v>334</v>
@@ -28053,7 +27870,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1198" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
         <v>18</v>
       </c>
@@ -28073,9 +27890,6 @@
         <f t="shared" si="30"/>
         <v>90.1</v>
       </c>
-      <c r="H1198" t="s">
-        <v>27</v>
-      </c>
       <c r="I1198" s="5">
         <f t="shared" si="29"/>
         <v>326</v>
@@ -28084,7 +27898,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
         <v>18</v>
       </c>
@@ -28112,7 +27926,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
         <v>18</v>
       </c>
@@ -28140,7 +27954,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
         <v>18</v>
       </c>
@@ -28168,7 +27982,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1202" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
         <v>18</v>
       </c>
@@ -28196,7 +28010,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1203" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
         <v>18</v>
       </c>
@@ -28224,7 +28038,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1204" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
         <v>18</v>
       </c>
@@ -28252,7 +28066,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1205" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
         <v>18</v>
       </c>
@@ -28280,7 +28094,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1206" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
         <v>18</v>
       </c>
@@ -28308,7 +28122,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
         <v>18</v>
       </c>
@@ -28336,7 +28150,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
         <v>18</v>
       </c>
@@ -28356,9 +28170,6 @@
         <f t="shared" si="30"/>
         <v>102.7</v>
       </c>
-      <c r="H1208" t="s">
-        <v>27</v>
-      </c>
       <c r="I1208" s="5">
         <f t="shared" si="29"/>
         <v>333</v>
@@ -28367,7 +28178,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1209" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
         <v>18</v>
       </c>
@@ -28387,9 +28198,6 @@
         <f t="shared" si="30"/>
         <v>102.3</v>
       </c>
-      <c r="H1209" t="s">
-        <v>27</v>
-      </c>
       <c r="I1209" s="5">
         <f t="shared" si="29"/>
         <v>334</v>
@@ -28398,7 +28206,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="1210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1210" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
         <v>18</v>
       </c>
@@ -28426,7 +28234,7 @@
         <v>45251</v>
       </c>
     </row>
-    <row r="1211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1211" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
         <v>18</v>
       </c>
@@ -28454,7 +28262,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="1212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1212" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
         <v>18</v>
       </c>
@@ -28482,7 +28290,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1213" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
         <v>18</v>
       </c>
@@ -28506,7 +28314,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="1214" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
         <v>23</v>
       </c>
@@ -28534,7 +28342,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1215" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
         <v>23</v>
       </c>
@@ -28562,7 +28370,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1216" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
         <v>23</v>
       </c>
@@ -28590,7 +28398,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1217" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
         <v>23</v>
       </c>
@@ -28618,7 +28426,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1218" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
         <v>23</v>
       </c>
@@ -28646,7 +28454,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1219" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
         <v>23</v>
       </c>
@@ -28674,7 +28482,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1220" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
         <v>23</v>
       </c>
@@ -28691,8 +28499,7 @@
         <v>113.8</v>
       </c>
       <c r="G1220">
-        <f t="shared" si="30"/>
-        <v>113.8</v>
+        <v>100.85</v>
       </c>
       <c r="H1220" t="s">
         <v>27</v>
@@ -28705,7 +28512,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1221" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
         <v>23</v>
       </c>
@@ -28725,9 +28532,6 @@
         <f t="shared" si="30"/>
         <v>87.9</v>
       </c>
-      <c r="H1221" t="s">
-        <v>27</v>
-      </c>
       <c r="I1221" s="4">
         <f t="shared" si="32"/>
         <v>327</v>
@@ -28736,7 +28540,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1222" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
         <v>23</v>
       </c>
@@ -28764,7 +28568,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1223" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
         <v>23</v>
       </c>
@@ -28792,7 +28596,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="1224" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
         <v>23</v>
       </c>
@@ -28824,15 +28628,11 @@
   <autoFilter ref="A1:A1224" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="TPHW2016"/>
-        <filter val="TPHW2017"/>
-        <filter val="TPHW2018"/>
-        <filter val="TPHW2019"/>
-        <filter val="TPHW2020"/>
-        <filter val="TPHW2021"/>
-        <filter val="TPHW2022"/>
-        <filter val="TPHW2023"/>
-        <filter val="TPHW2024"/>
+        <filter val="KKHW2020"/>
+        <filter val="KKHW2021"/>
+        <filter val="KKHW2022"/>
+        <filter val="KKHW2023"/>
+        <filter val="KKHW2024"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -46826,7 +46626,7 @@
         <v>18.060959017147049</v>
       </c>
       <c r="G1024">
-        <f t="shared" ref="G1024:G1057" si="10">F1024</f>
+        <f t="shared" ref="G1024" si="10">F1024</f>
         <v>18.060959017147049</v>
       </c>
       <c r="H1024" t="s">
@@ -49097,7 +48897,7 @@
         <v>24.252000000000002</v>
       </c>
       <c r="G1156">
-        <f t="shared" ref="G1156:G1175" si="11">F1156</f>
+        <f t="shared" ref="G1156" si="11">F1156</f>
         <v>24.252000000000002</v>
       </c>
       <c r="H1156" t="s">

--- a/Prototypes/KiwiFruit/Yield.xlsx
+++ b/Prototypes/KiwiFruit/Yield.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583BCCF3-6030-4013-9903-3D49400B045A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3135AD3-433A-4E72-B992-39247A7EEA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SingleBerryFW" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8718" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8666" uniqueCount="33">
   <si>
     <t>SimulationName</t>
   </si>
@@ -16913,7 +16913,7 @@
         <v>105.5</v>
       </c>
       <c r="G807">
-        <f t="shared" ref="G807:G870" si="15">F807</f>
+        <f t="shared" ref="G807:G869" si="15">F807</f>
         <v>105.5</v>
       </c>
       <c r="I807" s="5">
@@ -50097,7 +50097,8 @@
     <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="7" width="41.42578125" customWidth="1"/>
+    <col min="6" max="6" width="41.42578125" customWidth="1"/>
+    <col min="7" max="7" width="60.28515625" customWidth="1"/>
     <col min="8" max="8" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -61651,7 +61652,7 @@
       </c>
     </row>
     <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>10</v>
       </c>
@@ -61669,7 +61670,7 @@
         <v>7.3999999999999995</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>10</v>
       </c>
@@ -61687,7 +61688,7 @@
         <v>6.8999999999999995</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>10</v>
       </c>
@@ -61705,7 +61706,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>10</v>
       </c>
@@ -61723,7 +61724,7 @@
         <v>11.899999999999999</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>10</v>
       </c>
@@ -61741,7 +61742,7 @@
         <v>13.399999999999999</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>10</v>
       </c>
@@ -61759,7 +61760,7 @@
         <v>13.600000000000001</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>10</v>
       </c>
@@ -61777,7 +61778,7 @@
         <v>14.299999999999999</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>10</v>
       </c>
@@ -61795,7 +61796,7 @@
         <v>14.899999999999999</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>10</v>
       </c>
@@ -61813,7 +61814,7 @@
         <v>14.500000000000002</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>10</v>
       </c>
@@ -61831,7 +61832,7 @@
         <v>15.299999999999999</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>10</v>
       </c>
@@ -61849,7 +61850,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>10</v>
       </c>
@@ -61867,7 +61868,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>10</v>
       </c>
@@ -61885,7 +61886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>10</v>
       </c>
@@ -61903,7 +61904,7 @@
         <v>15.599999999999998</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>10</v>
       </c>
@@ -61921,7 +61922,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>10</v>
       </c>
@@ -61939,7 +61940,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>10</v>
       </c>
@@ -61956,15 +61957,8 @@
         <f>(SingleBerryDW!F630/SingleBerryFW!F630)*100</f>
         <v>15.7</v>
       </c>
-      <c r="G630">
-        <f>F630</f>
-        <v>15.7</v>
-      </c>
-      <c r="H630" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>10</v>
       </c>
@@ -61981,15 +61975,8 @@
         <f>(SingleBerryDW!F631/SingleBerryFW!F631)*100</f>
         <v>16.5</v>
       </c>
-      <c r="G631">
-        <f>F631</f>
-        <v>16.5</v>
-      </c>
-      <c r="H631" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>10</v>
       </c>
@@ -62007,7 +61994,7 @@
         <v>15.800000000000002</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>10</v>
       </c>
@@ -62025,7 +62012,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>10</v>
       </c>
@@ -62043,7 +62030,7 @@
         <v>15.900000000000002</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>10</v>
       </c>
@@ -62061,7 +62048,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>10</v>
       </c>
@@ -62079,7 +62066,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>10</v>
       </c>
@@ -62097,7 +62084,7 @@
         <v>17.100000000000005</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>10</v>
       </c>
@@ -62115,7 +62102,7 @@
         <v>7.2000000000000011</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>10</v>
       </c>
@@ -62133,7 +62120,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>10</v>
       </c>
@@ -62151,7 +62138,7 @@
         <v>14.400000000000002</v>
       </c>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>10</v>
       </c>
@@ -62169,7 +62156,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>10</v>
       </c>
@@ -62187,7 +62174,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>10</v>
       </c>
@@ -62205,7 +62192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>10</v>
       </c>
@@ -62223,7 +62210,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>10</v>
       </c>
@@ -62241,7 +62228,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>10</v>
       </c>
@@ -62258,15 +62245,8 @@
         <f>(SingleBerryDW!F646/SingleBerryFW!F646)*100</f>
         <v>16.8</v>
       </c>
-      <c r="G646">
-        <f>F646</f>
-        <v>16.8</v>
-      </c>
-      <c r="H646" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>10</v>
       </c>
@@ -62284,7 +62264,7 @@
         <v>17.700000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>10</v>
       </c>
@@ -62302,7 +62282,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>10</v>
       </c>
@@ -62320,7 +62300,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>10</v>
       </c>
@@ -62338,7 +62318,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>10</v>
       </c>
@@ -62356,7 +62336,7 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>10</v>
       </c>
@@ -62374,7 +62354,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>10</v>
       </c>
@@ -62392,7 +62372,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>10</v>
       </c>
@@ -62410,7 +62390,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>10</v>
       </c>
@@ -62428,7 +62408,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>10</v>
       </c>
@@ -62446,7 +62426,7 @@
         <v>11.600000000000001</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>10</v>
       </c>
@@ -62464,7 +62444,7 @@
         <v>11.800000000000002</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>10</v>
       </c>
@@ -62482,7 +62462,7 @@
         <v>13.600000000000001</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>10</v>
       </c>
@@ -62500,7 +62480,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>10</v>
       </c>
@@ -62518,7 +62498,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>10</v>
       </c>
@@ -62536,7 +62516,7 @@
         <v>13.100000000000001</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>10</v>
       </c>
@@ -62554,7 +62534,7 @@
         <v>15.800000000000002</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>10</v>
       </c>
@@ -62572,7 +62552,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>10</v>
       </c>
@@ -62590,7 +62570,7 @@
         <v>14.099999999999998</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>10</v>
       </c>
@@ -62608,7 +62588,7 @@
         <v>14.499999999999998</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>10</v>
       </c>
@@ -62626,7 +62606,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>10</v>
       </c>
@@ -62644,7 +62624,7 @@
         <v>15.400000000000002</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>10</v>
       </c>
@@ -62662,7 +62642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>10</v>
       </c>
@@ -62680,7 +62660,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>10</v>
       </c>
@@ -62698,7 +62678,7 @@
         <v>15.400000000000002</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>10</v>
       </c>
@@ -62716,7 +62696,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>10</v>
       </c>
@@ -62734,7 +62714,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>10</v>
       </c>
@@ -62752,7 +62732,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>10</v>
       </c>
@@ -62770,7 +62750,7 @@
         <v>16.900000000000002</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>10</v>
       </c>
@@ -62788,7 +62768,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>10</v>
       </c>
@@ -62806,7 +62786,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>10</v>
       </c>
@@ -62824,7 +62804,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>10</v>
       </c>
@@ -62842,7 +62822,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>10</v>
       </c>
@@ -62860,7 +62840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>10</v>
       </c>
@@ -62878,7 +62858,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>10</v>
       </c>
@@ -62896,7 +62876,7 @@
         <v>15.699999999999998</v>
       </c>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>10</v>
       </c>
@@ -62914,14 +62894,13 @@
         <v>16.100000000000001</v>
       </c>
       <c r="G682">
-        <f>F682</f>
-        <v>16.100000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="H682" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>10</v>
       </c>
@@ -62939,7 +62918,7 @@
         <v>17.200000000000003</v>
       </c>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>10</v>
       </c>
@@ -62957,7 +62936,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>10</v>
       </c>
@@ -62975,7 +62954,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>10</v>
       </c>
@@ -62993,7 +62972,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>10</v>
       </c>
@@ -63011,7 +62990,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>10</v>
       </c>
@@ -63029,7 +63008,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>10</v>
       </c>
@@ -63047,7 +63026,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>10</v>
       </c>
@@ -63065,7 +63044,7 @@
         <v>17.099999999999998</v>
       </c>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>10</v>
       </c>
@@ -63083,7 +63062,7 @@
         <v>18.000000000000004</v>
       </c>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>10</v>
       </c>
@@ -63101,7 +63080,7 @@
         <v>17.099999999999998</v>
       </c>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>10</v>
       </c>
@@ -63119,7 +63098,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>10</v>
       </c>
@@ -63137,7 +63116,7 @@
         <v>16.800000000000004</v>
       </c>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>10</v>
       </c>
@@ -63155,7 +63134,7 @@
         <v>18.000000000000004</v>
       </c>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>10</v>
       </c>
@@ -63173,7 +63152,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>11</v>
       </c>
@@ -63191,7 +63170,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>11</v>
       </c>
@@ -63209,7 +63188,7 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>11</v>
       </c>
@@ -63227,7 +63206,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>11</v>
       </c>
@@ -63245,7 +63224,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>11</v>
       </c>
@@ -63263,7 +63242,7 @@
         <v>14.299999999999999</v>
       </c>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>11</v>
       </c>
@@ -63281,7 +63260,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>11</v>
       </c>
@@ -63299,7 +63278,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>11</v>
       </c>
@@ -63317,7 +63296,7 @@
         <v>13.700000000000001</v>
       </c>
     </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>11</v>
       </c>
@@ -63335,7 +63314,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>11</v>
       </c>
@@ -63353,7 +63332,7 @@
         <v>14.400000000000002</v>
       </c>
     </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>11</v>
       </c>
@@ -63371,7 +63350,7 @@
         <v>14.900000000000002</v>
       </c>
     </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>11</v>
       </c>
@@ -63389,7 +63368,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>11</v>
       </c>
@@ -63407,7 +63386,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>11</v>
       </c>
@@ -63425,7 +63404,7 @@
         <v>14.900000000000002</v>
       </c>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>11</v>
       </c>
@@ -63443,7 +63422,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>11</v>
       </c>
@@ -63461,7 +63440,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>11</v>
       </c>
@@ -63478,15 +63457,8 @@
         <f>(SingleBerryDW!F713/SingleBerryFW!F713)*100</f>
         <v>16.100000000000001</v>
       </c>
-      <c r="G713">
-        <f>F713</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="H713" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>11</v>
       </c>
@@ -63503,15 +63475,8 @@
         <f>(SingleBerryDW!F714/SingleBerryFW!F714)*100</f>
         <v>15</v>
       </c>
-      <c r="G714">
-        <f>F714</f>
-        <v>15</v>
-      </c>
-      <c r="H714" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>11</v>
       </c>
@@ -63529,7 +63494,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>11</v>
       </c>
@@ -63547,7 +63512,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>11</v>
       </c>
@@ -63565,7 +63530,7 @@
         <v>16.900000000000002</v>
       </c>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>11</v>
       </c>
@@ -63583,7 +63548,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>11</v>
       </c>
@@ -63601,7 +63566,7 @@
         <v>17.100000000000005</v>
       </c>
     </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>11</v>
       </c>
@@ -63619,7 +63584,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>11</v>
       </c>
@@ -63637,7 +63602,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="722" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>11</v>
       </c>
@@ -63655,7 +63620,7 @@
         <v>16.400000000000002</v>
       </c>
     </row>
-    <row r="723" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>11</v>
       </c>
@@ -63673,7 +63638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="724" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>11</v>
       </c>
@@ -63691,7 +63656,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="725" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>11</v>
       </c>
@@ -63709,7 +63674,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>11</v>
       </c>
@@ -63727,7 +63692,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="727" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>11</v>
       </c>
@@ -63745,7 +63710,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="728" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>11</v>
       </c>
@@ -63763,7 +63728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>11</v>
       </c>
@@ -63781,7 +63746,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="730" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>11</v>
       </c>
@@ -63799,7 +63764,7 @@
         <v>16.900000000000002</v>
       </c>
     </row>
-    <row r="731" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>11</v>
       </c>
@@ -63816,15 +63781,8 @@
         <f>(SingleBerryDW!F731/SingleBerryFW!F731)*100</f>
         <v>17</v>
       </c>
-      <c r="G731">
-        <f>F731</f>
-        <v>17</v>
-      </c>
-      <c r="H731" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="732" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>11</v>
       </c>
@@ -63842,7 +63800,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="733" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>11</v>
       </c>
@@ -63860,7 +63818,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="734" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>11</v>
       </c>
@@ -63878,7 +63836,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="735" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>11</v>
       </c>
@@ -63896,7 +63854,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="736" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>11</v>
       </c>
@@ -63914,7 +63872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>11</v>
       </c>
@@ -63932,7 +63890,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>11</v>
       </c>
@@ -63950,7 +63908,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>11</v>
       </c>
@@ -63968,7 +63926,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>11</v>
       </c>
@@ -63986,7 +63944,7 @@
         <v>13.100000000000001</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>11</v>
       </c>
@@ -64004,7 +63962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>11</v>
       </c>
@@ -64022,7 +63980,7 @@
         <v>12.400000000000002</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>11</v>
       </c>
@@ -64040,7 +63998,7 @@
         <v>12.999999999999998</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>11</v>
       </c>
@@ -64058,7 +64016,7 @@
         <v>14.400000000000002</v>
       </c>
     </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>11</v>
       </c>
@@ -64076,7 +64034,7 @@
         <v>14.899999999999999</v>
       </c>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>11</v>
       </c>
@@ -64094,7 +64052,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>11</v>
       </c>
@@ -64112,7 +64070,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>11</v>
       </c>
@@ -64130,7 +64088,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>11</v>
       </c>
@@ -64148,7 +64106,7 @@
         <v>15.599999999999998</v>
       </c>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>11</v>
       </c>
@@ -64166,7 +64124,7 @@
         <v>14.899999999999999</v>
       </c>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>11</v>
       </c>
@@ -64184,7 +64142,7 @@
         <v>15.699999999999998</v>
       </c>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>11</v>
       </c>
@@ -64202,7 +64160,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>11</v>
       </c>
@@ -64220,7 +64178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>11</v>
       </c>
@@ -64238,7 +64196,7 @@
         <v>15.400000000000002</v>
       </c>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>11</v>
       </c>
@@ -64256,7 +64214,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>11</v>
       </c>
@@ -64274,7 +64232,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>11</v>
       </c>
@@ -64292,7 +64250,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>11</v>
       </c>
@@ -64310,7 +64268,7 @@
         <v>15.400000000000002</v>
       </c>
     </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>11</v>
       </c>
@@ -64328,7 +64286,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>11</v>
       </c>
@@ -64346,7 +64304,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>11</v>
       </c>
@@ -64364,7 +64322,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>11</v>
       </c>
@@ -64382,7 +64340,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>11</v>
       </c>
@@ -64400,7 +64358,7 @@
         <v>16.799999999999997</v>
       </c>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>11</v>
       </c>
@@ -64418,7 +64376,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>11</v>
       </c>
@@ -64436,7 +64394,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>11</v>
       </c>
@@ -64454,7 +64412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>11</v>
       </c>
@@ -64472,7 +64430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>11</v>
       </c>
@@ -64490,7 +64448,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>11</v>
       </c>
@@ -64508,7 +64466,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>11</v>
       </c>
@@ -64526,14 +64484,13 @@
         <v>16.800000000000004</v>
       </c>
       <c r="G770">
-        <f>F770</f>
-        <v>16.800000000000004</v>
+        <v>16.5</v>
       </c>
       <c r="H770" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>11</v>
       </c>
@@ -64550,15 +64507,8 @@
         <f>(SingleBerryDW!F771/SingleBerryFW!F771)*100</f>
         <v>17.199999999999996</v>
       </c>
-      <c r="G771">
-        <f>F771</f>
-        <v>17.199999999999996</v>
-      </c>
-      <c r="H771" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>11</v>
       </c>
@@ -64576,7 +64526,7 @@
         <v>17.699999999999996</v>
       </c>
     </row>
-    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>11</v>
       </c>
@@ -64594,7 +64544,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>11</v>
       </c>
@@ -64612,7 +64562,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>11</v>
       </c>
@@ -64630,7 +64580,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>11</v>
       </c>
@@ -64648,7 +64598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>11</v>
       </c>
@@ -64666,7 +64616,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>11</v>
       </c>
@@ -64684,7 +64634,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>11</v>
       </c>
@@ -64702,7 +64652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>11</v>
       </c>
@@ -64720,7 +64670,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>11</v>
       </c>
@@ -64738,7 +64688,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>11</v>
       </c>
@@ -64756,7 +64706,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>11</v>
       </c>
@@ -64774,7 +64724,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>11</v>
       </c>
@@ -64792,7 +64742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>11</v>
       </c>
@@ -64810,7 +64760,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>12</v>
       </c>
@@ -64828,7 +64778,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>12</v>
       </c>
@@ -64846,7 +64796,7 @@
         <v>6.7999999999999989</v>
       </c>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>12</v>
       </c>
@@ -64864,7 +64814,7 @@
         <v>12.599999999999998</v>
       </c>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>12</v>
       </c>
@@ -64882,7 +64832,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>12</v>
       </c>
@@ -64900,7 +64850,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>12</v>
       </c>
@@ -64918,7 +64868,7 @@
         <v>13.299999999999997</v>
       </c>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>12</v>
       </c>
@@ -64936,7 +64886,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>12</v>
       </c>
@@ -64954,7 +64904,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>12</v>
       </c>
@@ -64972,7 +64922,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>12</v>
       </c>
@@ -64990,7 +64940,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>12</v>
       </c>
@@ -65008,7 +64958,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>12</v>
       </c>
@@ -65026,7 +64976,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>12</v>
       </c>
@@ -65044,7 +64994,7 @@
         <v>17.200000000000003</v>
       </c>
     </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>12</v>
       </c>
@@ -65062,7 +65012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>12</v>
       </c>
@@ -65080,7 +65030,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="801" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>12</v>
       </c>
@@ -65098,7 +65048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>12</v>
       </c>
@@ -65115,15 +65065,8 @@
         <f>(SingleBerryDW!F802/SingleBerryFW!F802)*100</f>
         <v>17.399999999999999</v>
       </c>
-      <c r="G802">
-        <f>F802</f>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="H802" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="803" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="803" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>12</v>
       </c>
@@ -65140,15 +65083,8 @@
         <f>(SingleBerryDW!F803/SingleBerryFW!F803)*100</f>
         <v>16.600000000000001</v>
       </c>
-      <c r="G803">
-        <f>F803</f>
-        <v>16.600000000000001</v>
-      </c>
-      <c r="H803" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="804" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="804" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>12</v>
       </c>
@@ -65166,7 +65102,7 @@
         <v>18.099999999999998</v>
       </c>
     </row>
-    <row r="805" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>12</v>
       </c>
@@ -65184,7 +65120,7 @@
         <v>16.600000000000005</v>
       </c>
     </row>
-    <row r="806" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>12</v>
       </c>
@@ -65202,7 +65138,7 @@
         <v>18.299999999999997</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>12</v>
       </c>
@@ -65220,7 +65156,7 @@
         <v>17.299999999999997</v>
       </c>
     </row>
-    <row r="808" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>12</v>
       </c>
@@ -65238,7 +65174,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="809" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>12</v>
       </c>
@@ -65256,7 +65192,7 @@
         <v>11.300000000000002</v>
       </c>
     </row>
-    <row r="810" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>12</v>
       </c>
@@ -65274,7 +65210,7 @@
         <v>13.699999999999998</v>
       </c>
     </row>
-    <row r="811" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>12</v>
       </c>
@@ -65292,7 +65228,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="812" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>12</v>
       </c>
@@ -65310,7 +65246,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="813" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>12</v>
       </c>
@@ -65328,7 +65264,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="814" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>12</v>
       </c>
@@ -65346,7 +65282,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="815" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>12</v>
       </c>
@@ -65364,7 +65300,7 @@
         <v>16.800000000000004</v>
       </c>
     </row>
-    <row r="816" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>12</v>
       </c>
@@ -65381,15 +65317,8 @@
         <f>(SingleBerryDW!F816/SingleBerryFW!F816)*100</f>
         <v>17</v>
       </c>
-      <c r="G816">
-        <f>F816</f>
-        <v>17</v>
-      </c>
-      <c r="H816" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="817" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>12</v>
       </c>
@@ -65407,7 +65336,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>12</v>
       </c>
@@ -65425,7 +65354,7 @@
         <v>17.599999999999998</v>
       </c>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>12</v>
       </c>
@@ -65443,7 +65372,7 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>12</v>
       </c>
@@ -65461,7 +65390,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>12</v>
       </c>
@@ -65479,7 +65408,7 @@
         <v>7.4000000000000012</v>
       </c>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>12</v>
       </c>
@@ -65497,7 +65426,7 @@
         <v>7.4000000000000012</v>
       </c>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>12</v>
       </c>
@@ -65515,7 +65444,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>12</v>
       </c>
@@ -65533,7 +65462,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>12</v>
       </c>
@@ -65551,7 +65480,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>12</v>
       </c>
@@ -65569,7 +65498,7 @@
         <v>12.000000000000002</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>12</v>
       </c>
@@ -65587,7 +65516,7 @@
         <v>14.200000000000001</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>12</v>
       </c>
@@ -65605,7 +65534,7 @@
         <v>14.200000000000001</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>12</v>
       </c>
@@ -65623,7 +65552,7 @@
         <v>12.800000000000002</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>12</v>
       </c>
@@ -65641,7 +65570,7 @@
         <v>14.100000000000001</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>12</v>
       </c>
@@ -65659,7 +65588,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>12</v>
       </c>
@@ -65677,7 +65606,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>12</v>
       </c>
@@ -65695,7 +65624,7 @@
         <v>14.099999999999998</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>12</v>
       </c>
@@ -65713,7 +65642,7 @@
         <v>15.299999999999999</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>12</v>
       </c>
@@ -65731,7 +65660,7 @@
         <v>15.600000000000003</v>
       </c>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>12</v>
       </c>
@@ -65749,7 +65678,7 @@
         <v>16.600000000000005</v>
       </c>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>12</v>
       </c>
@@ -65767,7 +65696,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>12</v>
       </c>
@@ -65785,7 +65714,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>12</v>
       </c>
@@ -65803,7 +65732,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>12</v>
       </c>
@@ -65821,7 +65750,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>12</v>
       </c>
@@ -65839,7 +65768,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>12</v>
       </c>
@@ -65857,7 +65786,7 @@
         <v>16.300000000000004</v>
       </c>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>12</v>
       </c>
@@ -65875,7 +65804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>12</v>
       </c>
@@ -65893,7 +65822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>12</v>
       </c>
@@ -65911,7 +65840,7 @@
         <v>15.299999999999999</v>
       </c>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>12</v>
       </c>
@@ -65929,7 +65858,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>12</v>
       </c>
@@ -65947,7 +65876,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>12</v>
       </c>
@@ -65965,7 +65894,7 @@
         <v>16.600000000000005</v>
       </c>
     </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>12</v>
       </c>
@@ -65983,7 +65912,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>12</v>
       </c>
@@ -66001,7 +65930,7 @@
         <v>17.100000000000005</v>
       </c>
     </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>12</v>
       </c>
@@ -66018,15 +65947,8 @@
         <f>(SingleBerryDW!F851/SingleBerryFW!F851)*100</f>
         <v>15.7</v>
       </c>
-      <c r="G851">
-        <f>F851</f>
-        <v>15.7</v>
-      </c>
-      <c r="H851" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>12</v>
       </c>
@@ -66044,14 +65966,13 @@
         <v>16.600000000000001</v>
       </c>
       <c r="G852">
-        <f>F852</f>
-        <v>16.600000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="H852" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>12</v>
       </c>
@@ -66068,15 +65989,8 @@
         <f>(SingleBerryDW!F853/SingleBerryFW!F853)*100</f>
         <v>17</v>
       </c>
-      <c r="G853">
-        <f>F853</f>
-        <v>17</v>
-      </c>
-      <c r="H853" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>12</v>
       </c>
@@ -66093,15 +66007,8 @@
         <f>(SingleBerryDW!F854/SingleBerryFW!F854)*100</f>
         <v>17.2</v>
       </c>
-      <c r="G854">
-        <f>F854</f>
-        <v>17.2</v>
-      </c>
-      <c r="H854" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="855" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>12</v>
       </c>
@@ -66119,7 +66026,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>12</v>
       </c>
@@ -66137,7 +66044,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>12</v>
       </c>
@@ -66155,7 +66062,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>12</v>
       </c>
@@ -66173,7 +66080,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>12</v>
       </c>
@@ -66191,7 +66098,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>12</v>
       </c>
@@ -66209,7 +66116,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>12</v>
       </c>
@@ -66227,7 +66134,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="862" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>12</v>
       </c>
@@ -66245,7 +66152,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>13</v>
       </c>
@@ -66263,7 +66170,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>13</v>
       </c>
@@ -66281,7 +66188,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>13</v>
       </c>
@@ -66299,7 +66206,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>13</v>
       </c>
@@ -66317,7 +66224,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>13</v>
       </c>
@@ -66335,7 +66242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>13</v>
       </c>
@@ -66353,7 +66260,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>13</v>
       </c>
@@ -66371,7 +66278,7 @@
         <v>16.600000000000005</v>
       </c>
     </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>13</v>
       </c>
@@ -66388,15 +66295,8 @@
         <f>(SingleBerryDW!F870/SingleBerryFW!F870)*100</f>
         <v>16.7</v>
       </c>
-      <c r="G870">
-        <f>F870</f>
-        <v>16.7</v>
-      </c>
-      <c r="H870" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="871" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>13</v>
       </c>
@@ -66413,15 +66313,8 @@
         <f>(SingleBerryDW!F871/SingleBerryFW!F871)*100</f>
         <v>17.100000000000001</v>
       </c>
-      <c r="G871">
-        <f>F871</f>
-        <v>17.100000000000001</v>
-      </c>
-      <c r="H871" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="872" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>13</v>
       </c>
@@ -66439,7 +66332,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>13</v>
       </c>
@@ -66457,7 +66350,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>13</v>
       </c>
@@ -66475,7 +66368,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>13</v>
       </c>
@@ -66493,7 +66386,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>13</v>
       </c>
@@ -66511,7 +66404,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>13</v>
       </c>
@@ -66529,7 +66422,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>13</v>
       </c>
@@ -66547,7 +66440,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>13</v>
       </c>
@@ -66565,7 +66458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>13</v>
       </c>
@@ -66582,15 +66475,8 @@
         <f>(SingleBerryDW!F880/SingleBerryFW!F880)*100</f>
         <v>17.299999999999997</v>
       </c>
-      <c r="G880">
-        <f>F880</f>
-        <v>17.299999999999997</v>
-      </c>
-      <c r="H880" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="881" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>13</v>
       </c>
@@ -66607,15 +66493,8 @@
         <f>(SingleBerryDW!F881/SingleBerryFW!F881)*100</f>
         <v>17.5</v>
       </c>
-      <c r="G881">
-        <f>F881</f>
-        <v>17.5</v>
-      </c>
-      <c r="H881" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="882" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>13</v>
       </c>
@@ -66633,7 +66512,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>13</v>
       </c>
@@ -66651,7 +66530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>13</v>
       </c>
@@ -66669,7 +66548,7 @@
         <v>7.4000000000000012</v>
       </c>
     </row>
-    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>13</v>
       </c>
@@ -66687,7 +66566,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>13</v>
       </c>
@@ -66705,7 +66584,7 @@
         <v>7.7999999999999989</v>
       </c>
     </row>
-    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>13</v>
       </c>
@@ -66723,7 +66602,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>13</v>
       </c>
@@ -66741,7 +66620,7 @@
         <v>12.800000000000002</v>
       </c>
     </row>
-    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>13</v>
       </c>
@@ -66759,7 +66638,7 @@
         <v>12.899999999999997</v>
       </c>
     </row>
-    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>13</v>
       </c>
@@ -66777,7 +66656,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>13</v>
       </c>
@@ -66795,7 +66674,7 @@
         <v>14.499999999999998</v>
       </c>
     </row>
-    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>13</v>
       </c>
@@ -66813,7 +66692,7 @@
         <v>14.700000000000003</v>
       </c>
     </row>
-    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>13</v>
       </c>
@@ -66831,7 +66710,7 @@
         <v>15.200000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>13</v>
       </c>
@@ -66849,7 +66728,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>13</v>
       </c>
@@ -66867,7 +66746,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>13</v>
       </c>
@@ -66885,7 +66764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>13</v>
       </c>
@@ -66903,7 +66782,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>13</v>
       </c>
@@ -66921,7 +66800,7 @@
         <v>16.400000000000002</v>
       </c>
     </row>
-    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>13</v>
       </c>
@@ -66939,7 +66818,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>13</v>
       </c>
@@ -66957,7 +66836,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>13</v>
       </c>
@@ -66975,7 +66854,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="902" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>13</v>
       </c>
@@ -66993,7 +66872,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="903" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>13</v>
       </c>
@@ -67011,7 +66890,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="904" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>13</v>
       </c>
@@ -67029,7 +66908,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="905" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>13</v>
       </c>
@@ -67047,7 +66926,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="906" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>13</v>
       </c>
@@ -67065,7 +66944,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="907" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>13</v>
       </c>
@@ -67083,7 +66962,7 @@
         <v>17.299999999999997</v>
       </c>
     </row>
-    <row r="908" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>13</v>
       </c>
@@ -67101,7 +66980,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="909" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>13</v>
       </c>
@@ -67118,15 +66997,8 @@
         <f>(SingleBerryDW!F909/SingleBerryFW!F909)*100</f>
         <v>16.400000000000002</v>
       </c>
-      <c r="G909">
-        <f>F909</f>
-        <v>16.400000000000002</v>
-      </c>
-      <c r="H909" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="910" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="910" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>13</v>
       </c>
@@ -67144,14 +67016,13 @@
         <v>16.8</v>
       </c>
       <c r="G910">
-        <f t="shared" ref="G910:G916" si="9">F910</f>
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="H910" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="911" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>13</v>
       </c>
@@ -67168,15 +67039,8 @@
         <f>(SingleBerryDW!F911/SingleBerryFW!F911)*100</f>
         <v>17.399999999999999</v>
       </c>
-      <c r="G911">
-        <f t="shared" si="9"/>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="H911" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="912" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="912" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>13</v>
       </c>
@@ -67193,15 +67057,8 @@
         <f>(SingleBerryDW!F912/SingleBerryFW!F912)*100</f>
         <v>16.3</v>
       </c>
-      <c r="G912">
-        <f t="shared" si="9"/>
-        <v>16.3</v>
-      </c>
-      <c r="H912" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="913" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>13</v>
       </c>
@@ -67218,15 +67075,8 @@
         <f>(SingleBerryDW!F913/SingleBerryFW!F913)*100</f>
         <v>16.7</v>
       </c>
-      <c r="G913">
-        <f t="shared" si="9"/>
-        <v>16.7</v>
-      </c>
-      <c r="H913" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="914" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="914" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>13</v>
       </c>
@@ -67243,15 +67093,8 @@
         <f>(SingleBerryDW!F914/SingleBerryFW!F914)*100</f>
         <v>16.899999999999999</v>
       </c>
-      <c r="G914">
-        <f t="shared" si="9"/>
-        <v>16.899999999999999</v>
-      </c>
-      <c r="H914" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="915" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="915" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>13</v>
       </c>
@@ -67268,15 +67111,8 @@
         <f>(SingleBerryDW!F915/SingleBerryFW!F915)*100</f>
         <v>17.599999999999998</v>
       </c>
-      <c r="G915">
-        <f t="shared" si="9"/>
-        <v>17.599999999999998</v>
-      </c>
-      <c r="H915" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="916" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>13</v>
       </c>
@@ -67293,15 +67129,8 @@
         <f>(SingleBerryDW!F916/SingleBerryFW!F916)*100</f>
         <v>16.600000000000001</v>
       </c>
-      <c r="G916">
-        <f t="shared" si="9"/>
-        <v>16.600000000000001</v>
-      </c>
-      <c r="H916" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="917" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="917" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>13</v>
       </c>
@@ -67319,7 +67148,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="918" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>13</v>
       </c>
@@ -67337,7 +67166,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="919" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>13</v>
       </c>
@@ -67355,7 +67184,7 @@
         <v>17.599999999999998</v>
       </c>
     </row>
-    <row r="920" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>13</v>
       </c>
@@ -67373,7 +67202,7 @@
         <v>17.700000000000003</v>
       </c>
     </row>
-    <row r="921" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>14</v>
       </c>
@@ -67391,7 +67220,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="922" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>14</v>
       </c>
@@ -67409,7 +67238,7 @@
         <v>12.400000000000002</v>
       </c>
     </row>
-    <row r="923" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>14</v>
       </c>
@@ -67427,7 +67256,7 @@
         <v>13.999999999999998</v>
       </c>
     </row>
-    <row r="924" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>14</v>
       </c>
@@ -67445,7 +67274,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="925" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>14</v>
       </c>
@@ -67462,15 +67291,8 @@
         <f>(SingleBerryDW!F925/SingleBerryFW!F925)*100</f>
         <v>17.5</v>
       </c>
-      <c r="G925">
-        <f>F925</f>
-        <v>17.5</v>
-      </c>
-      <c r="H925" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="926" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="926" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>14</v>
       </c>
@@ -67488,7 +67310,7 @@
         <v>17.699999999999996</v>
       </c>
     </row>
-    <row r="927" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>14</v>
       </c>
@@ -67506,7 +67328,7 @@
         <v>17.700000000000003</v>
       </c>
     </row>
-    <row r="928" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>14</v>
       </c>
@@ -67524,7 +67346,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="929" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>14</v>
       </c>
@@ -67542,7 +67364,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="930" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>14</v>
       </c>
@@ -67560,7 +67382,7 @@
         <v>14.899999999999999</v>
       </c>
     </row>
-    <row r="931" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>14</v>
       </c>
@@ -67578,7 +67400,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="932" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>14</v>
       </c>
@@ -67595,15 +67417,8 @@
         <f>(SingleBerryDW!F932/SingleBerryFW!F932)*100</f>
         <v>18.800000000000004</v>
       </c>
-      <c r="G932">
-        <f>F932</f>
-        <v>18.800000000000004</v>
-      </c>
-      <c r="H932" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="933" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="933" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>14</v>
       </c>
@@ -67621,7 +67436,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="934" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>14</v>
       </c>
@@ -67639,7 +67454,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="935" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>14</v>
       </c>
@@ -67657,7 +67472,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="936" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>14</v>
       </c>
@@ -67675,7 +67490,7 @@
         <v>8.6000000000000014</v>
       </c>
     </row>
-    <row r="937" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>14</v>
       </c>
@@ -67693,7 +67508,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="938" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>14</v>
       </c>
@@ -67711,7 +67526,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="939" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>14</v>
       </c>
@@ -67729,7 +67544,7 @@
         <v>12.799999999999997</v>
       </c>
     </row>
-    <row r="940" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>14</v>
       </c>
@@ -67747,7 +67562,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="941" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>14</v>
       </c>
@@ -67765,7 +67580,7 @@
         <v>14.900000000000002</v>
       </c>
     </row>
-    <row r="942" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>14</v>
       </c>
@@ -67783,7 +67598,7 @@
         <v>14.900000000000002</v>
       </c>
     </row>
-    <row r="943" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>14</v>
       </c>
@@ -67801,7 +67616,7 @@
         <v>14.400000000000002</v>
       </c>
     </row>
-    <row r="944" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>14</v>
       </c>
@@ -67819,7 +67634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="945" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>14</v>
       </c>
@@ -67837,7 +67652,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>14</v>
       </c>
@@ -67855,7 +67670,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="947" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>14</v>
       </c>
@@ -67873,14 +67688,13 @@
         <v>18.5</v>
       </c>
       <c r="G947">
-        <f>F947</f>
-        <v>18.5</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="H947" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="948" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>14</v>
       </c>
@@ -67897,15 +67711,8 @@
         <f>(SingleBerryDW!F948/SingleBerryFW!F948)*100</f>
         <v>18.5</v>
       </c>
-      <c r="G948">
-        <f t="shared" ref="G948:G949" si="10">F948</f>
-        <v>18.5</v>
-      </c>
-      <c r="H948" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="949" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>14</v>
       </c>
@@ -67922,15 +67729,8 @@
         <f>(SingleBerryDW!F949/SingleBerryFW!F949)*100</f>
         <v>17.299999999999997</v>
       </c>
-      <c r="G949">
-        <f t="shared" si="10"/>
-        <v>17.299999999999997</v>
-      </c>
-      <c r="H949" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="950" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>14</v>
       </c>
@@ -67948,7 +67748,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="951" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>14</v>
       </c>
@@ -67966,7 +67766,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="952" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>14</v>
       </c>
@@ -67984,7 +67784,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="953" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>14</v>
       </c>
@@ -68002,7 +67802,7 @@
         <v>18.999999999999996</v>
       </c>
     </row>
-    <row r="954" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>14</v>
       </c>
@@ -68020,7 +67820,7 @@
         <v>18.199999999999996</v>
       </c>
     </row>
-    <row r="955" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>19</v>
       </c>
@@ -68038,7 +67838,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="956" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>19</v>
       </c>
@@ -68056,7 +67856,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="957" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>19</v>
       </c>
@@ -68074,7 +67874,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="958" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>19</v>
       </c>
@@ -68092,7 +67892,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="959" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>19</v>
       </c>
@@ -68117,7 +67917,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="960" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>19</v>
       </c>
@@ -68135,7 +67935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="961" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>19</v>
       </c>
@@ -68153,7 +67953,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="962" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>15</v>
       </c>
@@ -68171,7 +67971,7 @@
         <v>8.8219087849999998</v>
       </c>
     </row>
-    <row r="963" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>15</v>
       </c>
@@ -68189,7 +67989,7 @@
         <v>11.326228609999999</v>
       </c>
     </row>
-    <row r="964" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>15</v>
       </c>
@@ -68207,7 +68007,7 @@
         <v>13.338020979999998</v>
       </c>
     </row>
-    <row r="965" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>15</v>
       </c>
@@ -68225,7 +68025,7 @@
         <v>14.397584729999998</v>
       </c>
     </row>
-    <row r="966" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>15</v>
       </c>
@@ -68243,7 +68043,7 @@
         <v>15.18128198</v>
       </c>
     </row>
-    <row r="967" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>15</v>
       </c>
@@ -68261,7 +68061,7 @@
         <v>15.203008900000004</v>
       </c>
     </row>
-    <row r="968" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>15</v>
       </c>
@@ -68279,7 +68079,7 @@
         <v>15.654528790000002</v>
       </c>
     </row>
-    <row r="969" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>15</v>
       </c>
@@ -68296,15 +68096,8 @@
         <f>(SingleBerryDW!F969/SingleBerryFW!F969)*100</f>
         <v>15.291157419999998</v>
       </c>
-      <c r="G969">
-        <f>F969</f>
-        <v>15.291157419999998</v>
-      </c>
-      <c r="H969" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="970" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="970" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>15</v>
       </c>
@@ -68322,7 +68115,7 @@
         <v>16.521215380000001</v>
       </c>
     </row>
-    <row r="971" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>15</v>
       </c>
@@ -68340,7 +68133,7 @@
         <v>16.493120660000002</v>
       </c>
     </row>
-    <row r="972" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>15</v>
       </c>
@@ -68358,7 +68151,7 @@
         <v>17.19554462</v>
       </c>
     </row>
-    <row r="973" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>15</v>
       </c>
@@ -68376,7 +68169,7 @@
         <v>10.179676189999999</v>
       </c>
     </row>
-    <row r="974" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>15</v>
       </c>
@@ -68394,7 +68187,7 @@
         <v>15.628000080000001</v>
       </c>
     </row>
-    <row r="975" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>15</v>
       </c>
@@ -68412,7 +68205,7 @@
         <v>16.63794643</v>
       </c>
     </row>
-    <row r="976" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>15</v>
       </c>
@@ -68430,7 +68223,7 @@
         <v>17.359527880000002</v>
       </c>
     </row>
-    <row r="977" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>15</v>
       </c>
@@ -68448,7 +68241,7 @@
         <v>17.60640596</v>
       </c>
     </row>
-    <row r="978" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>15</v>
       </c>
@@ -68466,7 +68259,7 @@
         <v>17.904109959999996</v>
       </c>
     </row>
-    <row r="979" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>15</v>
       </c>
@@ -68483,15 +68276,8 @@
         <f>(SingleBerryDW!F979/SingleBerryFW!F979)*100</f>
         <v>18.175619019999996</v>
       </c>
-      <c r="G979">
-        <f>F979</f>
-        <v>18.175619019999996</v>
-      </c>
-      <c r="H979" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="980" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="980" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>15</v>
       </c>
@@ -68509,7 +68295,7 @@
         <v>18.282530170000001</v>
       </c>
     </row>
-    <row r="981" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>15</v>
       </c>
@@ -68527,7 +68313,7 @@
         <v>18.609304609999999</v>
       </c>
     </row>
-    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>15</v>
       </c>
@@ -68545,7 +68331,7 @@
         <v>18.614446149999999</v>
       </c>
     </row>
-    <row r="983" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>15</v>
       </c>
@@ -68563,7 +68349,7 @@
         <v>10.13879683</v>
       </c>
     </row>
-    <row r="984" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>15</v>
       </c>
@@ -68581,7 +68367,7 @@
         <v>8.9871780220000002</v>
       </c>
     </row>
-    <row r="985" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>15</v>
       </c>
@@ -68599,7 +68385,7 @@
         <v>9.5918194680000006</v>
       </c>
     </row>
-    <row r="986" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>15</v>
       </c>
@@ -68617,7 +68403,7 @@
         <v>12.588401129999999</v>
       </c>
     </row>
-    <row r="987" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>15</v>
       </c>
@@ -68635,7 +68421,7 @@
         <v>12.309720889999999</v>
       </c>
     </row>
-    <row r="988" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>15</v>
       </c>
@@ -68653,7 +68439,7 @@
         <v>11.80923168</v>
       </c>
     </row>
-    <row r="989" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>15</v>
       </c>
@@ -68671,7 +68457,7 @@
         <v>14.489709960000003</v>
       </c>
     </row>
-    <row r="990" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>15</v>
       </c>
@@ -68689,7 +68475,7 @@
         <v>15.025325560000002</v>
       </c>
     </row>
-    <row r="991" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>15</v>
       </c>
@@ -68707,7 +68493,7 @@
         <v>14.567588619999999</v>
       </c>
     </row>
-    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>15</v>
       </c>
@@ -68725,7 +68511,7 @@
         <v>15.51031553</v>
       </c>
     </row>
-    <row r="993" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>15</v>
       </c>
@@ -68743,7 +68529,7 @@
         <v>16.65752165</v>
       </c>
     </row>
-    <row r="994" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>15</v>
       </c>
@@ -68761,7 +68547,7 @@
         <v>16.516183529999999</v>
       </c>
     </row>
-    <row r="995" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>15</v>
       </c>
@@ -68779,7 +68565,7 @@
         <v>17.496831</v>
       </c>
     </row>
-    <row r="996" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>15</v>
       </c>
@@ -68797,7 +68583,7 @@
         <v>16.263976929999998</v>
       </c>
     </row>
-    <row r="997" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>15</v>
       </c>
@@ -68815,7 +68601,7 @@
         <v>16.644487419999997</v>
       </c>
     </row>
-    <row r="998" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>15</v>
       </c>
@@ -68833,7 +68619,7 @@
         <v>17.395084430000001</v>
       </c>
     </row>
-    <row r="999" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>15</v>
       </c>
@@ -68851,7 +68637,7 @@
         <v>17.0100801</v>
       </c>
     </row>
-    <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>15</v>
       </c>
@@ -68869,7 +68655,7 @@
         <v>16.621431399999999</v>
       </c>
     </row>
-    <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>15</v>
       </c>
@@ -68887,7 +68673,7 @@
         <v>17.17040458</v>
       </c>
     </row>
-    <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>15</v>
       </c>
@@ -68905,7 +68691,7 @@
         <v>17.699558069999998</v>
       </c>
     </row>
-    <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>15</v>
       </c>
@@ -68923,7 +68709,7 @@
         <v>17.108626829999999</v>
       </c>
     </row>
-    <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>15</v>
       </c>
@@ -68941,14 +68727,13 @@
         <v>17.549679300000001</v>
       </c>
       <c r="G1004">
-        <f>F1004</f>
-        <v>17.549679300000001</v>
+        <v>17</v>
       </c>
       <c r="H1004" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>15</v>
       </c>
@@ -68966,7 +68751,7 @@
         <v>17.88764406</v>
       </c>
     </row>
-    <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>15</v>
       </c>
@@ -68984,7 +68769,7 @@
         <v>17.83926323</v>
       </c>
     </row>
-    <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>15</v>
       </c>
@@ -69002,7 +68787,7 @@
         <v>18.53625375</v>
       </c>
     </row>
-    <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>15</v>
       </c>
@@ -69020,7 +68805,7 @@
         <v>17.838277249999997</v>
       </c>
     </row>
-    <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>15</v>
       </c>
@@ -69038,7 +68823,7 @@
         <v>18.04045911</v>
       </c>
     </row>
-    <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>15</v>
       </c>
@@ -69056,7 +68841,7 @@
         <v>19.368199059999995</v>
       </c>
     </row>
-    <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>15</v>
       </c>
@@ -69074,7 +68859,7 @@
         <v>18.251158749999998</v>
       </c>
     </row>
-    <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>15</v>
       </c>
@@ -69092,7 +68877,7 @@
         <v>18.661880759999999</v>
       </c>
     </row>
-    <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>15</v>
       </c>
@@ -69110,7 +68895,7 @@
         <v>18.629489569999997</v>
       </c>
     </row>
-    <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>15</v>
       </c>
@@ -69128,7 +68913,7 @@
         <v>18.968877419999998</v>
       </c>
     </row>
-    <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>15</v>
       </c>
@@ -69146,7 +68931,7 @@
         <v>18.861529709999999</v>
       </c>
     </row>
-    <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>20</v>
       </c>
@@ -69164,7 +68949,7 @@
         <v>10.189048139999999</v>
       </c>
     </row>
-    <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>20</v>
       </c>
@@ -69182,7 +68967,7 @@
         <v>13.187815029999999</v>
       </c>
     </row>
-    <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>20</v>
       </c>
@@ -69200,7 +68985,7 @@
         <v>14.327754919999999</v>
       </c>
     </row>
-    <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>20</v>
       </c>
@@ -69218,7 +69003,7 @@
         <v>14.806242410000001</v>
       </c>
     </row>
-    <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>20</v>
       </c>
@@ -69236,7 +69021,7 @@
         <v>15.547038700000002</v>
       </c>
     </row>
-    <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>20</v>
       </c>
@@ -69254,7 +69039,7 @@
         <v>15.93281812</v>
       </c>
     </row>
-    <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>20</v>
       </c>
@@ -69272,7 +69057,7 @@
         <v>15.991152989999998</v>
       </c>
     </row>
-    <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>20</v>
       </c>
@@ -69290,7 +69075,7 @@
         <v>16.40011294</v>
       </c>
     </row>
-    <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>20</v>
       </c>
@@ -69315,7 +69100,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>20</v>
       </c>
@@ -69333,7 +69118,7 @@
         <v>17.180538370000001</v>
       </c>
     </row>
-    <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>20</v>
       </c>
@@ -69351,7 +69136,7 @@
         <v>17.54431529</v>
       </c>
     </row>
-    <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -69370,7 +69155,7 @@
         <v>11.399999999999999</v>
       </c>
     </row>
-    <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -69388,7 +69173,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -69406,7 +69191,7 @@
         <v>11.699999999999998</v>
       </c>
     </row>
-    <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -69424,7 +69209,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -69442,7 +69227,7 @@
         <v>15.100000000000001</v>
       </c>
     </row>
-    <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -69460,7 +69245,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -69478,7 +69263,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -69496,7 +69281,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -69513,15 +69298,8 @@
         <f>(SingleBerryDW!F1035/SingleBerryFW!F1035)*100</f>
         <v>15.8</v>
       </c>
-      <c r="G1035">
-        <f>F1035</f>
-        <v>15.8</v>
-      </c>
-      <c r="H1035" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1036" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -69539,7 +69317,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -69557,7 +69335,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -69575,7 +69353,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -69593,7 +69371,7 @@
         <v>13.200000000000001</v>
       </c>
     </row>
-    <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -69611,7 +69389,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -69629,7 +69407,7 @@
         <v>14.399999999999999</v>
       </c>
     </row>
-    <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -69647,7 +69425,7 @@
         <v>16.799999999999997</v>
       </c>
     </row>
-    <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -69665,7 +69443,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -69683,7 +69461,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -69701,7 +69479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -69718,15 +69496,8 @@
         <f>(SingleBerryDW!F1046/SingleBerryFW!F1046)*100</f>
         <v>18.3</v>
       </c>
-      <c r="G1046">
-        <f>F1046</f>
-        <v>18.3</v>
-      </c>
-      <c r="H1046" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1047" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -69744,7 +69515,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -69762,7 +69533,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -69781,7 +69552,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -69799,7 +69570,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -69817,7 +69588,7 @@
         <v>14.200000000000001</v>
       </c>
     </row>
-    <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -69835,7 +69606,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="1053" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -69853,7 +69624,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="1054" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -69871,7 +69642,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -69889,7 +69660,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -69907,7 +69678,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -69924,15 +69695,8 @@
         <f>(SingleBerryDW!F1057/SingleBerryFW!F1057)*100</f>
         <v>18.899999999999999</v>
       </c>
-      <c r="G1057">
-        <f>F1057</f>
-        <v>18.899999999999999</v>
-      </c>
-      <c r="H1057" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1058" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -69950,7 +69714,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -69968,7 +69732,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -69986,7 +69750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -70004,7 +69768,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -70022,7 +69786,7 @@
         <v>14.099999999999998</v>
       </c>
     </row>
-    <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -70040,7 +69804,7 @@
         <v>13.899999999999999</v>
       </c>
     </row>
-    <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
         <v>16</v>
       </c>
@@ -70058,7 +69822,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
         <v>16</v>
       </c>
@@ -70076,7 +69840,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
         <v>16</v>
       </c>
@@ -70094,7 +69858,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>16</v>
       </c>
@@ -70112,7 +69876,7 @@
         <v>17.599999999999998</v>
       </c>
     </row>
-    <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
         <v>16</v>
       </c>
@@ -70129,15 +69893,8 @@
         <f>(SingleBerryDW!F1068/SingleBerryFW!F1068)*100</f>
         <v>18.199999999999996</v>
       </c>
-      <c r="G1068">
-        <f>F1068</f>
-        <v>18.199999999999996</v>
-      </c>
-      <c r="H1068" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1069" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
         <v>16</v>
       </c>
@@ -70155,7 +69912,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>16</v>
       </c>
@@ -70173,7 +69930,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="1071" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
         <v>16</v>
       </c>
@@ -70191,7 +69948,7 @@
         <v>9.7000000000000011</v>
       </c>
     </row>
-    <row r="1072" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
         <v>16</v>
       </c>
@@ -70209,7 +69966,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
         <v>16</v>
       </c>
@@ -70227,7 +69984,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="1074" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
         <v>16</v>
       </c>
@@ -70245,7 +70002,7 @@
         <v>12.099999999999998</v>
       </c>
     </row>
-    <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
         <v>16</v>
       </c>
@@ -70263,7 +70020,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
         <v>16</v>
       </c>
@@ -70281,7 +70038,7 @@
         <v>14.400000000000002</v>
       </c>
     </row>
-    <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
         <v>16</v>
       </c>
@@ -70299,7 +70056,7 @@
         <v>14.799999999999999</v>
       </c>
     </row>
-    <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
         <v>16</v>
       </c>
@@ -70317,7 +70074,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
         <v>16</v>
       </c>
@@ -70335,14 +70092,13 @@
         <v>14.6</v>
       </c>
       <c r="G1079">
-        <f>F1079</f>
-        <v>14.6</v>
+        <v>17.16</v>
       </c>
       <c r="H1079" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
         <v>16</v>
       </c>
@@ -70360,7 +70116,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>16</v>
       </c>
@@ -70378,7 +70134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
         <v>21</v>
       </c>
@@ -70396,7 +70152,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>21</v>
       </c>
@@ -70414,7 +70170,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="1084" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>21</v>
       </c>
@@ -70432,7 +70188,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
         <v>21</v>
       </c>
@@ -70450,7 +70206,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
         <v>21</v>
       </c>
@@ -70468,7 +70224,7 @@
         <v>15.299999999999999</v>
       </c>
     </row>
-    <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
         <v>21</v>
       </c>
@@ -70486,7 +70242,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
         <v>21</v>
       </c>
@@ -70504,7 +70260,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
         <v>21</v>
       </c>
@@ -70522,7 +70278,7 @@
         <v>16.899999999999995</v>
       </c>
     </row>
-    <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
         <v>21</v>
       </c>
@@ -70540,7 +70296,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
         <v>21</v>
       </c>
@@ -70565,7 +70321,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1092" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
         <v>21</v>
       </c>
@@ -70583,7 +70339,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
         <v>17</v>
       </c>
@@ -70601,7 +70357,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
         <v>17</v>
       </c>
@@ -70619,7 +70375,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="1095" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
         <v>17</v>
       </c>
@@ -70637,7 +70393,7 @@
         <v>14.099999999999998</v>
       </c>
     </row>
-    <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
         <v>17</v>
       </c>
@@ -70655,7 +70411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
         <v>17</v>
       </c>
@@ -70673,7 +70429,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
         <v>17</v>
       </c>
@@ -70691,7 +70447,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
         <v>17</v>
       </c>
@@ -70709,7 +70465,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="1100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
         <v>17</v>
       </c>
@@ -70726,15 +70482,8 @@
         <f>(SingleBerryDW!F1100/SingleBerryFW!F1100)*100</f>
         <v>16.400000000000002</v>
       </c>
-      <c r="G1100">
-        <f>F1100</f>
-        <v>16.400000000000002</v>
-      </c>
-      <c r="H1100" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
         <v>17</v>
       </c>
@@ -70751,15 +70500,8 @@
         <f>(SingleBerryDW!F1101/SingleBerryFW!F1101)*100</f>
         <v>16.7</v>
       </c>
-      <c r="G1101">
-        <f>F1101</f>
-        <v>16.7</v>
-      </c>
-      <c r="H1101" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1102" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
         <v>17</v>
       </c>
@@ -70777,7 +70519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
         <v>17</v>
       </c>
@@ -70795,7 +70537,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
         <v>17</v>
       </c>
@@ -70813,7 +70555,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
         <v>17</v>
       </c>
@@ -70831,7 +70573,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
         <v>17</v>
       </c>
@@ -70849,7 +70591,7 @@
         <v>13.999999999999998</v>
       </c>
     </row>
-    <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
         <v>17</v>
       </c>
@@ -70867,7 +70609,7 @@
         <v>15.299999999999999</v>
       </c>
     </row>
-    <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
         <v>17</v>
       </c>
@@ -70885,7 +70627,7 @@
         <v>15.900000000000002</v>
       </c>
     </row>
-    <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
         <v>17</v>
       </c>
@@ -70903,7 +70645,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
         <v>17</v>
       </c>
@@ -70921,7 +70663,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
         <v>17</v>
       </c>
@@ -70938,15 +70680,8 @@
         <f>(SingleBerryDW!F1111/SingleBerryFW!F1111)*100</f>
         <v>17.2</v>
       </c>
-      <c r="G1111">
-        <f>F1111</f>
-        <v>17.2</v>
-      </c>
-      <c r="H1111" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
         <v>17</v>
       </c>
@@ -70963,15 +70698,8 @@
         <f>(SingleBerryDW!F1112/SingleBerryFW!F1112)*100</f>
         <v>17.399999999999999</v>
       </c>
-      <c r="G1112">
-        <f>F1112</f>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="H1112" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
         <v>17</v>
       </c>
@@ -70989,7 +70717,7 @@
         <v>17.399999999999995</v>
       </c>
     </row>
-    <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
         <v>17</v>
       </c>
@@ -71007,7 +70735,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
         <v>17</v>
       </c>
@@ -71025,7 +70753,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>17</v>
       </c>
@@ -71043,7 +70771,7 @@
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>17</v>
       </c>
@@ -71061,7 +70789,7 @@
         <v>14.399999999999999</v>
       </c>
     </row>
-    <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
         <v>17</v>
       </c>
@@ -71079,7 +70807,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
         <v>17</v>
       </c>
@@ -71097,7 +70825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
         <v>17</v>
       </c>
@@ -71115,7 +70843,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
         <v>17</v>
       </c>
@@ -71133,7 +70861,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
         <v>17</v>
       </c>
@@ -71150,15 +70878,8 @@
         <f>(SingleBerryDW!F1122/SingleBerryFW!F1122)*100</f>
         <v>18.699999999999996</v>
       </c>
-      <c r="G1122">
-        <f>F1122</f>
-        <v>18.699999999999996</v>
-      </c>
-      <c r="H1122" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
         <v>17</v>
       </c>
@@ -71175,15 +70896,8 @@
         <f>(SingleBerryDW!F1123/SingleBerryFW!F1123)*100</f>
         <v>18.2</v>
       </c>
-      <c r="G1123">
-        <f>F1123</f>
-        <v>18.2</v>
-      </c>
-      <c r="H1123" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
         <v>17</v>
       </c>
@@ -71201,7 +70915,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
         <v>17</v>
       </c>
@@ -71219,7 +70933,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
         <v>17</v>
       </c>
@@ -71237,7 +70951,7 @@
         <v>9.0000000000000018</v>
       </c>
     </row>
-    <row r="1127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
         <v>17</v>
       </c>
@@ -71255,7 +70969,7 @@
         <v>11.300000000000002</v>
       </c>
     </row>
-    <row r="1128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
         <v>17</v>
       </c>
@@ -71273,7 +70987,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
         <v>17</v>
       </c>
@@ -71291,7 +71005,7 @@
         <v>15.299999999999999</v>
       </c>
     </row>
-    <row r="1130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>17</v>
       </c>
@@ -71309,7 +71023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
         <v>17</v>
       </c>
@@ -71327,7 +71041,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="1132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
         <v>17</v>
       </c>
@@ -71345,7 +71059,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="1133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
         <v>17</v>
       </c>
@@ -71362,15 +71076,8 @@
         <f>(SingleBerryDW!F1133/SingleBerryFW!F1133)*100</f>
         <v>17.5</v>
       </c>
-      <c r="G1133">
-        <f>F1133</f>
-        <v>17.5</v>
-      </c>
-      <c r="H1133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
         <v>17</v>
       </c>
@@ -71387,15 +71094,8 @@
         <f>(SingleBerryDW!F1134/SingleBerryFW!F1134)*100</f>
         <v>17.8</v>
       </c>
-      <c r="G1134">
-        <f>F1134</f>
-        <v>17.8</v>
-      </c>
-      <c r="H1134" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1135" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
         <v>17</v>
       </c>
@@ -71413,7 +71113,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
         <v>17</v>
       </c>
@@ -71431,7 +71131,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
         <v>17</v>
       </c>
@@ -71449,7 +71149,7 @@
         <v>8.2999999999999989</v>
       </c>
     </row>
-    <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
         <v>17</v>
       </c>
@@ -71467,7 +71167,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="1139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
         <v>17</v>
       </c>
@@ -71485,7 +71185,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="1140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
         <v>17</v>
       </c>
@@ -71503,7 +71203,7 @@
         <v>14.299999999999999</v>
       </c>
     </row>
-    <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
         <v>17</v>
       </c>
@@ -71521,7 +71221,7 @@
         <v>15.000000000000002</v>
       </c>
     </row>
-    <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
         <v>17</v>
       </c>
@@ -71539,7 +71239,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
         <v>17</v>
       </c>
@@ -71557,7 +71257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
         <v>17</v>
       </c>
@@ -71575,14 +71275,13 @@
         <v>15.6</v>
       </c>
       <c r="G1144">
-        <f>F1144</f>
-        <v>15.6</v>
+        <v>17</v>
       </c>
       <c r="H1144" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="1145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
         <v>17</v>
       </c>
@@ -71599,15 +71298,8 @@
         <f>(SingleBerryDW!F1145/SingleBerryFW!F1145)*100</f>
         <v>15.4</v>
       </c>
-      <c r="G1145">
-        <f>F1145</f>
-        <v>15.4</v>
-      </c>
-      <c r="H1145" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
         <v>17</v>
       </c>
@@ -71625,7 +71317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
         <v>17</v>
       </c>
@@ -71643,7 +71335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
         <v>22</v>
       </c>
@@ -71661,7 +71353,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
         <v>22</v>
       </c>
@@ -71679,7 +71371,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
         <v>22</v>
       </c>
@@ -71697,7 +71389,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
         <v>22</v>
       </c>
@@ -71715,7 +71407,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
         <v>22</v>
       </c>
@@ -71733,7 +71425,7 @@
         <v>17.200000000000003</v>
       </c>
     </row>
-    <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
         <v>22</v>
       </c>
@@ -71751,7 +71443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
         <v>22</v>
       </c>
@@ -71769,7 +71461,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
         <v>22</v>
       </c>
@@ -71787,7 +71479,7 @@
         <v>18.500000000000004</v>
       </c>
     </row>
-    <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
         <v>22</v>
       </c>
@@ -71812,7 +71504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
         <v>22</v>
       </c>
@@ -71830,7 +71522,7 @@
         <v>19.300000000000004</v>
       </c>
     </row>
-    <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
         <v>22</v>
       </c>
@@ -71955,13 +71647,6 @@
         <f>(SingleBerryDW!F1164/SingleBerryFW!F1164)*100</f>
         <v>15.5</v>
       </c>
-      <c r="G1164">
-        <f>F1164</f>
-        <v>15.5</v>
-      </c>
-      <c r="H1164" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
@@ -71980,13 +71665,6 @@
         <f>(SingleBerryDW!F1165/SingleBerryFW!F1165)*100</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="G1165">
-        <f>F1165</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="H1165" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
@@ -72042,7 +71720,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
         <v>18</v>
       </c>
@@ -72060,7 +71738,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
         <v>18</v>
       </c>
@@ -72078,7 +71756,7 @@
         <v>8.8000000000000025</v>
       </c>
     </row>
-    <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
         <v>18</v>
       </c>
@@ -72096,7 +71774,7 @@
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="1172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
         <v>18</v>
       </c>
@@ -72114,7 +71792,7 @@
         <v>13.600000000000001</v>
       </c>
     </row>
-    <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
         <v>18</v>
       </c>
@@ -72132,7 +71810,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
         <v>18</v>
       </c>
@@ -72150,7 +71828,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="1175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
         <v>18</v>
       </c>
@@ -72167,15 +71845,8 @@
         <f>(SingleBerryDW!F1175/SingleBerryFW!F1175)*100</f>
         <v>17</v>
       </c>
-      <c r="G1175">
-        <f>F1175</f>
-        <v>17</v>
-      </c>
-      <c r="H1175" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
         <v>18</v>
       </c>
@@ -72193,7 +71864,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="1177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
         <v>18</v>
       </c>
@@ -72211,7 +71882,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="1178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
         <v>18</v>
       </c>
@@ -72229,7 +71900,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="1179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
         <v>18</v>
       </c>
@@ -72247,7 +71918,7 @@
         <v>18.099999999999998</v>
       </c>
     </row>
-    <row r="1180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
         <v>18</v>
       </c>
@@ -72265,7 +71936,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
         <v>18</v>
       </c>
@@ -72283,7 +71954,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="1182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
         <v>18</v>
       </c>
@@ -72301,7 +71972,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
         <v>18</v>
       </c>
@@ -72319,7 +71990,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="1184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
         <v>18</v>
       </c>
@@ -72337,7 +72008,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="1185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
         <v>18</v>
       </c>
@@ -72355,7 +72026,7 @@
         <v>16.400000000000002</v>
       </c>
     </row>
-    <row r="1186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
         <v>18</v>
       </c>
@@ -72372,15 +72043,8 @@
         <f>(SingleBerryDW!F1186/SingleBerryFW!F1186)*100</f>
         <v>16.8</v>
       </c>
-      <c r="G1186">
-        <f>F1186</f>
-        <v>16.8</v>
-      </c>
-      <c r="H1186" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
         <v>18</v>
       </c>
@@ -72397,15 +72061,8 @@
         <f>(SingleBerryDW!F1187/SingleBerryFW!F1187)*100</f>
         <v>17.2</v>
       </c>
-      <c r="G1187">
-        <f>F1187</f>
-        <v>17.2</v>
-      </c>
-      <c r="H1187" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1188" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
         <v>18</v>
       </c>
@@ -72423,7 +72080,7 @@
         <v>17.699999999999996</v>
       </c>
     </row>
-    <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
         <v>18</v>
       </c>
@@ -72441,7 +72098,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="1190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
         <v>18</v>
       </c>
@@ -72459,7 +72116,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
         <v>18</v>
       </c>
@@ -72477,7 +72134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
         <v>18</v>
       </c>
@@ -72495,7 +72152,7 @@
         <v>8.3000000000000025</v>
       </c>
     </row>
-    <row r="1193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
         <v>18</v>
       </c>
@@ -72513,7 +72170,7 @@
         <v>11.700000000000001</v>
       </c>
     </row>
-    <row r="1194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
         <v>18</v>
       </c>
@@ -72531,7 +72188,7 @@
         <v>13.600000000000001</v>
       </c>
     </row>
-    <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
         <v>18</v>
       </c>
@@ -72549,7 +72206,7 @@
         <v>15.000000000000002</v>
       </c>
     </row>
-    <row r="1196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
         <v>18</v>
       </c>
@@ -72567,7 +72224,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="1197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
         <v>18</v>
       </c>
@@ -72584,15 +72241,8 @@
         <f>(SingleBerryDW!F1197/SingleBerryFW!F1197)*100</f>
         <v>16.3</v>
       </c>
-      <c r="G1197">
-        <f>F1197</f>
-        <v>16.3</v>
-      </c>
-      <c r="H1197" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1198" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
         <v>18</v>
       </c>
@@ -72609,15 +72259,8 @@
         <f>(SingleBerryDW!F1198/SingleBerryFW!F1198)*100</f>
         <v>16.2</v>
       </c>
-      <c r="G1198">
-        <f>F1198</f>
-        <v>16.2</v>
-      </c>
-      <c r="H1198" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1199" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
         <v>18</v>
       </c>
@@ -72635,7 +72278,7 @@
         <v>17.099999999999998</v>
       </c>
     </row>
-    <row r="1200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
         <v>18</v>
       </c>
@@ -72821,13 +72464,6 @@
         <f>(SingleBerryDW!F1209/SingleBerryFW!F1209)*100</f>
         <v>16.5</v>
       </c>
-      <c r="G1209">
-        <f>F1209</f>
-        <v>16.5</v>
-      </c>
-      <c r="H1209" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="1210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
@@ -72901,7 +72537,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
         <v>23</v>
       </c>
@@ -72919,7 +72555,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="1215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
         <v>23</v>
       </c>
@@ -72937,7 +72573,7 @@
         <v>13.100000000000001</v>
       </c>
     </row>
-    <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
         <v>23</v>
       </c>
@@ -72955,7 +72591,7 @@
         <v>14.900000000000002</v>
       </c>
     </row>
-    <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
         <v>23</v>
       </c>
@@ -72973,7 +72609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
         <v>23</v>
       </c>
@@ -72991,7 +72627,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
         <v>23</v>
       </c>
@@ -73009,7 +72645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
         <v>23</v>
       </c>
@@ -73027,14 +72663,13 @@
         <v>17.3</v>
       </c>
       <c r="G1220">
-        <f>F1220</f>
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="H1220" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="1221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
         <v>23</v>
       </c>
@@ -73051,15 +72686,8 @@
         <f>(SingleBerryDW!F1221/SingleBerryFW!F1221)*100</f>
         <v>17.7</v>
       </c>
-      <c r="G1221">
-        <f>F1221</f>
-        <v>17.7</v>
-      </c>
-      <c r="H1221" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1222" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
         <v>23</v>
       </c>
@@ -73077,7 +72705,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
         <v>23</v>
       </c>
@@ -73095,7 +72723,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="1224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
         <v>23</v>
       </c>
@@ -73129,19 +72757,6 @@
   <autoFilter ref="A1:A1228" xr:uid="{B3CAF195-1F50-4308-BA2B-F7BFA06853CA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="KKHW2020"/>
-        <filter val="KKHW2021"/>
-        <filter val="KKHW2022"/>
-        <filter val="KKHW2023"/>
-        <filter val="KKHW2024"/>
-        <filter val="TPHW2016"/>
-        <filter val="TPHW2017"/>
-        <filter val="TPHW2018"/>
-        <filter val="TPHW2019"/>
-        <filter val="TPHW2020"/>
-        <filter val="TPHW2021"/>
-        <filter val="TPHW2022"/>
-        <filter val="TPHW2023"/>
         <filter val="TPHW2024"/>
       </filters>
     </filterColumn>

--- a/Prototypes/KiwiFruit/Yield.xlsx
+++ b/Prototypes/KiwiFruit/Yield.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3135AD3-433A-4E72-B992-39247A7EEA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB816A3-5401-4904-B79C-643700A0FBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,12 +184,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -219,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -228,6 +234,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -61940,38 +61948,38 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A630" t="s">
+    <row r="630" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B630" s="2">
+      <c r="B630" s="6">
         <v>42493</v>
       </c>
-      <c r="C630">
+      <c r="C630" s="7">
         <v>2016</v>
       </c>
-      <c r="E630" t="s">
-        <v>6</v>
-      </c>
-      <c r="F630">
+      <c r="E630" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F630" s="7">
         <f>(SingleBerryDW!F630/SingleBerryFW!F630)*100</f>
         <v>15.7</v>
       </c>
     </row>
-    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A631" t="s">
+    <row r="631" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B631" s="2">
+      <c r="B631" s="6">
         <v>42493</v>
       </c>
-      <c r="C631">
+      <c r="C631" s="7">
         <v>2016</v>
       </c>
-      <c r="E631" t="s">
-        <v>6</v>
-      </c>
-      <c r="F631">
+      <c r="E631" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F631" s="7">
         <f>(SingleBerryDW!F631/SingleBerryFW!F631)*100</f>
         <v>16.5</v>
       </c>
@@ -62228,20 +62236,20 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A646" t="s">
+    <row r="646" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B646" s="2">
+      <c r="B646" s="6">
         <v>42496</v>
       </c>
-      <c r="C646">
+      <c r="C646" s="7">
         <v>2016</v>
       </c>
-      <c r="E646" t="s">
-        <v>6</v>
-      </c>
-      <c r="F646">
+      <c r="E646" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F646" s="7">
         <f>(SingleBerryDW!F646/SingleBerryFW!F646)*100</f>
         <v>16.8</v>
       </c>
@@ -62876,27 +62884,28 @@
         <v>15.699999999999998</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A682" t="s">
+    <row r="682" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B682" s="2">
+      <c r="B682" s="6">
         <v>42494</v>
       </c>
-      <c r="C682">
+      <c r="C682" s="7">
         <v>2016</v>
       </c>
-      <c r="E682" t="s">
-        <v>6</v>
-      </c>
-      <c r="F682">
+      <c r="E682" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F682" s="7">
         <f>(SingleBerryDW!F682/SingleBerryFW!F682)*100</f>
         <v>16.100000000000001</v>
       </c>
-      <c r="G682">
-        <v>16.3</v>
-      </c>
-      <c r="H682" t="s">
+      <c r="G682" s="7">
+        <f>AVERAGE(F630:F631,F646,F682)</f>
+        <v>16.274999999999999</v>
+      </c>
+      <c r="H682" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -63458,56 +63467,56 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A714" t="s">
+    <row r="714" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A714" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B714" s="2">
+      <c r="B714" s="6">
         <v>42858</v>
       </c>
-      <c r="C714">
+      <c r="C714" s="7">
         <v>2017</v>
       </c>
-      <c r="E714" t="s">
-        <v>6</v>
-      </c>
-      <c r="F714">
+      <c r="E714" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F714" s="7">
         <f>(SingleBerryDW!F714/SingleBerryFW!F714)*100</f>
         <v>15</v>
       </c>
     </row>
-    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A715" t="s">
+    <row r="715" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A715" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B715" s="2">
+      <c r="B715" s="6">
         <v>42871</v>
       </c>
-      <c r="C715">
+      <c r="C715" s="7">
         <v>2017</v>
       </c>
-      <c r="E715" t="s">
-        <v>6</v>
-      </c>
-      <c r="F715">
+      <c r="E715" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F715" s="7">
         <f>(SingleBerryDW!F715/SingleBerryFW!F715)*100</f>
         <v>16.8</v>
       </c>
     </row>
-    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A716" t="s">
+    <row r="716" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A716" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B716" s="2">
+      <c r="B716" s="6">
         <v>42871</v>
       </c>
-      <c r="C716">
+      <c r="C716" s="7">
         <v>2017</v>
       </c>
-      <c r="E716" t="s">
-        <v>6</v>
-      </c>
-      <c r="F716">
+      <c r="E716" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F716" s="7">
         <f>(SingleBerryDW!F716/SingleBerryFW!F716)*100</f>
         <v>16.2</v>
       </c>
@@ -63764,38 +63773,38 @@
         <v>16.900000000000002</v>
       </c>
     </row>
-    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A731" t="s">
+    <row r="731" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A731" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B731" s="2">
+      <c r="B731" s="6">
         <v>42859</v>
       </c>
-      <c r="C731">
+      <c r="C731" s="7">
         <v>2017</v>
       </c>
-      <c r="E731" t="s">
-        <v>6</v>
-      </c>
-      <c r="F731">
+      <c r="E731" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F731" s="7">
         <f>(SingleBerryDW!F731/SingleBerryFW!F731)*100</f>
         <v>17</v>
       </c>
     </row>
-    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A732" t="s">
+    <row r="732" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A732" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B732" s="2">
+      <c r="B732" s="6">
         <v>42873</v>
       </c>
-      <c r="C732">
+      <c r="C732" s="7">
         <v>2017</v>
       </c>
-      <c r="E732" t="s">
-        <v>6</v>
-      </c>
-      <c r="F732">
+      <c r="E732" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F732" s="7">
         <f>(SingleBerryDW!F732/SingleBerryFW!F732)*100</f>
         <v>17.7</v>
       </c>
@@ -64466,62 +64475,63 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A770" t="s">
+    <row r="770" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A770" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B770" s="2">
+      <c r="B770" s="6">
         <v>42860</v>
       </c>
-      <c r="C770">
+      <c r="C770" s="7">
         <v>2017</v>
       </c>
-      <c r="E770" t="s">
-        <v>6</v>
-      </c>
-      <c r="F770">
+      <c r="E770" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F770" s="7">
         <f>(SingleBerryDW!F770/SingleBerryFW!F770)*100</f>
         <v>16.800000000000004</v>
       </c>
-      <c r="G770">
-        <v>16.5</v>
-      </c>
-      <c r="H770" t="s">
+      <c r="G770" s="7">
+        <f>AVERAGE(F770:F772,F731:F732,F714:F716)</f>
+        <v>16.799999999999997</v>
+      </c>
+      <c r="H770" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A771" t="s">
+    <row r="771" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A771" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B771" s="2">
+      <c r="B771" s="6">
         <v>42860</v>
       </c>
-      <c r="C771">
+      <c r="C771" s="7">
         <v>2017</v>
       </c>
-      <c r="E771" t="s">
-        <v>6</v>
-      </c>
-      <c r="F771">
+      <c r="E771" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F771" s="7">
         <f>(SingleBerryDW!F771/SingleBerryFW!F771)*100</f>
         <v>17.199999999999996</v>
       </c>
     </row>
-    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A772" t="s">
+    <row r="772" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A772" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B772" s="2">
+      <c r="B772" s="6">
         <v>42872</v>
       </c>
-      <c r="C772">
+      <c r="C772" s="7">
         <v>2017</v>
       </c>
-      <c r="E772" t="s">
-        <v>6</v>
-      </c>
-      <c r="F772">
+      <c r="E772" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F772" s="7">
         <f>(SingleBerryDW!F772/SingleBerryFW!F772)*100</f>
         <v>17.699999999999996</v>
       </c>
@@ -65048,38 +65058,38 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A802" t="s">
+    <row r="802" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A802" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B802" s="2">
+      <c r="B802" s="6">
         <v>43221</v>
       </c>
-      <c r="C802">
+      <c r="C802" s="7">
         <v>2018</v>
       </c>
-      <c r="E802" t="s">
-        <v>6</v>
-      </c>
-      <c r="F802">
+      <c r="E802" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F802" s="7">
         <f>(SingleBerryDW!F802/SingleBerryFW!F802)*100</f>
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="803" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A803" t="s">
+    <row r="803" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A803" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B803" s="2">
+      <c r="B803" s="6">
         <v>43221</v>
       </c>
-      <c r="C803">
+      <c r="C803" s="7">
         <v>2018</v>
       </c>
-      <c r="E803" t="s">
-        <v>6</v>
-      </c>
-      <c r="F803">
+      <c r="E803" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F803" s="7">
         <f>(SingleBerryDW!F803/SingleBerryFW!F803)*100</f>
         <v>16.600000000000001</v>
       </c>
@@ -65300,20 +65310,20 @@
         <v>16.800000000000004</v>
       </c>
     </row>
-    <row r="816" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A816" t="s">
+    <row r="816" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A816" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B816" s="2">
+      <c r="B816" s="6">
         <v>43221</v>
       </c>
-      <c r="C816">
+      <c r="C816" s="7">
         <v>2018</v>
       </c>
-      <c r="E816" t="s">
-        <v>6</v>
-      </c>
-      <c r="F816">
+      <c r="E816" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F816" s="7">
         <f>(SingleBerryDW!F816/SingleBerryFW!F816)*100</f>
         <v>17</v>
       </c>
@@ -65930,80 +65940,81 @@
         <v>17.100000000000005</v>
       </c>
     </row>
-    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A851" t="s">
+    <row r="851" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A851" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B851" s="2">
+      <c r="B851" s="6">
         <v>43221</v>
       </c>
-      <c r="C851">
+      <c r="C851" s="7">
         <v>2018</v>
       </c>
-      <c r="E851" t="s">
-        <v>6</v>
-      </c>
-      <c r="F851">
+      <c r="E851" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F851" s="7">
         <f>(SingleBerryDW!F851/SingleBerryFW!F851)*100</f>
         <v>15.7</v>
       </c>
     </row>
-    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A852" t="s">
+    <row r="852" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A852" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B852" s="2">
+      <c r="B852" s="6">
         <v>43221</v>
       </c>
-      <c r="C852">
+      <c r="C852" s="7">
         <v>2018</v>
       </c>
-      <c r="E852" t="s">
-        <v>6</v>
-      </c>
-      <c r="F852">
+      <c r="E852" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F852" s="7">
         <f>(SingleBerryDW!F852/SingleBerryFW!F852)*100</f>
         <v>16.600000000000001</v>
       </c>
-      <c r="G852">
-        <v>16.8</v>
-      </c>
-      <c r="H852" t="s">
+      <c r="G852" s="7">
+        <f>AVERAGE(F851:F854,F816,F802:F803)</f>
+        <v>16.785714285714285</v>
+      </c>
+      <c r="H852" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A853" t="s">
+    <row r="853" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A853" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B853" s="2">
+      <c r="B853" s="6">
         <v>43221</v>
       </c>
-      <c r="C853">
+      <c r="C853" s="7">
         <v>2018</v>
       </c>
-      <c r="E853" t="s">
-        <v>6</v>
-      </c>
-      <c r="F853">
+      <c r="E853" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F853" s="7">
         <f>(SingleBerryDW!F853/SingleBerryFW!F853)*100</f>
         <v>17</v>
       </c>
     </row>
-    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A854" t="s">
+    <row r="854" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A854" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B854" s="2">
+      <c r="B854" s="6">
         <v>43221</v>
       </c>
-      <c r="C854">
+      <c r="C854" s="7">
         <v>2018</v>
       </c>
-      <c r="E854" t="s">
-        <v>6</v>
-      </c>
-      <c r="F854">
+      <c r="E854" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F854" s="7">
         <f>(SingleBerryDW!F854/SingleBerryFW!F854)*100</f>
         <v>17.2</v>
       </c>
@@ -66296,20 +66307,20 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="871" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A871" t="s">
+    <row r="871" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A871" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B871" s="2">
+      <c r="B871" s="6">
         <v>43584</v>
       </c>
-      <c r="C871">
+      <c r="C871" s="7">
         <v>2019</v>
       </c>
-      <c r="E871" t="s">
-        <v>6</v>
-      </c>
-      <c r="F871">
+      <c r="E871" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F871" s="7">
         <f>(SingleBerryDW!F871/SingleBerryFW!F871)*100</f>
         <v>17.100000000000001</v>
       </c>
@@ -66476,20 +66487,20 @@
         <v>17.299999999999997</v>
       </c>
     </row>
-    <row r="881" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A881" t="s">
+    <row r="881" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A881" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B881" s="2">
+      <c r="B881" s="6">
         <v>43584</v>
       </c>
-      <c r="C881">
+      <c r="C881" s="7">
         <v>2019</v>
       </c>
-      <c r="E881" t="s">
-        <v>6</v>
-      </c>
-      <c r="F881">
+      <c r="E881" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F881" s="7">
         <f>(SingleBerryDW!F881/SingleBerryFW!F881)*100</f>
         <v>17.5</v>
       </c>
@@ -67016,7 +67027,8 @@
         <v>16.8</v>
       </c>
       <c r="G910">
-        <v>17</v>
+        <f>AVERAGE(F871,F881,F913:F916)</f>
+        <v>17.066666666666663</v>
       </c>
       <c r="H910" t="s">
         <v>27</v>
@@ -67058,74 +67070,74 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A913" t="s">
+    <row r="913" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A913" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B913" s="2">
+      <c r="B913" s="6">
         <v>43584</v>
       </c>
-      <c r="C913">
+      <c r="C913" s="7">
         <v>2019</v>
       </c>
-      <c r="E913" t="s">
-        <v>6</v>
-      </c>
-      <c r="F913">
+      <c r="E913" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F913" s="7">
         <f>(SingleBerryDW!F913/SingleBerryFW!F913)*100</f>
         <v>16.7</v>
       </c>
     </row>
-    <row r="914" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A914" t="s">
+    <row r="914" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A914" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B914" s="2">
+      <c r="B914" s="6">
         <v>43584</v>
       </c>
-      <c r="C914">
+      <c r="C914" s="7">
         <v>2019</v>
       </c>
-      <c r="E914" t="s">
-        <v>6</v>
-      </c>
-      <c r="F914">
+      <c r="E914" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F914" s="7">
         <f>(SingleBerryDW!F914/SingleBerryFW!F914)*100</f>
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="915" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A915" t="s">
+    <row r="915" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A915" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B915" s="2">
+      <c r="B915" s="6">
         <v>43584</v>
       </c>
-      <c r="C915">
+      <c r="C915" s="7">
         <v>2019</v>
       </c>
-      <c r="E915" t="s">
-        <v>6</v>
-      </c>
-      <c r="F915">
+      <c r="E915" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F915" s="7">
         <f>(SingleBerryDW!F915/SingleBerryFW!F915)*100</f>
         <v>17.599999999999998</v>
       </c>
     </row>
-    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A916" t="s">
+    <row r="916" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A916" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B916" s="2">
+      <c r="B916" s="6">
         <v>43584</v>
       </c>
-      <c r="C916">
+      <c r="C916" s="7">
         <v>2019</v>
       </c>
-      <c r="E916" t="s">
-        <v>6</v>
-      </c>
-      <c r="F916">
+      <c r="E916" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F916" s="7">
         <f>(SingleBerryDW!F916/SingleBerryFW!F916)*100</f>
         <v>16.600000000000001</v>
       </c>
@@ -67256,38 +67268,38 @@
         <v>13.999999999999998</v>
       </c>
     </row>
-    <row r="924" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A924" t="s">
+    <row r="924" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A924" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B924" s="2">
+      <c r="B924" s="6">
         <v>43906</v>
       </c>
-      <c r="C924">
+      <c r="C924" s="7">
         <v>2020</v>
       </c>
-      <c r="E924" t="s">
-        <v>6</v>
-      </c>
-      <c r="F924">
+      <c r="E924" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F924" s="7">
         <f>(SingleBerryDW!F924/SingleBerryFW!F924)*100</f>
         <v>15.5</v>
       </c>
     </row>
-    <row r="925" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A925" t="s">
+    <row r="925" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A925" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B925" s="2">
+      <c r="B925" s="6">
         <v>43950</v>
       </c>
-      <c r="C925">
+      <c r="C925" s="7">
         <v>2020</v>
       </c>
-      <c r="E925" t="s">
-        <v>6</v>
-      </c>
-      <c r="F925">
+      <c r="E925" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F925" s="7">
         <f>(SingleBerryDW!F925/SingleBerryFW!F925)*100</f>
         <v>17.5</v>
       </c>
@@ -67382,38 +67394,38 @@
         <v>14.899999999999999</v>
       </c>
     </row>
-    <row r="931" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A931" t="s">
+    <row r="931" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A931" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B931" s="2">
+      <c r="B931" s="6">
         <v>43907</v>
       </c>
-      <c r="C931">
+      <c r="C931" s="7">
         <v>2020</v>
       </c>
-      <c r="E931" t="s">
-        <v>6</v>
-      </c>
-      <c r="F931">
+      <c r="E931" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F931" s="7">
         <f>(SingleBerryDW!F931/SingleBerryFW!F931)*100</f>
         <v>16.5</v>
       </c>
     </row>
-    <row r="932" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A932" t="s">
+    <row r="932" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A932" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B932" s="2">
+      <c r="B932" s="6">
         <v>43951</v>
       </c>
-      <c r="C932">
+      <c r="C932" s="7">
         <v>2020</v>
       </c>
-      <c r="E932" t="s">
-        <v>6</v>
-      </c>
-      <c r="F932">
+      <c r="E932" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F932" s="7">
         <f>(SingleBerryDW!F932/SingleBerryFW!F932)*100</f>
         <v>18.800000000000004</v>
       </c>
@@ -67652,80 +67664,80 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A946" t="s">
+    <row r="946" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A946" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B946" s="2">
+      <c r="B946" s="6">
         <v>43907</v>
       </c>
-      <c r="C946">
+      <c r="C946" s="7">
         <v>2020</v>
       </c>
-      <c r="E946" t="s">
-        <v>6</v>
-      </c>
-      <c r="F946">
+      <c r="E946" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F946" s="7">
         <f>(SingleBerryDW!F946/SingleBerryFW!F946)*100</f>
         <v>15.4</v>
       </c>
     </row>
-    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A947" t="s">
+    <row r="947" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A947" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B947" s="2">
+      <c r="B947" s="6">
         <v>43950</v>
       </c>
-      <c r="C947">
+      <c r="C947" s="7">
         <v>2020</v>
       </c>
-      <c r="E947" t="s">
-        <v>6</v>
-      </c>
-      <c r="F947">
+      <c r="E947" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F947" s="7">
         <f>(SingleBerryDW!F947/SingleBerryFW!F947)*100</f>
         <v>18.5</v>
       </c>
-      <c r="G947">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="H947" t="s">
+      <c r="G947" s="7">
+        <v>17.25</v>
+      </c>
+      <c r="H947" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A948" t="s">
+    <row r="948" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A948" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B948" s="2">
+      <c r="B948" s="6">
         <v>43950</v>
       </c>
-      <c r="C948">
+      <c r="C948" s="7">
         <v>2020</v>
       </c>
-      <c r="E948" t="s">
-        <v>6</v>
-      </c>
-      <c r="F948">
+      <c r="E948" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F948" s="7">
         <f>(SingleBerryDW!F948/SingleBerryFW!F948)*100</f>
         <v>18.5</v>
       </c>
     </row>
-    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A949" t="s">
+    <row r="949" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A949" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B949" s="2">
+      <c r="B949" s="6">
         <v>43950</v>
       </c>
-      <c r="C949">
+      <c r="C949" s="7">
         <v>2020</v>
       </c>
-      <c r="E949" t="s">
-        <v>6</v>
-      </c>
-      <c r="F949">
+      <c r="E949" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F949" s="7">
         <f>(SingleBerryDW!F949/SingleBerryFW!F949)*100</f>
         <v>17.299999999999997</v>
       </c>
@@ -68079,20 +68091,20 @@
         <v>15.654528790000002</v>
       </c>
     </row>
-    <row r="969" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A969" t="s">
+    <row r="969" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A969" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B969" s="2">
+      <c r="B969" s="6">
         <v>44315</v>
       </c>
-      <c r="C969">
+      <c r="C969" s="7">
         <v>2021</v>
       </c>
-      <c r="E969" t="s">
-        <v>6</v>
-      </c>
-      <c r="F969">
+      <c r="E969" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F969" s="7">
         <f>(SingleBerryDW!F969/SingleBerryFW!F969)*100</f>
         <v>15.291157419999998</v>
       </c>
@@ -68259,20 +68271,20 @@
         <v>17.904109959999996</v>
       </c>
     </row>
-    <row r="979" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A979" t="s">
+    <row r="979" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A979" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B979" s="2">
+      <c r="B979" s="6">
         <v>44315</v>
       </c>
-      <c r="C979">
+      <c r="C979" s="7">
         <v>2021</v>
       </c>
-      <c r="E979" t="s">
-        <v>6</v>
-      </c>
-      <c r="F979">
+      <c r="E979" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F979" s="7">
         <f>(SingleBerryDW!F979/SingleBerryFW!F979)*100</f>
         <v>18.175619019999996</v>
       </c>
@@ -68709,27 +68721,28 @@
         <v>17.108626829999999</v>
       </c>
     </row>
-    <row r="1004" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A1004" t="s">
+    <row r="1004" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1004" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B1004" s="2">
+      <c r="B1004" s="6">
         <v>44315</v>
       </c>
-      <c r="C1004">
+      <c r="C1004" s="7">
         <v>2021</v>
       </c>
-      <c r="E1004" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1004">
+      <c r="E1004" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1004" s="7">
         <f>(SingleBerryDW!F1004/SingleBerryFW!F1004)*100</f>
         <v>17.549679300000001</v>
       </c>
-      <c r="G1004">
-        <v>17</v>
-      </c>
-      <c r="H1004" t="s">
+      <c r="G1004" s="7">
+        <f>AVERAGE(F969,F979,F1004)</f>
+        <v>17.005485246666662</v>
+      </c>
+      <c r="H1004" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -69281,20 +69294,20 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="1035" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A1035" t="s">
+    <row r="1035" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1035" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1035" s="2">
+      <c r="B1035" s="6">
         <v>44685</v>
       </c>
-      <c r="C1035">
+      <c r="C1035" s="7">
         <v>2022</v>
       </c>
-      <c r="E1035" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1035">
+      <c r="E1035" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1035" s="7">
         <f>(SingleBerryDW!F1035/SingleBerryFW!F1035)*100</f>
         <v>15.8</v>
       </c>
@@ -69479,20 +69492,20 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1046" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A1046" t="s">
+    <row r="1046" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1046" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1046" s="2">
+      <c r="B1046" s="6">
         <v>44685</v>
       </c>
-      <c r="C1046">
+      <c r="C1046" s="7">
         <v>2022</v>
       </c>
-      <c r="E1046" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1046">
+      <c r="E1046" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1046" s="7">
         <f>(SingleBerryDW!F1046/SingleBerryFW!F1046)*100</f>
         <v>18.3</v>
       </c>
@@ -69678,20 +69691,20 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="1057" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A1057" t="s">
+    <row r="1057" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1057" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1057" s="2">
+      <c r="B1057" s="6">
         <v>44685</v>
       </c>
-      <c r="C1057">
+      <c r="C1057" s="7">
         <v>2022</v>
       </c>
-      <c r="E1057" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1057">
+      <c r="E1057" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1057" s="7">
         <f>(SingleBerryDW!F1057/SingleBerryFW!F1057)*100</f>
         <v>18.899999999999999</v>
       </c>
@@ -69876,20 +69889,20 @@
         <v>17.599999999999998</v>
       </c>
     </row>
-    <row r="1068" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A1068" t="s">
+    <row r="1068" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1068" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1068" s="2">
+      <c r="B1068" s="6">
         <v>44685</v>
       </c>
-      <c r="C1068">
+      <c r="C1068" s="7">
         <v>2022</v>
       </c>
-      <c r="E1068" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1068">
+      <c r="E1068" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1068" s="7">
         <f>(SingleBerryDW!F1068/SingleBerryFW!F1068)*100</f>
         <v>18.199999999999996</v>
       </c>
@@ -70074,27 +70087,28 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="1079" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A1079" t="s">
+    <row r="1079" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1079" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1079" s="2">
+      <c r="B1079" s="6">
         <v>44685</v>
       </c>
-      <c r="C1079">
+      <c r="C1079" s="7">
         <v>2022</v>
       </c>
-      <c r="E1079" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1079">
+      <c r="E1079" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1079" s="7">
         <f>(SingleBerryDW!F1079/SingleBerryFW!F1079)*100</f>
         <v>14.6</v>
       </c>
-      <c r="G1079">
+      <c r="G1079" s="7">
+        <f>AVERAGE(F1079,F1068,F1057,F1046,F1035)</f>
         <v>17.16</v>
       </c>
-      <c r="H1079" t="s">
+      <c r="H1079" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -70314,8 +70328,7 @@
         <v>18.000000000000004</v>
       </c>
       <c r="G1091">
-        <f>F1091</f>
-        <v>18.000000000000004</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="H1091" t="s">
         <v>27</v>
@@ -71540,7 +71553,7 @@
         <v>19.300000000000004</v>
       </c>
     </row>
-    <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
         <v>18</v>
       </c>
@@ -71558,7 +71571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
         <v>18</v>
       </c>
@@ -71576,7 +71589,7 @@
         <v>12.000000000000002</v>
       </c>
     </row>
-    <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
         <v>18</v>
       </c>
@@ -71594,7 +71607,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
         <v>18</v>
       </c>
@@ -71612,7 +71625,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
         <v>18</v>
       </c>
@@ -71630,7 +71643,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
         <v>18</v>
       </c>
@@ -71648,25 +71661,25 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1165" t="s">
+    <row r="1165" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1165" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1165" s="2">
+      <c r="B1165" s="6">
         <v>45404</v>
       </c>
-      <c r="C1165">
+      <c r="C1165" s="7">
         <v>2024</v>
       </c>
-      <c r="E1165" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1165">
+      <c r="E1165" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1165" s="7">
         <f>(SingleBerryDW!F1165/SingleBerryFW!F1165)*100</f>
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
         <v>18</v>
       </c>
@@ -71684,7 +71697,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="1167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
         <v>18</v>
       </c>
@@ -71702,7 +71715,7 @@
         <v>17.200000000000003</v>
       </c>
     </row>
-    <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
         <v>18</v>
       </c>
@@ -71720,7 +71733,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="1169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
         <v>18</v>
       </c>
@@ -71738,7 +71751,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="1170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
         <v>18</v>
       </c>
@@ -71756,7 +71769,7 @@
         <v>8.8000000000000025</v>
       </c>
     </row>
-    <row r="1171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
         <v>18</v>
       </c>
@@ -71774,7 +71787,7 @@
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="1172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
         <v>18</v>
       </c>
@@ -71792,7 +71805,7 @@
         <v>13.600000000000001</v>
       </c>
     </row>
-    <row r="1173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
         <v>18</v>
       </c>
@@ -71810,7 +71823,7 @@
         <v>15.300000000000002</v>
       </c>
     </row>
-    <row r="1174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
         <v>18</v>
       </c>
@@ -71828,7 +71841,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="1175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
         <v>18</v>
       </c>
@@ -71846,25 +71859,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1176" t="s">
+    <row r="1176" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1176" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1176" s="2">
+      <c r="B1176" s="6">
         <v>45407</v>
       </c>
-      <c r="C1176">
+      <c r="C1176" s="7">
         <v>2024</v>
       </c>
-      <c r="E1176" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1176">
+      <c r="E1176" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1176" s="7">
         <f>(SingleBerryDW!F1176/SingleBerryFW!F1176)*100</f>
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="1177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
         <v>18</v>
       </c>
@@ -71882,7 +71895,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="1178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1178" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
         <v>18</v>
       </c>
@@ -71900,7 +71913,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="1179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
         <v>18</v>
       </c>
@@ -71918,7 +71931,7 @@
         <v>18.099999999999998</v>
       </c>
     </row>
-    <row r="1180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
         <v>18</v>
       </c>
@@ -71936,7 +71949,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
         <v>18</v>
       </c>
@@ -71954,7 +71967,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="1182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
         <v>18</v>
       </c>
@@ -71972,7 +71985,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="1183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
         <v>18</v>
       </c>
@@ -71990,7 +72003,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="1184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
         <v>18</v>
       </c>
@@ -72008,7 +72021,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
         <v>18</v>
       </c>
@@ -72026,7 +72039,7 @@
         <v>16.400000000000002</v>
       </c>
     </row>
-    <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
         <v>18</v>
       </c>
@@ -72044,25 +72057,25 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1187" t="s">
+    <row r="1187" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1187" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1187" s="2">
+      <c r="B1187" s="6">
         <v>45404</v>
       </c>
-      <c r="C1187">
+      <c r="C1187" s="7">
         <v>2024</v>
       </c>
-      <c r="E1187" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1187">
+      <c r="E1187" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1187" s="7">
         <f>(SingleBerryDW!F1187/SingleBerryFW!F1187)*100</f>
         <v>17.2</v>
       </c>
     </row>
-    <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
         <v>18</v>
       </c>
@@ -72080,7 +72093,7 @@
         <v>17.699999999999996</v>
       </c>
     </row>
-    <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
         <v>18</v>
       </c>
@@ -72098,7 +72111,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
         <v>18</v>
       </c>
@@ -72116,7 +72129,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
         <v>18</v>
       </c>
@@ -72134,7 +72147,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
         <v>18</v>
       </c>
@@ -72152,7 +72165,7 @@
         <v>8.3000000000000025</v>
       </c>
     </row>
-    <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
         <v>18</v>
       </c>
@@ -72170,7 +72183,7 @@
         <v>11.700000000000001</v>
       </c>
     </row>
-    <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
         <v>18</v>
       </c>
@@ -72188,7 +72201,7 @@
         <v>13.600000000000001</v>
       </c>
     </row>
-    <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
         <v>18</v>
       </c>
@@ -72206,7 +72219,7 @@
         <v>15.000000000000002</v>
       </c>
     </row>
-    <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
         <v>18</v>
       </c>
@@ -72224,7 +72237,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
         <v>18</v>
       </c>
@@ -72242,25 +72255,25 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1198" t="s">
+    <row r="1198" spans="1:6" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1198" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1198" s="2">
+      <c r="B1198" s="6">
         <v>45404</v>
       </c>
-      <c r="C1198">
+      <c r="C1198" s="7">
         <v>2024</v>
       </c>
-      <c r="E1198" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1198">
+      <c r="E1198" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1198" s="7">
         <f>(SingleBerryDW!F1198/SingleBerryFW!F1198)*100</f>
         <v>16.2</v>
       </c>
     </row>
-    <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
         <v>18</v>
       </c>
@@ -72278,7 +72291,7 @@
         <v>17.099999999999998</v>
       </c>
     </row>
-    <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
         <v>18</v>
       </c>
@@ -72296,7 +72309,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="1201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
         <v>18</v>
       </c>
@@ -72314,7 +72327,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
         <v>18</v>
       </c>
@@ -72332,7 +72345,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
         <v>18</v>
       </c>
@@ -72350,7 +72363,7 @@
         <v>8.6999999999999975</v>
       </c>
     </row>
-    <row r="1204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
         <v>18</v>
       </c>
@@ -72368,7 +72381,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
         <v>18</v>
       </c>
@@ -72386,7 +72399,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="1206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
         <v>18</v>
       </c>
@@ -72404,7 +72417,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
         <v>18</v>
       </c>
@@ -72422,7 +72435,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="1208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
         <v>18</v>
       </c>
@@ -72439,33 +72452,32 @@
         <f>(SingleBerryDW!F1208/SingleBerryFW!F1208)*100</f>
         <v>16.499999999999996</v>
       </c>
-      <c r="G1208">
-        <f>F1208</f>
-        <v>16.499999999999996</v>
-      </c>
-      <c r="H1208" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="1209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1209" t="s">
+    </row>
+    <row r="1209" spans="1:8" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1209" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1209" s="2">
+      <c r="B1209" s="6">
         <v>45407</v>
       </c>
-      <c r="C1209">
+      <c r="C1209" s="7">
         <v>2024</v>
       </c>
-      <c r="E1209" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1209">
+      <c r="E1209" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1209" s="7">
         <f>(SingleBerryDW!F1209/SingleBerryFW!F1209)*100</f>
         <v>16.5</v>
       </c>
-    </row>
-    <row r="1210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G1209" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="H1209" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
         <v>18</v>
       </c>
@@ -72483,7 +72495,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="1211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
         <v>18</v>
       </c>
@@ -72501,7 +72513,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
         <v>18</v>
       </c>
@@ -72519,7 +72531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
         <v>18</v>
       </c>
@@ -72537,7 +72549,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="1214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
         <v>23</v>
       </c>
@@ -72555,7 +72567,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="1215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
         <v>23</v>
       </c>
@@ -72573,7 +72585,7 @@
         <v>13.100000000000001</v>
       </c>
     </row>
-    <row r="1216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
         <v>23</v>
       </c>
@@ -72591,7 +72603,7 @@
         <v>14.900000000000002</v>
       </c>
     </row>
-    <row r="1217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
         <v>23</v>
       </c>
@@ -72609,7 +72621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
         <v>23</v>
       </c>
@@ -72627,7 +72639,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="1219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
         <v>23</v>
       </c>
@@ -72645,7 +72657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
         <v>23</v>
       </c>
@@ -72669,7 +72681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
         <v>23</v>
       </c>
@@ -72687,7 +72699,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="1222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
         <v>23</v>
       </c>
@@ -72705,7 +72717,7 @@
         <v>17.899999999999995</v>
       </c>
     </row>
-    <row r="1223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
         <v>23</v>
       </c>
@@ -72723,7 +72735,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="1224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
         <v>23</v>
       </c>
@@ -72757,7 +72769,7 @@
   <autoFilter ref="A1:A1228" xr:uid="{B3CAF195-1F50-4308-BA2B-F7BFA06853CA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="TPHW2024"/>
+        <filter val="KKHW2024"/>
       </filters>
     </filterColumn>
   </autoFilter>
